--- a/files/diet-reference-config-v1.0.0.xlsx
+++ b/files/diet-reference-config-v1.0.0.xlsx
@@ -4521,7 +4521,7 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>{지난 끼니}에 고기·생선·달걀·두부를 드셨나요?</t>
+    <t>{지난 끼니}에 단백질류(고기·생선·달걀 등)를 드셨나요?</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>

--- a/files/diet-reference-config-v1.0.0.xlsx
+++ b/files/diet-reference-config-v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{375CEEFA-D5E6-468B-A420-1597CC3EF1D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D6D5B64-1199-434F-849A-1FA7F6961367}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4267,10 +4267,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>거의 못 먹거나 거름</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>한 끼는 싱겁게 먹기</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -13855,10 +13851,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>전날 저녁 식사 후~당일 04:00 전의 야식 자기보고 양(간단히 / 한 끼만큼). 오늘 아침 식사는 제외. 위해성·수면 영향 판정 아님</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>야식 여부·양만 저장. 필요한 간식과 교대근무 상황은 구분할 수 없어 좋음/나쁨 등급 산출 중지</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -13867,10 +13859,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>한 끼만큼 먹었어요</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>light</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -13879,10 +13867,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>{지난 끼니}을 드신 뒤 배는 얼마나 불렀나요?</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>{지난 끼니}엔 단백질류(고기·생선·달걀 등)를 드셨나요?</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -14301,6 +14285,743 @@
   </si>
   <si>
     <r>
+      <t>질문</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시트</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> DIET-Q-01·02·03·05·06·07 · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>참조설정데이터</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축정의</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>야식</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질문을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>횟수에서</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>양으로</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>어젯밤</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>야식을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>몇</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>번</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>드셨나요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">? · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>안</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹었어요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>번</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>두</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>번</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이상</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>질문</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시트</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> DIET-Q-04 · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>선택지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시트</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 14~16</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>참조설정데이터</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축정의</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>어젯밤</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>야식은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>얼마나</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>드셨나요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">? · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>안</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹었어요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>간단히</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹었어요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>배부르게</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹었어요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>선택지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>코드는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> none · light · meal_sized, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>점수는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>그대로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>없음</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>배부르게 먹었어요</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>전날 저녁 식사 후~당일 04:00 전의 야식 자기보고 양(간단히 / 배부르게). 오늘 아침 식사는 제외. 위해성·수면 영향 판정 아님</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
       <t>{끼니</t>
     </r>
     <r>
@@ -14681,26 +15402,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>얼마나</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>불렀나요</t>
+      <t>어땠나요</t>
     </r>
     <r>
       <rPr>
@@ -14930,753 +15632,15 @@
       </rPr>
       <t>지킴</t>
     </r>
-  </si>
-  <si>
-    <r>
-      <t>질문</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시트</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> DIET-Q-01·02·03·05·06·07 · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>참조설정데이터</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축정의</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>야식</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>질문을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>횟수에서</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>양으로</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>어젯밤</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>야식을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>몇</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>번</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>드셨나요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">? · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>안</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>먹었어요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>한</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>번</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>두</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>번</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>이상</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>어젯밤</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>야식은</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>얼마나</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>드셨나요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">? · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>안</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>먹었어요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>간단히</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>먹었어요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>한</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>끼만큼</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>먹었어요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>선택지</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>코드는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> none · light · meal_sized, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>점수는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>그대로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>없음</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>질문</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시트</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> DIET-Q-04 · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>선택지</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시트</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 14~16</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>행</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>참조설정데이터</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축정의</t>
-    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>{지난 끼니}을 드신 뒤 배는 어땠나요?</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>거의 못 먹거나 걸렀어요</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -16266,16 +16230,16 @@
   <sheetData>
     <row r="1" spans="1:3" ht="35" customHeight="1">
       <c r="A1" s="14" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="C1" s="2"/>
     </row>
     <row r="2" spans="1:3" ht="24" customHeight="1">
       <c r="A2" s="11" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -16498,7 +16462,7 @@
         <v>46</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="24" customHeight="1">
@@ -16517,7 +16481,7 @@
         <v>49</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>50</v>
@@ -16698,82 +16662,82 @@
     <row r="44" spans="1:3" ht="24" customHeight="1"/>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
+        <v>1533</v>
+      </c>
+      <c r="B49" t="s">
         <v>1534</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49" t="s">
         <v>1535</v>
       </c>
-      <c r="C49" t="s">
+      <c r="D49" t="s">
         <v>1536</v>
-      </c>
-      <c r="D49" t="s">
-        <v>1537</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
+        <v>1537</v>
+      </c>
+      <c r="B50" t="s">
         <v>1538</v>
       </c>
-      <c r="B50" t="s">
+      <c r="C50" t="s">
+        <v>1655</v>
+      </c>
+      <c r="D50" t="s">
         <v>1539</v>
-      </c>
-      <c r="C50" t="s">
-        <v>1659</v>
-      </c>
-      <c r="D50" t="s">
-        <v>1540</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="12" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B51" s="12" t="s">
         <v>1541</v>
       </c>
-      <c r="B51" s="12" t="s">
+      <c r="C51" s="12" t="s">
         <v>1542</v>
       </c>
-      <c r="C51" s="12" t="s">
+      <c r="D51" s="12" t="s">
         <v>1543</v>
-      </c>
-      <c r="D51" s="12" t="s">
-        <v>1544</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="12" t="s">
-        <v>1661</v>
+        <v>1657</v>
       </c>
       <c r="B52" s="12" t="s">
-        <v>1662</v>
+        <v>1658</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>1663</v>
+        <v>1666</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>1664</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="12" t="s">
-        <v>1665</v>
+        <v>1660</v>
       </c>
       <c r="B53" s="12" t="s">
-        <v>1666</v>
+        <v>1661</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>1668</v>
+        <v>1662</v>
       </c>
     </row>
   </sheetData>
@@ -21524,7 +21488,7 @@
         <v>1119</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="H5" s="10">
         <v>11</v>
@@ -21669,7 +21633,7 @@
         <v>1115</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="H8" s="8">
         <v>11</v>
@@ -21718,7 +21682,7 @@
         <v>1119</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="H9" s="8">
         <v>12</v>
@@ -21814,7 +21778,7 @@
         <v>1115</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="H11" s="10">
         <v>12</v>
@@ -21914,7 +21878,7 @@
         <v>1119</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="H13" s="10">
         <v>11</v>
@@ -22059,7 +22023,7 @@
         <v>1115</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="H16" s="10">
         <v>11</v>
@@ -22106,13 +22070,13 @@
         <v>1119</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="H17" s="10">
         <v>9</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="J17" s="8"/>
       <c r="K17" s="8"/>
@@ -22296,7 +22260,7 @@
         <v>1110</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="H21" s="10">
         <v>12</v>
@@ -22345,7 +22309,7 @@
         <v>1115</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="H22" s="10">
         <v>11</v>
@@ -22394,7 +22358,7 @@
         <v>1119</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="H23" s="10">
         <v>12</v>
@@ -22639,7 +22603,7 @@
         <v>1160</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="H28" s="10">
         <v>10</v>
@@ -22688,7 +22652,7 @@
         <v>1160</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="H29" s="10">
         <v>11</v>
@@ -22739,7 +22703,7 @@
         <v>1160</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="H30" s="10">
         <v>14</v>
@@ -22786,7 +22750,7 @@
         <v>1160</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="H31" s="10">
         <v>12</v>
@@ -22884,7 +22848,7 @@
         <v>1110</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="H33" s="10">
         <v>11</v>
@@ -22935,7 +22899,7 @@
         <v>1115</v>
       </c>
       <c r="G34" s="10" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="H34" s="10">
         <v>11</v>
@@ -23135,7 +23099,7 @@
         <v>1110</v>
       </c>
       <c r="G38" s="10" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="H38" s="10">
         <v>11</v>
@@ -23288,7 +23252,7 @@
         <v>1119</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="H41" s="8">
         <v>11</v>
@@ -23486,7 +23450,7 @@
         <v>1119</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="H45" s="10">
         <v>11</v>
@@ -23588,7 +23552,7 @@
         <v>1110</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="H47" s="10">
         <v>10</v>
@@ -23739,7 +23703,7 @@
         <v>1119</v>
       </c>
       <c r="G50" s="10" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="H50" s="10">
         <v>9</v>
@@ -23788,7 +23752,7 @@
         <v>1119</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="H51" s="10">
         <v>12</v>
@@ -24090,7 +24054,7 @@
         <v>1119</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="H57" s="10">
         <v>12</v>
@@ -24190,7 +24154,7 @@
         <v>1110</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="H59" s="10">
         <v>12</v>
@@ -24494,7 +24458,7 @@
         <v>1115</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="H65" s="10">
         <v>10</v>
@@ -24596,7 +24560,7 @@
         <v>1119</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="H67" s="10">
         <v>11</v>
@@ -24696,7 +24660,7 @@
         <v>1119</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="H69" s="10">
         <v>12</v>
@@ -24747,7 +24711,7 @@
         <v>1119</v>
       </c>
       <c r="G70" s="10" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="H70" s="10">
         <v>12</v>
@@ -25049,7 +25013,7 @@
         <v>1119</v>
       </c>
       <c r="G76" s="10" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="H76" s="10">
         <v>10</v>
@@ -25100,7 +25064,7 @@
         <v>1115</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="H77" s="10">
         <v>10</v>
@@ -25455,7 +25419,7 @@
         <v>1119</v>
       </c>
       <c r="G84" s="10" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="H84" s="10">
         <v>12</v>
@@ -25602,7 +25566,7 @@
         <v>1119</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="H87" s="10">
         <v>10</v>
@@ -25702,7 +25666,7 @@
         <v>1119</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="H89" s="10">
         <v>11</v>
@@ -25853,7 +25817,7 @@
         <v>1119</v>
       </c>
       <c r="G92" s="10" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="H92" s="10">
         <v>12</v>
@@ -26002,7 +25966,7 @@
         <v>1119</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="H95" s="10">
         <v>11</v>
@@ -26053,7 +26017,7 @@
         <v>1119</v>
       </c>
       <c r="G96" s="10" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="H96" s="10">
         <v>11</v>
@@ -26153,7 +26117,7 @@
         <v>1115</v>
       </c>
       <c r="G98" s="10" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="H98" s="10">
         <v>12</v>
@@ -26506,7 +26470,7 @@
         <v>1160</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="H105" s="10">
         <v>12</v>
@@ -26608,7 +26572,7 @@
         <v>1160</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="H107" s="8">
         <v>12</v>
@@ -26710,7 +26674,7 @@
         <v>1119</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="H109" s="10">
         <v>11</v>
@@ -26861,7 +26825,7 @@
         <v>1119</v>
       </c>
       <c r="G112" s="10" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="H112" s="10">
         <v>12</v>
@@ -26961,7 +26925,7 @@
         <v>1110</v>
       </c>
       <c r="G114" s="10" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="H114" s="10">
         <v>10</v>
@@ -27063,7 +27027,7 @@
         <v>1110</v>
       </c>
       <c r="G116" s="10" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="H116" s="10">
         <v>12</v>
@@ -27420,7 +27384,7 @@
         <v>1115</v>
       </c>
       <c r="G123" s="10" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="H123" s="10">
         <v>11</v>
@@ -27569,7 +27533,7 @@
         <v>1110</v>
       </c>
       <c r="G126" s="10" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="H126" s="8">
         <v>12</v>
@@ -27669,7 +27633,7 @@
         <v>1110</v>
       </c>
       <c r="G128" s="10" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="H128" s="10">
         <v>12</v>
@@ -27820,7 +27784,7 @@
         <v>1160</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="H131" s="10">
         <v>11</v>
@@ -28065,7 +28029,7 @@
         <v>1119</v>
       </c>
       <c r="G136" s="10" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="H136" s="10">
         <v>10</v>
@@ -28457,7 +28421,7 @@
         <v>1160</v>
       </c>
       <c r="G144" s="10" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="H144" s="10">
         <v>12</v>
@@ -28491,49 +28455,49 @@
         <v>172</v>
       </c>
       <c r="B145" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C145" t="s">
         <v>1575</v>
       </c>
-      <c r="C145" t="s">
+      <c r="D145" t="s">
         <v>1576</v>
       </c>
-      <c r="D145" t="s">
+      <c r="E145" t="s">
         <v>1577</v>
       </c>
-      <c r="E145" t="s">
+      <c r="F145" t="s">
+        <v>1566</v>
+      </c>
+      <c r="G145" t="s">
         <v>1578</v>
-      </c>
-      <c r="F145" t="s">
-        <v>1567</v>
-      </c>
-      <c r="G145" t="s">
-        <v>1579</v>
       </c>
       <c r="H145">
         <v>11</v>
       </c>
       <c r="I145" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="J145" t="s">
         <v>986</v>
       </c>
       <c r="L145" t="s">
+        <v>1580</v>
+      </c>
+      <c r="M145" t="s">
+        <v>1480</v>
+      </c>
+      <c r="N145" t="s">
         <v>1581</v>
       </c>
-      <c r="M145" t="s">
+      <c r="O145" t="s">
         <v>1481</v>
-      </c>
-      <c r="N145" t="s">
-        <v>1582</v>
-      </c>
-      <c r="O145" t="s">
-        <v>1482</v>
       </c>
       <c r="P145" t="s">
         <v>104</v>
       </c>
       <c r="Q145" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="146" spans="1:17">
@@ -28541,46 +28505,46 @@
         <v>173</v>
       </c>
       <c r="B146" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C146" t="s">
         <v>1575</v>
       </c>
-      <c r="C146" t="s">
+      <c r="D146" t="s">
         <v>1576</v>
       </c>
-      <c r="D146" t="s">
+      <c r="E146" t="s">
         <v>1577</v>
       </c>
-      <c r="E146" t="s">
-        <v>1578</v>
-      </c>
       <c r="F146" t="s">
+        <v>1582</v>
+      </c>
+      <c r="G146" t="s">
         <v>1583</v>
-      </c>
-      <c r="G146" t="s">
-        <v>1584</v>
       </c>
       <c r="H146">
         <v>8</v>
       </c>
       <c r="I146" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="J146" t="s">
         <v>986</v>
       </c>
       <c r="M146" t="s">
+        <v>1482</v>
+      </c>
+      <c r="N146" t="s">
+        <v>1581</v>
+      </c>
+      <c r="O146" t="s">
         <v>1483</v>
-      </c>
-      <c r="N146" t="s">
-        <v>1582</v>
-      </c>
-      <c r="O146" t="s">
-        <v>1484</v>
       </c>
       <c r="P146" t="s">
         <v>104</v>
       </c>
       <c r="Q146" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="147" spans="1:17">
@@ -28588,46 +28552,46 @@
         <v>174</v>
       </c>
       <c r="B147" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C147" t="s">
         <v>1575</v>
       </c>
-      <c r="C147" t="s">
+      <c r="D147" t="s">
         <v>1576</v>
       </c>
-      <c r="D147" t="s">
-        <v>1577</v>
-      </c>
       <c r="E147" t="s">
+        <v>1585</v>
+      </c>
+      <c r="F147" t="s">
+        <v>1582</v>
+      </c>
+      <c r="G147" t="s">
         <v>1586</v>
-      </c>
-      <c r="F147" t="s">
-        <v>1583</v>
-      </c>
-      <c r="G147" t="s">
-        <v>1587</v>
       </c>
       <c r="H147">
         <v>10</v>
       </c>
       <c r="I147" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="J147" t="s">
         <v>986</v>
       </c>
       <c r="M147" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="N147" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="O147" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="P147" t="s">
         <v>104</v>
       </c>
       <c r="Q147" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="148" spans="1:17">
@@ -28635,46 +28599,46 @@
         <v>175</v>
       </c>
       <c r="B148" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C148" t="s">
         <v>1575</v>
       </c>
-      <c r="C148" t="s">
+      <c r="D148" t="s">
         <v>1576</v>
       </c>
-      <c r="D148" t="s">
-        <v>1577</v>
-      </c>
       <c r="E148" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="F148" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="G148" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H148">
         <v>11</v>
       </c>
       <c r="I148" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="J148" t="s">
         <v>986</v>
       </c>
       <c r="M148" t="s">
+        <v>1485</v>
+      </c>
+      <c r="N148" t="s">
+        <v>1581</v>
+      </c>
+      <c r="O148" t="s">
         <v>1486</v>
-      </c>
-      <c r="N148" t="s">
-        <v>1582</v>
-      </c>
-      <c r="O148" t="s">
-        <v>1487</v>
       </c>
       <c r="P148" t="s">
         <v>104</v>
       </c>
       <c r="Q148" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="149" spans="1:17">
@@ -28682,46 +28646,46 @@
         <v>176</v>
       </c>
       <c r="B149" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C149" t="s">
         <v>1575</v>
       </c>
-      <c r="C149" t="s">
+      <c r="D149" t="s">
         <v>1576</v>
       </c>
-      <c r="D149" t="s">
-        <v>1577</v>
-      </c>
       <c r="E149" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="F149" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="G149" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="H149">
         <v>10</v>
       </c>
       <c r="I149" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="J149" t="s">
         <v>986</v>
       </c>
       <c r="M149" t="s">
+        <v>1487</v>
+      </c>
+      <c r="N149" t="s">
+        <v>1581</v>
+      </c>
+      <c r="O149" t="s">
         <v>1488</v>
-      </c>
-      <c r="N149" t="s">
-        <v>1582</v>
-      </c>
-      <c r="O149" t="s">
-        <v>1489</v>
       </c>
       <c r="P149" t="s">
         <v>104</v>
       </c>
       <c r="Q149" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="150" spans="1:17">
@@ -28729,46 +28693,46 @@
         <v>177</v>
       </c>
       <c r="B150" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C150" t="s">
         <v>1575</v>
       </c>
-      <c r="C150" t="s">
+      <c r="D150" t="s">
         <v>1576</v>
       </c>
-      <c r="D150" t="s">
-        <v>1577</v>
-      </c>
       <c r="E150" t="s">
+        <v>1592</v>
+      </c>
+      <c r="F150" t="s">
+        <v>1566</v>
+      </c>
+      <c r="G150" t="s">
         <v>1593</v>
-      </c>
-      <c r="F150" t="s">
-        <v>1567</v>
-      </c>
-      <c r="G150" t="s">
-        <v>1594</v>
       </c>
       <c r="H150">
         <v>11</v>
       </c>
       <c r="I150" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="J150" t="s">
         <v>986</v>
       </c>
       <c r="M150" t="s">
+        <v>1489</v>
+      </c>
+      <c r="N150" t="s">
+        <v>1581</v>
+      </c>
+      <c r="O150" t="s">
         <v>1490</v>
-      </c>
-      <c r="N150" t="s">
-        <v>1582</v>
-      </c>
-      <c r="O150" t="s">
-        <v>1491</v>
       </c>
       <c r="P150" t="s">
         <v>104</v>
       </c>
       <c r="Q150" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="151" spans="1:17">
@@ -28776,46 +28740,46 @@
         <v>178</v>
       </c>
       <c r="B151" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C151" t="s">
         <v>1575</v>
       </c>
-      <c r="C151" t="s">
+      <c r="D151" t="s">
         <v>1576</v>
       </c>
-      <c r="D151" t="s">
-        <v>1577</v>
-      </c>
       <c r="E151" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="F151" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="G151" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H151">
         <v>10</v>
       </c>
       <c r="I151" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="J151" t="s">
         <v>986</v>
       </c>
       <c r="M151" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="N151" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="O151" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="P151" t="s">
         <v>104</v>
       </c>
       <c r="Q151" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="152" spans="1:17">
@@ -28823,46 +28787,46 @@
         <v>179</v>
       </c>
       <c r="B152" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C152" t="s">
         <v>1575</v>
       </c>
-      <c r="C152" t="s">
+      <c r="D152" t="s">
         <v>1576</v>
       </c>
-      <c r="D152" t="s">
-        <v>1577</v>
-      </c>
       <c r="E152" t="s">
+        <v>1597</v>
+      </c>
+      <c r="F152" t="s">
+        <v>1566</v>
+      </c>
+      <c r="G152" t="s">
         <v>1598</v>
-      </c>
-      <c r="F152" t="s">
-        <v>1567</v>
-      </c>
-      <c r="G152" t="s">
-        <v>1599</v>
       </c>
       <c r="H152">
         <v>12</v>
       </c>
       <c r="I152" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="J152" t="s">
         <v>986</v>
       </c>
       <c r="M152" t="s">
+        <v>1492</v>
+      </c>
+      <c r="N152" t="s">
+        <v>1581</v>
+      </c>
+      <c r="O152" t="s">
         <v>1493</v>
-      </c>
-      <c r="N152" t="s">
-        <v>1582</v>
-      </c>
-      <c r="O152" t="s">
-        <v>1494</v>
       </c>
       <c r="P152" t="s">
         <v>104</v>
       </c>
       <c r="Q152" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="153" spans="1:17">
@@ -28870,46 +28834,46 @@
         <v>180</v>
       </c>
       <c r="B153" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C153" t="s">
         <v>1575</v>
       </c>
-      <c r="C153" t="s">
+      <c r="D153" t="s">
         <v>1576</v>
       </c>
-      <c r="D153" t="s">
-        <v>1577</v>
-      </c>
       <c r="E153" t="s">
+        <v>1600</v>
+      </c>
+      <c r="F153" t="s">
+        <v>1566</v>
+      </c>
+      <c r="G153" t="s">
         <v>1601</v>
-      </c>
-      <c r="F153" t="s">
-        <v>1567</v>
-      </c>
-      <c r="G153" t="s">
-        <v>1602</v>
       </c>
       <c r="H153">
         <v>12</v>
       </c>
       <c r="I153" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="J153" t="s">
         <v>986</v>
       </c>
       <c r="M153" t="s">
+        <v>1494</v>
+      </c>
+      <c r="N153" t="s">
+        <v>1581</v>
+      </c>
+      <c r="O153" t="s">
         <v>1495</v>
-      </c>
-      <c r="N153" t="s">
-        <v>1582</v>
-      </c>
-      <c r="O153" t="s">
-        <v>1496</v>
       </c>
       <c r="P153" t="s">
         <v>104</v>
       </c>
       <c r="Q153" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="154" spans="1:17">
@@ -28917,46 +28881,46 @@
         <v>181</v>
       </c>
       <c r="B154" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C154" t="s">
         <v>1575</v>
       </c>
-      <c r="C154" t="s">
+      <c r="D154" t="s">
         <v>1576</v>
       </c>
-      <c r="D154" t="s">
-        <v>1577</v>
-      </c>
       <c r="E154" t="s">
+        <v>1603</v>
+      </c>
+      <c r="F154" t="s">
         <v>1604</v>
       </c>
-      <c r="F154" t="s">
+      <c r="G154" t="s">
         <v>1605</v>
-      </c>
-      <c r="G154" t="s">
-        <v>1606</v>
       </c>
       <c r="H154">
         <v>12</v>
       </c>
       <c r="I154" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="J154" t="s">
         <v>986</v>
       </c>
       <c r="M154" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="N154" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="O154" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="P154" t="s">
         <v>104</v>
       </c>
       <c r="Q154" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="155" spans="1:17">
@@ -28964,46 +28928,46 @@
         <v>182</v>
       </c>
       <c r="B155" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C155" t="s">
         <v>1575</v>
       </c>
-      <c r="C155" t="s">
+      <c r="D155" t="s">
         <v>1576</v>
       </c>
-      <c r="D155" t="s">
-        <v>1577</v>
-      </c>
       <c r="E155" t="s">
+        <v>1603</v>
+      </c>
+      <c r="F155" t="s">
         <v>1604</v>
       </c>
-      <c r="F155" t="s">
-        <v>1605</v>
-      </c>
       <c r="G155" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="H155">
         <v>11</v>
       </c>
       <c r="I155" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="J155" t="s">
         <v>986</v>
       </c>
       <c r="M155" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="N155" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="O155" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="P155" t="s">
         <v>104</v>
       </c>
       <c r="Q155" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="156" spans="1:17">
@@ -29011,46 +28975,46 @@
         <v>183</v>
       </c>
       <c r="B156" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C156" t="s">
         <v>1575</v>
       </c>
-      <c r="C156" t="s">
+      <c r="D156" t="s">
         <v>1576</v>
       </c>
-      <c r="D156" t="s">
-        <v>1577</v>
-      </c>
       <c r="E156" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="F156" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="G156" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="H156">
         <v>10</v>
       </c>
       <c r="I156" t="s">
+        <v>1610</v>
+      </c>
+      <c r="J156" t="s">
         <v>1611</v>
       </c>
-      <c r="J156" t="s">
-        <v>1612</v>
-      </c>
       <c r="M156" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="N156" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="O156" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="P156" t="s">
         <v>104</v>
       </c>
       <c r="Q156" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="157" spans="1:17">
@@ -29058,49 +29022,49 @@
         <v>184</v>
       </c>
       <c r="B157" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C157" t="s">
         <v>1575</v>
       </c>
-      <c r="C157" t="s">
+      <c r="D157" t="s">
         <v>1576</v>
       </c>
-      <c r="D157" t="s">
-        <v>1577</v>
-      </c>
       <c r="E157" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="F157" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="G157" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="H157">
         <v>10</v>
       </c>
       <c r="I157" t="s">
+        <v>1613</v>
+      </c>
+      <c r="J157" t="s">
+        <v>1611</v>
+      </c>
+      <c r="L157" t="s">
         <v>1614</v>
       </c>
-      <c r="J157" t="s">
-        <v>1612</v>
-      </c>
-      <c r="L157" t="s">
-        <v>1615</v>
-      </c>
       <c r="M157" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="N157" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="O157" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="P157" t="s">
         <v>104</v>
       </c>
       <c r="Q157" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="158" spans="1:17">
@@ -29108,49 +29072,49 @@
         <v>185</v>
       </c>
       <c r="B158" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C158" t="s">
         <v>1575</v>
       </c>
-      <c r="C158" t="s">
+      <c r="D158" t="s">
         <v>1576</v>
       </c>
-      <c r="D158" t="s">
+      <c r="E158" t="s">
         <v>1577</v>
       </c>
-      <c r="E158" t="s">
-        <v>1578</v>
-      </c>
       <c r="F158" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="G158" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="H158">
         <v>10</v>
       </c>
       <c r="I158" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="J158" t="s">
         <v>986</v>
       </c>
       <c r="L158" t="s">
+        <v>1580</v>
+      </c>
+      <c r="M158" t="s">
+        <v>1480</v>
+      </c>
+      <c r="N158" t="s">
         <v>1581</v>
       </c>
-      <c r="M158" t="s">
-        <v>1481</v>
-      </c>
-      <c r="N158" t="s">
-        <v>1582</v>
-      </c>
       <c r="O158" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="P158" t="s">
         <v>104</v>
       </c>
       <c r="Q158" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="159" spans="1:17">
@@ -29158,46 +29122,46 @@
         <v>186</v>
       </c>
       <c r="B159" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C159" t="s">
         <v>1575</v>
       </c>
-      <c r="C159" t="s">
+      <c r="D159" t="s">
         <v>1576</v>
       </c>
-      <c r="D159" t="s">
-        <v>1577</v>
-      </c>
       <c r="E159" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="F159" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="G159" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="H159">
         <v>10</v>
       </c>
       <c r="I159" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="J159" t="s">
         <v>986</v>
       </c>
       <c r="M159" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="N159" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="O159" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="P159" t="s">
         <v>104</v>
       </c>
       <c r="Q159" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="160" spans="1:17">
@@ -29205,46 +29169,46 @@
         <v>187</v>
       </c>
       <c r="B160" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C160" t="s">
         <v>1575</v>
       </c>
-      <c r="C160" t="s">
+      <c r="D160" t="s">
         <v>1576</v>
       </c>
-      <c r="D160" t="s">
-        <v>1577</v>
-      </c>
       <c r="E160" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="F160" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="G160" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="H160">
         <v>9</v>
       </c>
       <c r="I160" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="J160" t="s">
         <v>986</v>
       </c>
       <c r="M160" t="s">
+        <v>1502</v>
+      </c>
+      <c r="N160" t="s">
+        <v>1581</v>
+      </c>
+      <c r="O160" t="s">
         <v>1503</v>
-      </c>
-      <c r="N160" t="s">
-        <v>1582</v>
-      </c>
-      <c r="O160" t="s">
-        <v>1504</v>
       </c>
       <c r="P160" t="s">
         <v>104</v>
       </c>
       <c r="Q160" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="161" spans="1:17">
@@ -29252,46 +29216,46 @@
         <v>188</v>
       </c>
       <c r="B161" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C161" t="s">
         <v>1575</v>
       </c>
-      <c r="C161" t="s">
+      <c r="D161" t="s">
         <v>1576</v>
       </c>
-      <c r="D161" t="s">
-        <v>1577</v>
-      </c>
       <c r="E161" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="F161" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="G161" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="H161">
         <v>10</v>
       </c>
       <c r="I161" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="J161" t="s">
         <v>986</v>
       </c>
       <c r="M161" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="N161" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="O161" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="P161" t="s">
         <v>104</v>
       </c>
       <c r="Q161" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="162" spans="1:17">
@@ -29299,46 +29263,46 @@
         <v>189</v>
       </c>
       <c r="B162" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C162" t="s">
         <v>1575</v>
       </c>
-      <c r="C162" t="s">
+      <c r="D162" t="s">
         <v>1576</v>
       </c>
-      <c r="D162" t="s">
-        <v>1577</v>
-      </c>
       <c r="E162" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="F162" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="G162" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="H162">
         <v>11</v>
       </c>
       <c r="I162" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="J162" t="s">
         <v>986</v>
       </c>
       <c r="M162" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="N162" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="O162" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="P162" t="s">
         <v>104</v>
       </c>
       <c r="Q162" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="163" spans="1:17">
@@ -29346,46 +29310,46 @@
         <v>190</v>
       </c>
       <c r="B163" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C163" t="s">
         <v>1575</v>
       </c>
-      <c r="C163" t="s">
+      <c r="D163" t="s">
         <v>1576</v>
       </c>
-      <c r="D163" t="s">
-        <v>1577</v>
-      </c>
       <c r="E163" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="F163" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="G163" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="H163">
         <v>8</v>
       </c>
       <c r="I163" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="J163" t="s">
         <v>986</v>
       </c>
       <c r="M163" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="N163" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="O163" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="P163" t="s">
         <v>104</v>
       </c>
       <c r="Q163" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="164" spans="1:17">
@@ -29393,28 +29357,28 @@
         <v>191</v>
       </c>
       <c r="B164" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C164" t="s">
         <v>1575</v>
       </c>
-      <c r="C164" t="s">
+      <c r="D164" t="s">
         <v>1576</v>
       </c>
-      <c r="D164" t="s">
-        <v>1577</v>
-      </c>
       <c r="E164" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="F164" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="G164" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="H164">
         <v>10</v>
       </c>
       <c r="I164" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="J164" t="s">
         <v>986</v>
@@ -29423,10 +29387,10 @@
         <v>1113</v>
       </c>
       <c r="N164" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="O164" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="P164" t="s">
         <v>104</v>
@@ -29440,46 +29404,46 @@
         <v>192</v>
       </c>
       <c r="B165" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C165" t="s">
         <v>1575</v>
       </c>
-      <c r="C165" t="s">
+      <c r="D165" t="s">
         <v>1576</v>
       </c>
-      <c r="D165" t="s">
-        <v>1577</v>
-      </c>
       <c r="E165" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="F165" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="G165" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="H165">
         <v>11</v>
       </c>
       <c r="I165" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="J165" t="s">
         <v>986</v>
       </c>
       <c r="M165" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="N165" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="O165" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="P165" t="s">
         <v>104</v>
       </c>
       <c r="Q165" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="166" spans="1:17">
@@ -29487,46 +29451,46 @@
         <v>193</v>
       </c>
       <c r="B166" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C166" t="s">
         <v>1575</v>
       </c>
-      <c r="C166" t="s">
+      <c r="D166" t="s">
         <v>1576</v>
       </c>
-      <c r="D166" t="s">
-        <v>1577</v>
-      </c>
       <c r="E166" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="F166" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="G166" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="H166">
         <v>11</v>
       </c>
       <c r="I166" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="J166" t="s">
         <v>986</v>
       </c>
       <c r="M166" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="N166" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="O166" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="P166" t="s">
         <v>104</v>
       </c>
       <c r="Q166" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="167" spans="1:17">
@@ -29534,46 +29498,46 @@
         <v>195</v>
       </c>
       <c r="B167" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C167" t="s">
         <v>1575</v>
       </c>
-      <c r="C167" t="s">
+      <c r="D167" t="s">
         <v>1576</v>
       </c>
-      <c r="D167" t="s">
-        <v>1577</v>
-      </c>
       <c r="E167" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="F167" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="G167" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="H167">
         <v>11</v>
       </c>
       <c r="I167" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="J167" t="s">
         <v>986</v>
       </c>
       <c r="M167" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="N167" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="O167" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="P167" t="s">
         <v>104</v>
       </c>
       <c r="Q167" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="168" spans="1:17">
@@ -29581,43 +29545,43 @@
         <v>196</v>
       </c>
       <c r="B168" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C168" t="s">
         <v>1575</v>
       </c>
-      <c r="C168" t="s">
+      <c r="D168" t="s">
         <v>1576</v>
       </c>
-      <c r="D168" t="s">
-        <v>1577</v>
-      </c>
       <c r="F168" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="G168" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="H168">
         <v>8</v>
       </c>
       <c r="I168" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="J168" t="s">
         <v>986</v>
       </c>
       <c r="M168" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="N168" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="O168" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="P168" t="s">
         <v>104</v>
       </c>
       <c r="Q168" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="169" spans="1:17">
@@ -29625,46 +29589,46 @@
         <v>197</v>
       </c>
       <c r="B169" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C169" t="s">
         <v>1575</v>
       </c>
-      <c r="C169" t="s">
+      <c r="D169" t="s">
         <v>1576</v>
       </c>
-      <c r="D169" t="s">
-        <v>1577</v>
-      </c>
       <c r="E169" t="s">
+        <v>1603</v>
+      </c>
+      <c r="F169" t="s">
         <v>1604</v>
       </c>
-      <c r="F169" t="s">
-        <v>1605</v>
-      </c>
       <c r="G169" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="H169">
         <v>10</v>
       </c>
       <c r="I169" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="J169" t="s">
         <v>986</v>
       </c>
       <c r="M169" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="N169" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="O169" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="P169" t="s">
         <v>104</v>
       </c>
       <c r="Q169" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="170" spans="1:17">
@@ -29672,46 +29636,46 @@
         <v>198</v>
       </c>
       <c r="B170" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C170" t="s">
         <v>1575</v>
       </c>
-      <c r="C170" t="s">
+      <c r="D170" t="s">
         <v>1576</v>
       </c>
-      <c r="D170" t="s">
-        <v>1577</v>
-      </c>
       <c r="E170" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="F170" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="G170" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="H170">
         <v>10</v>
       </c>
       <c r="I170" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
       <c r="J170" t="s">
         <v>986</v>
       </c>
       <c r="M170" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="N170" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="O170" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="P170" t="s">
         <v>104</v>
       </c>
       <c r="Q170" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="171" spans="1:17">
@@ -29719,49 +29683,49 @@
         <v>199</v>
       </c>
       <c r="B171" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C171" t="s">
         <v>1575</v>
       </c>
-      <c r="C171" t="s">
+      <c r="D171" t="s">
         <v>1576</v>
       </c>
-      <c r="D171" t="s">
-        <v>1577</v>
-      </c>
       <c r="E171" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="F171" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="G171" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="H171">
         <v>10</v>
       </c>
       <c r="I171" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="J171" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="L171" t="s">
+        <v>1580</v>
+      </c>
+      <c r="M171" t="s">
+        <v>1482</v>
+      </c>
+      <c r="N171" t="s">
         <v>1581</v>
       </c>
-      <c r="M171" t="s">
-        <v>1483</v>
-      </c>
-      <c r="N171" t="s">
-        <v>1582</v>
-      </c>
       <c r="O171" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="P171" t="s">
         <v>104</v>
       </c>
       <c r="Q171" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="172" spans="1:17">
@@ -29769,28 +29733,28 @@
         <v>200</v>
       </c>
       <c r="B172" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C172" t="s">
         <v>1575</v>
       </c>
-      <c r="C172" t="s">
+      <c r="D172" t="s">
         <v>1576</v>
       </c>
-      <c r="D172" t="s">
-        <v>1577</v>
-      </c>
       <c r="E172" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="F172" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="G172" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
       <c r="H172">
         <v>11</v>
       </c>
       <c r="I172" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="J172" t="s">
         <v>986</v>
@@ -29799,10 +29763,10 @@
         <v>1113</v>
       </c>
       <c r="N172" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="O172" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="P172" t="s">
         <v>104</v>
@@ -29816,46 +29780,46 @@
         <v>201</v>
       </c>
       <c r="B173" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C173" t="s">
         <v>1575</v>
       </c>
-      <c r="C173" t="s">
+      <c r="D173" t="s">
         <v>1576</v>
       </c>
-      <c r="D173" t="s">
-        <v>1577</v>
-      </c>
       <c r="E173" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="F173" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="G173" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="H173">
         <v>7</v>
       </c>
       <c r="I173" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="J173" t="s">
         <v>986</v>
       </c>
       <c r="M173" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="N173" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="O173" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="P173" t="s">
         <v>104</v>
       </c>
       <c r="Q173" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
     </row>
   </sheetData>
@@ -29955,7 +29919,7 @@
         <v>97</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>98</v>
@@ -29963,8 +29927,8 @@
       <c r="F2" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="G2" s="11" t="s">
-        <v>1388</v>
+      <c r="G2" s="13" t="s">
+        <v>1668</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>100</v>
@@ -30011,7 +29975,7 @@
         <v>109</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>110</v>
@@ -30067,7 +30031,7 @@
         <v>121</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>122</v>
@@ -30123,7 +30087,7 @@
         <v>131</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>132</v>
@@ -30176,19 +30140,19 @@
         <v>138</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>1652</v>
+        <v>1665</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>132</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>1654</v>
+        <v>1652</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>1655</v>
+        <v>1664</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>139</v>
@@ -30197,7 +30161,7 @@
         <v>140</v>
       </c>
       <c r="J6" s="13" t="s">
-        <v>1653</v>
+        <v>1651</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>141</v>
@@ -30209,10 +30173,10 @@
         <v>119</v>
       </c>
       <c r="N6" s="13" t="s">
-        <v>1656</v>
+        <v>1653</v>
       </c>
       <c r="O6" s="13" t="s">
-        <v>1657</v>
+        <v>1654</v>
       </c>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
@@ -30229,7 +30193,7 @@
         <v>143</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>1658</v>
+        <v>1667</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>144</v>
@@ -30285,7 +30249,7 @@
         <v>152</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>1659</v>
+        <v>1655</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>153</v>
@@ -30341,7 +30305,7 @@
         <v>162</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>1660</v>
+        <v>1656</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>132</v>
@@ -30456,10 +30420,10 @@
         <v>177</v>
       </c>
       <c r="G2" s="11" t="s">
+        <v>1466</v>
+      </c>
+      <c r="H2" s="11" t="s">
         <v>1467</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>1468</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="24" customHeight="1">
@@ -30480,10 +30444,10 @@
         <v>177</v>
       </c>
       <c r="G3" s="11" t="s">
+        <v>1466</v>
+      </c>
+      <c r="H3" s="11" t="s">
         <v>1467</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>1468</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="24" customHeight="1">
@@ -30504,10 +30468,10 @@
         <v>177</v>
       </c>
       <c r="G4" s="11" t="s">
+        <v>1466</v>
+      </c>
+      <c r="H4" s="11" t="s">
         <v>1467</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>1468</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="24" customHeight="1">
@@ -30973,47 +30937,47 @@
         <v>241</v>
       </c>
       <c r="H24" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="B25" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C25" t="s">
         <v>1449</v>
       </c>
-      <c r="C25" t="s">
+      <c r="E25" t="s">
         <v>1450</v>
       </c>
-      <c r="E25" t="s">
+      <c r="G25" t="s">
         <v>1451</v>
       </c>
-      <c r="G25" t="s">
-        <v>1452</v>
-      </c>
       <c r="H25" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="B26" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="C26" t="s">
         <v>187</v>
       </c>
       <c r="E26" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="G26" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="H26" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -31021,19 +30985,19 @@
         <v>417</v>
       </c>
       <c r="B27" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="C27" t="s">
         <v>187</v>
       </c>
       <c r="E27" t="s">
+        <v>1461</v>
+      </c>
+      <c r="G27" t="s">
         <v>1462</v>
       </c>
-      <c r="G27" t="s">
-        <v>1463</v>
-      </c>
       <c r="H27" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -31041,7 +31005,7 @@
         <v>174</v>
       </c>
       <c r="B28" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="C28" t="s">
         <v>187</v>
@@ -31053,10 +31017,10 @@
         <v>188</v>
       </c>
       <c r="G28" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="H28" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -31064,7 +31028,7 @@
         <v>174</v>
       </c>
       <c r="B29" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="C29" t="s">
         <v>176</v>
@@ -31076,10 +31040,10 @@
         <v>193</v>
       </c>
       <c r="G29" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="H29" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -31087,7 +31051,7 @@
         <v>180</v>
       </c>
       <c r="B30" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="C30" t="s">
         <v>187</v>
@@ -31099,10 +31063,10 @@
         <v>193</v>
       </c>
       <c r="G30" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="H30" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -31110,7 +31074,7 @@
         <v>180</v>
       </c>
       <c r="B31" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="C31" t="s">
         <v>200</v>
@@ -31122,10 +31086,10 @@
         <v>188</v>
       </c>
       <c r="G31" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="H31" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -31133,7 +31097,7 @@
         <v>182</v>
       </c>
       <c r="B32" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="C32" t="s">
         <v>187</v>
@@ -31145,10 +31109,10 @@
         <v>193</v>
       </c>
       <c r="G32" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="H32" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -31156,7 +31120,7 @@
         <v>182</v>
       </c>
       <c r="B33" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="C33" t="s">
         <v>200</v>
@@ -31168,10 +31132,10 @@
         <v>188</v>
       </c>
       <c r="G33" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="H33" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -31179,22 +31143,22 @@
         <v>184</v>
       </c>
       <c r="B34" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="C34" t="s">
         <v>187</v>
       </c>
       <c r="E34" t="s">
+        <v>1473</v>
+      </c>
+      <c r="F34" t="s">
         <v>1474</v>
       </c>
-      <c r="F34" t="s">
-        <v>1475</v>
-      </c>
       <c r="G34" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="H34" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -31202,22 +31166,22 @@
         <v>184</v>
       </c>
       <c r="B35" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="C35" t="s">
         <v>187</v>
       </c>
       <c r="E35" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="F35" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="G35" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="H35" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -31225,7 +31189,7 @@
         <v>277</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="C36" s="12" t="s">
         <v>187</v>
@@ -31237,10 +31201,10 @@
         <v>193</v>
       </c>
       <c r="G36" s="12" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="H36" s="12" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -31248,7 +31212,7 @@
         <v>277</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="C37" s="12" t="s">
         <v>176</v>
@@ -31260,10 +31224,10 @@
         <v>193</v>
       </c>
       <c r="G37" s="12" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="H37" s="12" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -31271,7 +31235,7 @@
         <v>277</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="C38" s="12" t="s">
         <v>176</v>
@@ -31283,10 +31247,10 @@
         <v>193</v>
       </c>
       <c r="G38" s="12" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="H38" s="12" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -31294,7 +31258,7 @@
         <v>280</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="C39" s="12" t="s">
         <v>187</v>
@@ -31306,18 +31270,18 @@
         <v>193</v>
       </c>
       <c r="G39" s="12" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="12" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="C40" s="12" t="s">
         <v>200</v>
@@ -31329,10 +31293,10 @@
         <v>188</v>
       </c>
       <c r="G40" s="12" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="H40" s="12" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
     </row>
   </sheetData>
@@ -31550,13 +31514,13 @@
         <v>278</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>279</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="24" customHeight="1">
@@ -31570,7 +31534,7 @@
         <v>281</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>282</v>
@@ -32166,13 +32130,13 @@
         <v>418</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>412</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="24" customHeight="1">
@@ -32500,16 +32464,16 @@
         <v>224</v>
       </c>
       <c r="B58" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="C58" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="D58">
         <v>1</v>
       </c>
       <c r="E58" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -32517,16 +32481,16 @@
         <v>228</v>
       </c>
       <c r="B59" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="C59" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="D59">
         <v>2</v>
       </c>
       <c r="E59" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -32534,16 +32498,16 @@
         <v>230</v>
       </c>
       <c r="B60" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="C60" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="D60">
         <v>3</v>
       </c>
       <c r="E60" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -32551,16 +32515,16 @@
         <v>232</v>
       </c>
       <c r="B61" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="C61" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="D61">
         <v>4</v>
       </c>
       <c r="E61" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -32628,99 +32592,99 @@
         <v>1381</v>
       </c>
       <c r="B65" t="s">
+        <v>1441</v>
+      </c>
+      <c r="C65" t="s">
         <v>1442</v>
       </c>
-      <c r="C65" t="s">
+      <c r="D65" t="s">
         <v>1443</v>
       </c>
-      <c r="D65" t="s">
+      <c r="E65" t="s">
         <v>1444</v>
       </c>
-      <c r="E65" t="s">
+      <c r="F65" t="s">
         <v>1445</v>
-      </c>
-      <c r="F65" t="s">
-        <v>1446</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="B66" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C66" t="s">
         <v>1561</v>
       </c>
-      <c r="C66" t="s">
+      <c r="D66" t="s">
         <v>1562</v>
       </c>
-      <c r="D66" t="s">
+      <c r="E66" t="s">
         <v>1563</v>
       </c>
-      <c r="E66" t="s">
+      <c r="F66" t="s">
         <v>1564</v>
-      </c>
-      <c r="F66" t="s">
-        <v>1565</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="B67" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="C67" t="s">
+        <v>1565</v>
+      </c>
+      <c r="D67" t="s">
         <v>1566</v>
       </c>
-      <c r="D67" t="s">
+      <c r="E67" t="s">
+        <v>1563</v>
+      </c>
+      <c r="F67" t="s">
         <v>1567</v>
-      </c>
-      <c r="E67" t="s">
-        <v>1564</v>
-      </c>
-      <c r="F67" t="s">
-        <v>1568</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="12" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="B68" s="12" t="s">
         <v>42</v>
       </c>
       <c r="C68" s="12" t="s">
+        <v>1568</v>
+      </c>
+      <c r="D68" s="12" t="s">
         <v>1569</v>
       </c>
-      <c r="D68" s="12" t="s">
+      <c r="E68" s="12" t="s">
+        <v>1454</v>
+      </c>
+      <c r="F68" s="12" t="s">
         <v>1570</v>
-      </c>
-      <c r="E68" s="12" t="s">
-        <v>1455</v>
-      </c>
-      <c r="F68" s="12" t="s">
-        <v>1571</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="12" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="B69" s="12" t="s">
         <v>42</v>
       </c>
       <c r="C69" s="12" t="s">
+        <v>1571</v>
+      </c>
+      <c r="D69" s="12" t="s">
         <v>1572</v>
       </c>
-      <c r="D69" s="12" t="s">
+      <c r="E69" s="12" t="s">
+        <v>1454</v>
+      </c>
+      <c r="F69" s="12" t="s">
         <v>1573</v>
-      </c>
-      <c r="E69" s="12" t="s">
-        <v>1455</v>
-      </c>
-      <c r="F69" s="12" t="s">
-        <v>1574</v>
       </c>
     </row>
   </sheetData>
@@ -33139,7 +33103,7 @@
         <v>32</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>544</v>
@@ -33161,7 +33125,7 @@
         <v>573</v>
       </c>
       <c r="L6" s="11" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>550</v>

--- a/files/diet-reference-config-v1.0.0.xlsx
+++ b/files/diet-reference-config-v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D6D5B64-1199-434F-849A-1FA7F6961367}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C38E9BDE-3DFB-485D-B58C-64A51674F7E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15021,6 +15021,10 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
+    <t>거의 못 먹거나 걸렀어요</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <t>{끼니</t>
     </r>
@@ -15383,26 +15387,45 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>배는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>어땠나요</t>
+      <t>배부름은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>어느</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>정도였나요</t>
     </r>
     <r>
       <rPr>
@@ -15635,11 +15658,7 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>{지난 끼니}을 드신 뒤 배는 어땠나요?</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>거의 못 먹거나 걸렀어요</t>
+    <t>{지난 끼니}을 드신 뒤 배부름은 어느 정도였나요?</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -16720,7 +16739,7 @@
         <v>1658</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="D52" s="12" t="s">
         <v>1659</v>
@@ -29928,7 +29947,7 @@
         <v>99</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>1668</v>
+        <v>1666</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>100</v>
@@ -30193,7 +30212,7 @@
         <v>143</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>144</v>

--- a/files/diet-reference-config-v1.0.0.xlsx
+++ b/files/diet-reference-config-v1.0.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C38E9BDE-3DFB-485D-B58C-64A51674F7E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97C478E0-DF8B-49FB-8567-8C2E2C3D2C69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="안내" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5216" uniqueCount="1669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5208" uniqueCount="1662">
   <si>
     <t>시트</t>
   </si>
@@ -5737,254 +5737,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>단백질</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>질문</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>문구</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>변경</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>{</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>지난</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>끼니</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>에</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>고기</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>생선</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>달걀</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>두부를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>드셨나요</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>?</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>질문</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시트</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> DIET-Q-06 · </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>참조설정데이터</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축정의</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시트</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>단계</t>
     </r>
     <r>
@@ -13875,1144 +13627,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>질문</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>문장</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>다듬기</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>{끼니</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>}</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>에</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>채소</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>반찬</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>몇</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>가지</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>드셨나요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>? · {</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>끼니</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">} </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>전후에</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>단</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>음료</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>간식</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>몇</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>번</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>드셨나요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>? · {</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>끼니</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">} </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>먹고</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>얼마나</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>배불렀나요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">? </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>등</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>질문</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시트</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> DIET-Q-01·02·03·05·06·07 · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>참조설정데이터</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축정의</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>야식</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>질문을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>횟수에서</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>양으로</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>어젯밤</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>야식을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>몇</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>번</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>드셨나요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">? · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>안</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>먹었어요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>한</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>번</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>두</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>번</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>이상</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>질문</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시트</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> DIET-Q-04 · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>선택지</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>시트</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 14~16</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>행</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>참조설정데이터</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축정의</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>어젯밤</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>야식은</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>얼마나</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>드셨나요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">? · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>안</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>먹었어요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>간단히</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>먹었어요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>배부르게</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>먹었어요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>선택지</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>코드는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> none · light · meal_sized, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>점수는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>그대로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>없음</t>
-    </r>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>배부르게 먹었어요</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -15025,8 +13639,94 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>{끼니</t>
+    <t>{지난 끼니}을 드신 뒤 배부름은 어느 정도였나요?</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>질문</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>답변</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문장</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>다듬기</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>단백질</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>: {</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼니</t>
     </r>
     <r>
       <rPr>
@@ -15045,6 +13745,1139 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
+      <t>에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>고기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>생선</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>달걀</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>두부를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>드셨나요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>채소</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>: {</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼니</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>채소</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>반찬</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>몇</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>가지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>드셨나요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>단</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>음료</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>간식</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>: {</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼니</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">} </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>전후에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>단</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>음료</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>간식</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>몇</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>번</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>드셨나요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>국물</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>: {</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼니</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>국물은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>얼마나</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>드셨나요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>배부름</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>: {</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼니</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>얼마나</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>배불렀나요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>야식</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>어젯밤</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>야식을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>몇</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>번</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>드셨나요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">? </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>답</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>안</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹었어요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>번</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>두</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>번</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이상
+식사</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>규칙</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>답</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>거의</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>못</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹거나</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>거름</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>단백질</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>: {</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼니</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
       <t>엔</t>
     </r>
     <r>
@@ -15064,6 +14897,140 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
+      <t>단백질류</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>고기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>생선</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>달걀</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>등</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>드셨나요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
       <t>채소</t>
     </r>
     <r>
@@ -15074,16 +15041,73 @@
         <rFont val="Carlito"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>반찬을</t>
+      <t>: {</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼니</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>엔</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>채소</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>반찬은</t>
     </r>
     <r>
       <rPr>
@@ -15121,7 +15145,294 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>가지</t>
+      <t>가지였나요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>단</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>음료</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>간식</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>: {</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼니</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">} </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>전후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>단</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>음료</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>간식은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>몇</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>번이었나요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>국물</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>: {</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼니</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>엔</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>국물을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>얼마나</t>
     </r>
     <r>
       <rPr>
@@ -15150,7 +15461,27 @@
         <rFont val="Carlito"/>
         <family val="2"/>
       </rPr>
-      <t>? · {</t>
+      <t xml:space="preserve">?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>배부름</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>: {</t>
     </r>
     <r>
       <rPr>
@@ -15178,102 +15509,122 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>전후로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>단</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>음료나</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>간식을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>몇</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>번</t>
+      <t>후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>배부름은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>어땠나요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>야식</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>어젯밤</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>야식은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>얼마나</t>
     </r>
     <r>
       <rPr>
@@ -15302,54 +15653,360 @@
         <rFont val="Carlito"/>
         <family val="2"/>
       </rPr>
-      <t>? · {</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>끼니</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>}</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>드신</t>
+      <t xml:space="preserve">? </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>답</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>안</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹었어요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>간단히</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹었어요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>배부르게</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹었어요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>코드</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> none · light · meal_sized, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>점수</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>없음</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>그대로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식사</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>규칙</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>답</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>거의</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>못</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹거나</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>걸렀어요
+끼니</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이름</t>
     </r>
     <r>
       <rPr>
@@ -15387,102 +16044,102 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>배부름은</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>어느</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>정도였나요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">? </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>등</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>끼니</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>이름</t>
+      <t>조사를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문장에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>미리</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>써</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>두고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>치환</t>
     </r>
     <r>
       <rPr>
@@ -15511,101 +16168,6 @@
         <rFont val="Carlito"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>조사를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>문장에</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>미리</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>써</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>두고</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve"> 32</t>
     </r>
     <r>
@@ -15634,31 +16196,147 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>이내를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>지킴</t>
+      <t>이하로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>맞춤</t>
     </r>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>{지난 끼니}을 드신 뒤 배부름은 어느 정도였나요?</t>
+    <r>
+      <t>질문</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시트</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> DIET-Q-00~07 · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>선택지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시트</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> DIET-Q-00, DIET-Q-04 · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>참조설정데이터</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축정의</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시트</t>
+    </r>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -15792,7 +16470,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -15833,6 +16511,9 @@
     </xf>
     <xf numFmtId="49" fontId="14" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -16238,7 +16919,7 @@
   <sheetPr>
     <tabColor rgb="FF315A7D"/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="22.58203125" customWidth="1"/>
@@ -16703,60 +17384,32 @@
         <v>1536</v>
       </c>
     </row>
-    <row r="50" spans="1:4">
-      <c r="A50" t="s">
-        <v>1537</v>
-      </c>
-      <c r="B50" t="s">
-        <v>1538</v>
-      </c>
-      <c r="C50" t="s">
-        <v>1655</v>
-      </c>
-      <c r="D50" t="s">
-        <v>1539</v>
+    <row r="50" spans="1:4" ht="140">
+      <c r="A50" s="16" t="s">
+        <v>1658</v>
+      </c>
+      <c r="B50" s="16" t="s">
+        <v>1659</v>
+      </c>
+      <c r="C50" s="16" t="s">
+        <v>1660</v>
+      </c>
+      <c r="D50" s="16" t="s">
+        <v>1661</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="12" t="s">
+        <v>1537</v>
+      </c>
+      <c r="B51" s="12" t="s">
+        <v>1538</v>
+      </c>
+      <c r="C51" s="12" t="s">
+        <v>1539</v>
+      </c>
+      <c r="D51" s="12" t="s">
         <v>1540</v>
-      </c>
-      <c r="B51" s="12" t="s">
-        <v>1541</v>
-      </c>
-      <c r="C51" s="12" t="s">
-        <v>1542</v>
-      </c>
-      <c r="D51" s="12" t="s">
-        <v>1543</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4">
-      <c r="A52" s="12" t="s">
-        <v>1657</v>
-      </c>
-      <c r="B52" s="12" t="s">
-        <v>1658</v>
-      </c>
-      <c r="C52" s="12" t="s">
-        <v>1667</v>
-      </c>
-      <c r="D52" s="12" t="s">
-        <v>1659</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4">
-      <c r="A53" s="12" t="s">
-        <v>1660</v>
-      </c>
-      <c r="B53" s="12" t="s">
-        <v>1661</v>
-      </c>
-      <c r="C53" s="12" t="s">
-        <v>1663</v>
-      </c>
-      <c r="D53" s="12" t="s">
-        <v>1662</v>
       </c>
     </row>
   </sheetData>
@@ -28474,40 +29127,40 @@
         <v>172</v>
       </c>
       <c r="B145" t="s">
+        <v>1571</v>
+      </c>
+      <c r="C145" t="s">
+        <v>1572</v>
+      </c>
+      <c r="D145" t="s">
+        <v>1573</v>
+      </c>
+      <c r="E145" t="s">
         <v>1574</v>
       </c>
-      <c r="C145" t="s">
+      <c r="F145" t="s">
+        <v>1563</v>
+      </c>
+      <c r="G145" t="s">
         <v>1575</v>
-      </c>
-      <c r="D145" t="s">
-        <v>1576</v>
-      </c>
-      <c r="E145" t="s">
-        <v>1577</v>
-      </c>
-      <c r="F145" t="s">
-        <v>1566</v>
-      </c>
-      <c r="G145" t="s">
-        <v>1578</v>
       </c>
       <c r="H145">
         <v>11</v>
       </c>
       <c r="I145" t="s">
-        <v>1579</v>
+        <v>1576</v>
       </c>
       <c r="J145" t="s">
         <v>986</v>
       </c>
       <c r="L145" t="s">
-        <v>1580</v>
+        <v>1577</v>
       </c>
       <c r="M145" t="s">
         <v>1480</v>
       </c>
       <c r="N145" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O145" t="s">
         <v>1481</v>
@@ -28524,28 +29177,28 @@
         <v>173</v>
       </c>
       <c r="B146" t="s">
+        <v>1571</v>
+      </c>
+      <c r="C146" t="s">
+        <v>1572</v>
+      </c>
+      <c r="D146" t="s">
+        <v>1573</v>
+      </c>
+      <c r="E146" t="s">
         <v>1574</v>
       </c>
-      <c r="C146" t="s">
-        <v>1575</v>
-      </c>
-      <c r="D146" t="s">
-        <v>1576</v>
-      </c>
-      <c r="E146" t="s">
-        <v>1577</v>
-      </c>
       <c r="F146" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="G146" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="H146">
         <v>8</v>
       </c>
       <c r="I146" t="s">
-        <v>1584</v>
+        <v>1581</v>
       </c>
       <c r="J146" t="s">
         <v>986</v>
@@ -28554,7 +29207,7 @@
         <v>1482</v>
       </c>
       <c r="N146" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O146" t="s">
         <v>1483</v>
@@ -28571,28 +29224,28 @@
         <v>174</v>
       </c>
       <c r="B147" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="C147" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="D147" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="E147" t="s">
-        <v>1585</v>
+        <v>1582</v>
       </c>
       <c r="F147" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="G147" t="s">
-        <v>1586</v>
+        <v>1583</v>
       </c>
       <c r="H147">
         <v>10</v>
       </c>
       <c r="I147" t="s">
-        <v>1587</v>
+        <v>1584</v>
       </c>
       <c r="J147" t="s">
         <v>986</v>
@@ -28601,7 +29254,7 @@
         <v>1519</v>
       </c>
       <c r="N147" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O147" t="s">
         <v>1484</v>
@@ -28618,28 +29271,28 @@
         <v>175</v>
       </c>
       <c r="B148" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="C148" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="D148" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="E148" t="s">
+        <v>1582</v>
+      </c>
+      <c r="F148" t="s">
+        <v>1579</v>
+      </c>
+      <c r="G148" t="s">
         <v>1585</v>
-      </c>
-      <c r="F148" t="s">
-        <v>1582</v>
-      </c>
-      <c r="G148" t="s">
-        <v>1588</v>
       </c>
       <c r="H148">
         <v>11</v>
       </c>
       <c r="I148" t="s">
-        <v>1589</v>
+        <v>1586</v>
       </c>
       <c r="J148" t="s">
         <v>986</v>
@@ -28648,7 +29301,7 @@
         <v>1485</v>
       </c>
       <c r="N148" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O148" t="s">
         <v>1486</v>
@@ -28665,28 +29318,28 @@
         <v>176</v>
       </c>
       <c r="B149" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="C149" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="D149" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="E149" t="s">
-        <v>1585</v>
+        <v>1582</v>
       </c>
       <c r="F149" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="G149" t="s">
-        <v>1590</v>
+        <v>1587</v>
       </c>
       <c r="H149">
         <v>10</v>
       </c>
       <c r="I149" t="s">
-        <v>1591</v>
+        <v>1588</v>
       </c>
       <c r="J149" t="s">
         <v>986</v>
@@ -28695,7 +29348,7 @@
         <v>1487</v>
       </c>
       <c r="N149" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O149" t="s">
         <v>1488</v>
@@ -28712,28 +29365,28 @@
         <v>177</v>
       </c>
       <c r="B150" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="C150" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="D150" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="E150" t="s">
-        <v>1592</v>
+        <v>1589</v>
       </c>
       <c r="F150" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="G150" t="s">
-        <v>1593</v>
+        <v>1590</v>
       </c>
       <c r="H150">
         <v>11</v>
       </c>
       <c r="I150" t="s">
-        <v>1594</v>
+        <v>1591</v>
       </c>
       <c r="J150" t="s">
         <v>986</v>
@@ -28742,7 +29395,7 @@
         <v>1489</v>
       </c>
       <c r="N150" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O150" t="s">
         <v>1490</v>
@@ -28759,28 +29412,28 @@
         <v>178</v>
       </c>
       <c r="B151" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="C151" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="D151" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="E151" t="s">
+        <v>1589</v>
+      </c>
+      <c r="F151" t="s">
+        <v>1563</v>
+      </c>
+      <c r="G151" t="s">
         <v>1592</v>
-      </c>
-      <c r="F151" t="s">
-        <v>1566</v>
-      </c>
-      <c r="G151" t="s">
-        <v>1595</v>
       </c>
       <c r="H151">
         <v>10</v>
       </c>
       <c r="I151" t="s">
-        <v>1596</v>
+        <v>1593</v>
       </c>
       <c r="J151" t="s">
         <v>986</v>
@@ -28789,7 +29442,7 @@
         <v>1489</v>
       </c>
       <c r="N151" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O151" t="s">
         <v>1491</v>
@@ -28806,28 +29459,28 @@
         <v>179</v>
       </c>
       <c r="B152" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="C152" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="D152" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="E152" t="s">
-        <v>1597</v>
+        <v>1594</v>
       </c>
       <c r="F152" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="G152" t="s">
-        <v>1598</v>
+        <v>1595</v>
       </c>
       <c r="H152">
         <v>12</v>
       </c>
       <c r="I152" t="s">
-        <v>1599</v>
+        <v>1596</v>
       </c>
       <c r="J152" t="s">
         <v>986</v>
@@ -28836,7 +29489,7 @@
         <v>1492</v>
       </c>
       <c r="N152" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O152" t="s">
         <v>1493</v>
@@ -28853,28 +29506,28 @@
         <v>180</v>
       </c>
       <c r="B153" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="C153" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="D153" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="E153" t="s">
-        <v>1600</v>
+        <v>1597</v>
       </c>
       <c r="F153" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="G153" t="s">
-        <v>1601</v>
+        <v>1598</v>
       </c>
       <c r="H153">
         <v>12</v>
       </c>
       <c r="I153" t="s">
-        <v>1602</v>
+        <v>1599</v>
       </c>
       <c r="J153" t="s">
         <v>986</v>
@@ -28883,7 +29536,7 @@
         <v>1494</v>
       </c>
       <c r="N153" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O153" t="s">
         <v>1495</v>
@@ -28900,28 +29553,28 @@
         <v>181</v>
       </c>
       <c r="B154" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="C154" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="D154" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="E154" t="s">
-        <v>1603</v>
+        <v>1600</v>
       </c>
       <c r="F154" t="s">
-        <v>1604</v>
+        <v>1601</v>
       </c>
       <c r="G154" t="s">
-        <v>1605</v>
+        <v>1602</v>
       </c>
       <c r="H154">
         <v>12</v>
       </c>
       <c r="I154" t="s">
-        <v>1606</v>
+        <v>1603</v>
       </c>
       <c r="J154" t="s">
         <v>986</v>
@@ -28930,7 +29583,7 @@
         <v>1482</v>
       </c>
       <c r="N154" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O154" t="s">
         <v>1496</v>
@@ -28947,28 +29600,28 @@
         <v>182</v>
       </c>
       <c r="B155" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="C155" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="D155" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="E155" t="s">
-        <v>1603</v>
+        <v>1600</v>
       </c>
       <c r="F155" t="s">
+        <v>1601</v>
+      </c>
+      <c r="G155" t="s">
         <v>1604</v>
-      </c>
-      <c r="G155" t="s">
-        <v>1607</v>
       </c>
       <c r="H155">
         <v>11</v>
       </c>
       <c r="I155" t="s">
-        <v>1608</v>
+        <v>1605</v>
       </c>
       <c r="J155" t="s">
         <v>986</v>
@@ -28977,7 +29630,7 @@
         <v>1480</v>
       </c>
       <c r="N155" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O155" t="s">
         <v>1497</v>
@@ -28994,37 +29647,37 @@
         <v>183</v>
       </c>
       <c r="B156" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="C156" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="D156" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="E156" t="s">
-        <v>1603</v>
+        <v>1600</v>
       </c>
       <c r="F156" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="G156" t="s">
-        <v>1609</v>
+        <v>1606</v>
       </c>
       <c r="H156">
         <v>10</v>
       </c>
       <c r="I156" t="s">
-        <v>1610</v>
+        <v>1607</v>
       </c>
       <c r="J156" t="s">
-        <v>1611</v>
+        <v>1608</v>
       </c>
       <c r="M156" t="s">
         <v>1482</v>
       </c>
       <c r="N156" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O156" t="s">
         <v>1498</v>
@@ -29041,40 +29694,40 @@
         <v>184</v>
       </c>
       <c r="B157" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="C157" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="D157" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="E157" t="s">
-        <v>1603</v>
+        <v>1600</v>
       </c>
       <c r="F157" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="G157" t="s">
-        <v>1612</v>
+        <v>1609</v>
       </c>
       <c r="H157">
         <v>10</v>
       </c>
       <c r="I157" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
       <c r="J157" t="s">
+        <v>1608</v>
+      </c>
+      <c r="L157" t="s">
         <v>1611</v>
-      </c>
-      <c r="L157" t="s">
-        <v>1614</v>
       </c>
       <c r="M157" t="s">
         <v>1480</v>
       </c>
       <c r="N157" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O157" t="s">
         <v>1499</v>
@@ -29091,40 +29744,40 @@
         <v>185</v>
       </c>
       <c r="B158" t="s">
+        <v>1571</v>
+      </c>
+      <c r="C158" t="s">
+        <v>1572</v>
+      </c>
+      <c r="D158" t="s">
+        <v>1573</v>
+      </c>
+      <c r="E158" t="s">
         <v>1574</v>
       </c>
-      <c r="C158" t="s">
-        <v>1575</v>
-      </c>
-      <c r="D158" t="s">
-        <v>1576</v>
-      </c>
-      <c r="E158" t="s">
-        <v>1577</v>
-      </c>
       <c r="F158" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="G158" t="s">
-        <v>1615</v>
+        <v>1612</v>
       </c>
       <c r="H158">
         <v>10</v>
       </c>
       <c r="I158" t="s">
-        <v>1616</v>
+        <v>1613</v>
       </c>
       <c r="J158" t="s">
         <v>986</v>
       </c>
       <c r="L158" t="s">
-        <v>1580</v>
+        <v>1577</v>
       </c>
       <c r="M158" t="s">
         <v>1480</v>
       </c>
       <c r="N158" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O158" t="s">
         <v>1500</v>
@@ -29141,28 +29794,28 @@
         <v>186</v>
       </c>
       <c r="B159" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="C159" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="D159" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="E159" t="s">
-        <v>1585</v>
+        <v>1582</v>
       </c>
       <c r="F159" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="G159" t="s">
-        <v>1617</v>
+        <v>1614</v>
       </c>
       <c r="H159">
         <v>10</v>
       </c>
       <c r="I159" t="s">
-        <v>1618</v>
+        <v>1615</v>
       </c>
       <c r="J159" t="s">
         <v>986</v>
@@ -29171,7 +29824,7 @@
         <v>1487</v>
       </c>
       <c r="N159" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O159" t="s">
         <v>1501</v>
@@ -29188,28 +29841,28 @@
         <v>187</v>
       </c>
       <c r="B160" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="C160" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="D160" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="E160" t="s">
-        <v>1585</v>
+        <v>1582</v>
       </c>
       <c r="F160" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="G160" t="s">
-        <v>1619</v>
+        <v>1616</v>
       </c>
       <c r="H160">
         <v>9</v>
       </c>
       <c r="I160" t="s">
-        <v>1620</v>
+        <v>1617</v>
       </c>
       <c r="J160" t="s">
         <v>986</v>
@@ -29218,7 +29871,7 @@
         <v>1502</v>
       </c>
       <c r="N160" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O160" t="s">
         <v>1503</v>
@@ -29235,28 +29888,28 @@
         <v>188</v>
       </c>
       <c r="B161" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="C161" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="D161" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="E161" t="s">
-        <v>1585</v>
+        <v>1582</v>
       </c>
       <c r="F161" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="G161" t="s">
-        <v>1621</v>
+        <v>1618</v>
       </c>
       <c r="H161">
         <v>10</v>
       </c>
       <c r="I161" t="s">
-        <v>1622</v>
+        <v>1619</v>
       </c>
       <c r="J161" t="s">
         <v>986</v>
@@ -29265,7 +29918,7 @@
         <v>1485</v>
       </c>
       <c r="N161" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O161" t="s">
         <v>1504</v>
@@ -29282,28 +29935,28 @@
         <v>189</v>
       </c>
       <c r="B162" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="C162" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="D162" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="E162" t="s">
-        <v>1585</v>
+        <v>1582</v>
       </c>
       <c r="F162" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="G162" t="s">
-        <v>1623</v>
+        <v>1620</v>
       </c>
       <c r="H162">
         <v>11</v>
       </c>
       <c r="I162" t="s">
-        <v>1624</v>
+        <v>1621</v>
       </c>
       <c r="J162" t="s">
         <v>986</v>
@@ -29312,7 +29965,7 @@
         <v>1485</v>
       </c>
       <c r="N162" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O162" t="s">
         <v>1505</v>
@@ -29329,28 +29982,28 @@
         <v>190</v>
       </c>
       <c r="B163" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="C163" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="D163" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="E163" t="s">
-        <v>1585</v>
+        <v>1582</v>
       </c>
       <c r="F163" t="s">
-        <v>1604</v>
+        <v>1601</v>
       </c>
       <c r="G163" t="s">
-        <v>1625</v>
+        <v>1622</v>
       </c>
       <c r="H163">
         <v>8</v>
       </c>
       <c r="I163" t="s">
-        <v>1626</v>
+        <v>1623</v>
       </c>
       <c r="J163" t="s">
         <v>986</v>
@@ -29359,7 +30012,7 @@
         <v>1485</v>
       </c>
       <c r="N163" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O163" t="s">
         <v>1506</v>
@@ -29376,28 +30029,28 @@
         <v>191</v>
       </c>
       <c r="B164" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="C164" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="D164" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="E164" t="s">
-        <v>1597</v>
+        <v>1594</v>
       </c>
       <c r="F164" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="G164" t="s">
-        <v>1627</v>
+        <v>1624</v>
       </c>
       <c r="H164">
         <v>10</v>
       </c>
       <c r="I164" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
       <c r="J164" t="s">
         <v>986</v>
@@ -29406,7 +30059,7 @@
         <v>1113</v>
       </c>
       <c r="N164" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O164" t="s">
         <v>1507</v>
@@ -29423,28 +30076,28 @@
         <v>192</v>
       </c>
       <c r="B165" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="C165" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="D165" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="E165" t="s">
-        <v>1592</v>
+        <v>1589</v>
       </c>
       <c r="F165" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="G165" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
       <c r="H165">
         <v>11</v>
       </c>
       <c r="I165" t="s">
-        <v>1630</v>
+        <v>1627</v>
       </c>
       <c r="J165" t="s">
         <v>986</v>
@@ -29453,7 +30106,7 @@
         <v>1489</v>
       </c>
       <c r="N165" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O165" t="s">
         <v>1508</v>
@@ -29470,28 +30123,28 @@
         <v>193</v>
       </c>
       <c r="B166" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="C166" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="D166" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="E166" t="s">
-        <v>1592</v>
+        <v>1589</v>
       </c>
       <c r="F166" t="s">
-        <v>1604</v>
+        <v>1601</v>
       </c>
       <c r="G166" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
       <c r="H166">
         <v>11</v>
       </c>
       <c r="I166" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="J166" t="s">
         <v>986</v>
@@ -29500,7 +30153,7 @@
         <v>1489</v>
       </c>
       <c r="N166" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O166" t="s">
         <v>1509</v>
@@ -29517,28 +30170,28 @@
         <v>195</v>
       </c>
       <c r="B167" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="C167" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="D167" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="E167" t="s">
-        <v>1600</v>
+        <v>1597</v>
       </c>
       <c r="F167" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="G167" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
       <c r="H167">
         <v>11</v>
       </c>
       <c r="I167" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
       <c r="J167" t="s">
         <v>986</v>
@@ -29547,7 +30200,7 @@
         <v>1494</v>
       </c>
       <c r="N167" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O167" t="s">
         <v>1510</v>
@@ -29564,25 +30217,25 @@
         <v>196</v>
       </c>
       <c r="B168" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="C168" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="D168" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="F168" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="G168" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
       <c r="H168">
         <v>8</v>
       </c>
       <c r="I168" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="J168" t="s">
         <v>986</v>
@@ -29591,7 +30244,7 @@
         <v>1485</v>
       </c>
       <c r="N168" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O168" t="s">
         <v>1511</v>
@@ -29608,28 +30261,28 @@
         <v>197</v>
       </c>
       <c r="B169" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="C169" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="D169" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="E169" t="s">
-        <v>1603</v>
+        <v>1600</v>
       </c>
       <c r="F169" t="s">
-        <v>1604</v>
+        <v>1601</v>
       </c>
       <c r="G169" t="s">
-        <v>1637</v>
+        <v>1634</v>
       </c>
       <c r="H169">
         <v>10</v>
       </c>
       <c r="I169" t="s">
-        <v>1638</v>
+        <v>1635</v>
       </c>
       <c r="J169" t="s">
         <v>986</v>
@@ -29638,7 +30291,7 @@
         <v>1480</v>
       </c>
       <c r="N169" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O169" t="s">
         <v>1514</v>
@@ -29655,28 +30308,28 @@
         <v>198</v>
       </c>
       <c r="B170" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="C170" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="D170" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="E170" t="s">
-        <v>1603</v>
+        <v>1600</v>
       </c>
       <c r="F170" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="G170" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
       <c r="H170">
         <v>10</v>
       </c>
       <c r="I170" t="s">
-        <v>1640</v>
+        <v>1637</v>
       </c>
       <c r="J170" t="s">
         <v>986</v>
@@ -29685,7 +30338,7 @@
         <v>1482</v>
       </c>
       <c r="N170" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O170" t="s">
         <v>1515</v>
@@ -29702,40 +30355,40 @@
         <v>199</v>
       </c>
       <c r="B171" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="C171" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="D171" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="E171" t="s">
-        <v>1603</v>
+        <v>1600</v>
       </c>
       <c r="F171" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="G171" t="s">
-        <v>1641</v>
+        <v>1638</v>
       </c>
       <c r="H171">
         <v>10</v>
       </c>
       <c r="I171" t="s">
-        <v>1642</v>
+        <v>1639</v>
       </c>
       <c r="J171" t="s">
-        <v>1611</v>
+        <v>1608</v>
       </c>
       <c r="L171" t="s">
-        <v>1580</v>
+        <v>1577</v>
       </c>
       <c r="M171" t="s">
         <v>1482</v>
       </c>
       <c r="N171" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O171" t="s">
         <v>1516</v>
@@ -29752,28 +30405,28 @@
         <v>200</v>
       </c>
       <c r="B172" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="C172" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="D172" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="E172" t="s">
-        <v>1597</v>
+        <v>1594</v>
       </c>
       <c r="F172" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="G172" t="s">
-        <v>1643</v>
+        <v>1640</v>
       </c>
       <c r="H172">
         <v>11</v>
       </c>
       <c r="I172" t="s">
-        <v>1644</v>
+        <v>1641</v>
       </c>
       <c r="J172" t="s">
         <v>986</v>
@@ -29782,7 +30435,7 @@
         <v>1113</v>
       </c>
       <c r="N172" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O172" t="s">
         <v>1517</v>
@@ -29799,28 +30452,28 @@
         <v>201</v>
       </c>
       <c r="B173" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="C173" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="D173" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="E173" t="s">
-        <v>1585</v>
+        <v>1582</v>
       </c>
       <c r="F173" t="s">
-        <v>1604</v>
+        <v>1601</v>
       </c>
       <c r="G173" t="s">
-        <v>1645</v>
+        <v>1642</v>
       </c>
       <c r="H173">
         <v>7</v>
       </c>
       <c r="I173" t="s">
-        <v>1646</v>
+        <v>1643</v>
       </c>
       <c r="J173" t="s">
         <v>986</v>
@@ -29829,7 +30482,7 @@
         <v>1485</v>
       </c>
       <c r="N173" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="O173" t="s">
         <v>1518</v>
@@ -29947,7 +30600,7 @@
         <v>99</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>1666</v>
+        <v>1656</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>100</v>
@@ -29994,7 +30647,7 @@
         <v>109</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>1647</v>
+        <v>1644</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>110</v>
@@ -30050,7 +30703,7 @@
         <v>121</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>1648</v>
+        <v>1645</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>122</v>
@@ -30106,7 +30759,7 @@
         <v>131</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>1649</v>
+        <v>1646</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>132</v>
@@ -30159,19 +30812,19 @@
         <v>138</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>1665</v>
+        <v>1655</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>1650</v>
+        <v>1647</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>132</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>1652</v>
+        <v>1649</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>1664</v>
+        <v>1654</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>139</v>
@@ -30180,7 +30833,7 @@
         <v>140</v>
       </c>
       <c r="J6" s="13" t="s">
-        <v>1651</v>
+        <v>1648</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>141</v>
@@ -30192,10 +30845,10 @@
         <v>119</v>
       </c>
       <c r="N6" s="13" t="s">
-        <v>1653</v>
+        <v>1650</v>
       </c>
       <c r="O6" s="13" t="s">
-        <v>1654</v>
+        <v>1651</v>
       </c>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
@@ -30212,7 +30865,7 @@
         <v>143</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>1668</v>
+        <v>1657</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>144</v>
@@ -30268,7 +30921,7 @@
         <v>152</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>1655</v>
+        <v>1652</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>153</v>
@@ -30324,7 +30977,7 @@
         <v>162</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>1656</v>
+        <v>1653</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>132</v>
@@ -30976,7 +31629,7 @@
         <v>1451</v>
       </c>
       <c r="H25" t="s">
-        <v>1544</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -30996,7 +31649,7 @@
         <v>1451</v>
       </c>
       <c r="H26" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -31016,7 +31669,7 @@
         <v>1462</v>
       </c>
       <c r="H27" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -31039,7 +31692,7 @@
         <v>1465</v>
       </c>
       <c r="H28" t="s">
-        <v>1547</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -31062,7 +31715,7 @@
         <v>1465</v>
       </c>
       <c r="H29" t="s">
-        <v>1548</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -31085,7 +31738,7 @@
         <v>1465</v>
       </c>
       <c r="H30" t="s">
-        <v>1549</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -31108,7 +31761,7 @@
         <v>1465</v>
       </c>
       <c r="H31" t="s">
-        <v>1550</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -31131,7 +31784,7 @@
         <v>1465</v>
       </c>
       <c r="H32" t="s">
-        <v>1551</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -31154,7 +31807,7 @@
         <v>1465</v>
       </c>
       <c r="H33" t="s">
-        <v>1552</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -31177,7 +31830,7 @@
         <v>1465</v>
       </c>
       <c r="H34" t="s">
-        <v>1553</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -31200,7 +31853,7 @@
         <v>1465</v>
       </c>
       <c r="H35" t="s">
-        <v>1554</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -31223,7 +31876,7 @@
         <v>1451</v>
       </c>
       <c r="H36" s="12" t="s">
-        <v>1555</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -31246,7 +31899,7 @@
         <v>1451</v>
       </c>
       <c r="H37" s="12" t="s">
-        <v>1556</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -31269,7 +31922,7 @@
         <v>1451</v>
       </c>
       <c r="H38" s="12" t="s">
-        <v>1557</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -31292,7 +31945,7 @@
         <v>1451</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>1558</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -31315,7 +31968,7 @@
         <v>1451</v>
       </c>
       <c r="H40" s="12" t="s">
-        <v>1559</v>
+        <v>1556</v>
       </c>
     </row>
   </sheetData>
@@ -32631,19 +33284,19 @@
         <v>1446</v>
       </c>
       <c r="B66" t="s">
+        <v>1557</v>
+      </c>
+      <c r="C66" t="s">
+        <v>1558</v>
+      </c>
+      <c r="D66" t="s">
+        <v>1559</v>
+      </c>
+      <c r="E66" t="s">
         <v>1560</v>
       </c>
-      <c r="C66" t="s">
+      <c r="F66" t="s">
         <v>1561</v>
-      </c>
-      <c r="D66" t="s">
-        <v>1562</v>
-      </c>
-      <c r="E66" t="s">
-        <v>1563</v>
-      </c>
-      <c r="F66" t="s">
-        <v>1564</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -32651,19 +33304,19 @@
         <v>1447</v>
       </c>
       <c r="B67" t="s">
+        <v>1557</v>
+      </c>
+      <c r="C67" t="s">
+        <v>1562</v>
+      </c>
+      <c r="D67" t="s">
+        <v>1563</v>
+      </c>
+      <c r="E67" t="s">
         <v>1560</v>
       </c>
-      <c r="C67" t="s">
-        <v>1565</v>
-      </c>
-      <c r="D67" t="s">
-        <v>1566</v>
-      </c>
-      <c r="E67" t="s">
-        <v>1563</v>
-      </c>
       <c r="F67" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -32674,16 +33327,16 @@
         <v>42</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>1568</v>
+        <v>1565</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>1569</v>
+        <v>1566</v>
       </c>
       <c r="E68" s="12" t="s">
         <v>1454</v>
       </c>
       <c r="F68" s="12" t="s">
-        <v>1570</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -32694,16 +33347,16 @@
         <v>42</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>1571</v>
+        <v>1568</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>1572</v>
+        <v>1569</v>
       </c>
       <c r="E69" s="12" t="s">
         <v>1454</v>
       </c>
       <c r="F69" s="12" t="s">
-        <v>1573</v>
+        <v>1570</v>
       </c>
     </row>
   </sheetData>

--- a/files/diet-reference-config-v1.0.0.xlsx
+++ b/files/diet-reference-config-v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8932E6D-E1C1-439A-89FC-552680D7E445}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{484C8CDF-4A78-480E-84EF-DBB534D0A9E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -14928,46 +14928,46 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
+    <t>거의 못 먹음</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>{지난 끼니}엔 채소 반찬은 몇 가지였나요?</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>{지난 끼니} 전후 단 음료·간식은 몇 번이었나요?</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>조금 먹었어요</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>{지난 끼니} 후 배부름은 어땠나요?</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>7자 (5~7자)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
     <t>단백질: {끼니}엔 단백질류(고기·생선·달걀 등)를 드셨나요?
 채소: {끼니}엔 채소 반찬은 몇 가지였나요?
 단 음료·간식: {끼니} 전후 단 음료·간식은 몇 번이었나요?
 국물: {끼니}엔 국물을 얼마나 드셨나요?
 배부름: {끼니} 후 배부름은 어땠나요?
-야식: 어젯밤 야식은 얼마나 드셨나요? 답 안 먹었어요 · 조금 먹었어요 · 많이 먹었어요 (코드 none · light · meal_sized, 점수 없음 그대로)
+야식: 어젯밤 야식은 얼마나 드셨나요? 답 안 먹었어요 · 조금 먹었어요 · 배부르게 먹음 (코드 none · light · meal_sized, 점수 없음 그대로)
 식사 규칙 답: 거의 못 먹음
 끼니 이름 뒤 조사를 문장에 미리 써 두고, 치환 뒤 32자 이하로 맞춤</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>거의 못 먹음</t>
+    <t>전날 저녁 식사 후~당일 04:00 전의 야식 자기보고 양(조금 / 배부르게). 오늘 아침 식사는 제외. 위해성·수면 영향 판정 아님</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>{지난 끼니}엔 채소 반찬은 몇 가지였나요?</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>{지난 끼니} 전후 단 음료·간식은 몇 번이었나요?</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>전날 저녁 식사 후~당일 04:00 전의 야식 자기보고 양(조금 / 많이). 오늘 아침 식사는 제외. 위해성·수면 영향 판정 아님</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>조금 먹었어요</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>많이 먹었어요</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>{지난 끼니} 후 배부름은 어땠나요?</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>7자 (5~7자)</t>
+    <t>배부르게 먹음</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -16023,7 +16023,7 @@
         <v>1651</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>1653</v>
+        <v>1659</v>
       </c>
       <c r="D50" s="16" t="s">
         <v>1652</v>
@@ -29231,7 +29231,7 @@
         <v>99</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>100</v>
@@ -29278,7 +29278,7 @@
         <v>109</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>110</v>
@@ -29334,7 +29334,7 @@
         <v>121</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>122</v>
@@ -29443,7 +29443,7 @@
         <v>138</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>1657</v>
+        <v>1660</v>
       </c>
       <c r="D6" s="13" t="s">
         <v>1644</v>
@@ -29452,10 +29452,10 @@
         <v>132</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>1658</v>
+        <v>1656</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>1659</v>
+        <v>1661</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>139</v>
@@ -29496,7 +29496,7 @@
         <v>143</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>1660</v>
+        <v>1657</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>144</v>
@@ -31233,7 +31233,7 @@
         <v>371</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>1661</v>
+        <v>1658</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>372</v>

--- a/files/diet-reference-config-v1.0.0.xlsx
+++ b/files/diet-reference-config-v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{484C8CDF-4A78-480E-84EF-DBB534D0A9E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD37CA0C-C323-43EF-9528-277A27337FA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5208" uniqueCount="1662">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5208" uniqueCount="1663">
   <si>
     <t>시트</t>
   </si>
@@ -14937,10 +14937,6 @@
   </si>
   <si>
     <t>{지난 끼니} 전후 단 음료·간식은 몇 번이었나요?</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>조금 먹었어요</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
@@ -14957,17 +14953,25 @@
 단 음료·간식: {끼니} 전후 단 음료·간식은 몇 번이었나요?
 국물: {끼니}엔 국물을 얼마나 드셨나요?
 배부름: {끼니} 후 배부름은 어땠나요?
-야식: 어젯밤 야식은 얼마나 드셨나요? 답 안 먹었어요 · 조금 먹었어요 · 배부르게 먹음 (코드 none · light · meal_sized, 점수 없음 그대로)
+야식: 어젯밤 야식은 얼마나 드셨나요? 답 먹지 않음 · 조금 먹음 · 배불리 먹음 (코드 none · light · meal_sized, 점수 없음 그대로)
 식사 규칙 답: 거의 못 먹음
 끼니 이름 뒤 조사를 문장에 미리 써 두고, 치환 뒤 32자 이하로 맞춤</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>전날 저녁 식사 후~당일 04:00 전의 야식 자기보고 양(조금 / 배부르게). 오늘 아침 식사는 제외. 위해성·수면 영향 판정 아님</t>
+    <t>전날 저녁 식사 후~당일 04:00 전의 야식 자기보고 양(조금 / 배불리). 오늘 아침 식사는 제외. 위해성·수면 영향 판정 아님</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>배부르게 먹음</t>
+    <t>먹지 않음</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>조금 먹음</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>배불리 먹음</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -16023,7 +16027,7 @@
         <v>1651</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="D50" s="16" t="s">
         <v>1652</v>
@@ -29443,19 +29447,19 @@
         <v>138</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="D6" s="13" t="s">
         <v>1644</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>132</v>
+      <c r="E6" s="13" t="s">
+        <v>1660</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>1656</v>
+        <v>1661</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>139</v>
@@ -29496,7 +29500,7 @@
         <v>143</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>144</v>
@@ -31233,7 +31237,7 @@
         <v>371</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>372</v>

--- a/files/diet-reference-config-v1.0.0.xlsx
+++ b/files/diet-reference-config-v1.0.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6FFD423-2130-40AF-8E8C-0CDB5CF043B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C27A6596-E3F4-4B21-9D86-4DBC3044A2D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="안내" sheetId="1" r:id="rId1"/>
@@ -8691,45 +8691,69 @@
   </si>
   <si>
     <r>
-      <t>축</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>목표만</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>센다</t>
+      <t>단계</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>판단</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>유효</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>기간</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>56일</t>
     </r>
     <r>
       <rPr>
@@ -8748,282 +8772,6 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
-      <t>앱을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>열지</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>않은</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>날과</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>안내만</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>나간</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>날은</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>목표가</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>없어</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대상이</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>아니다</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>단계</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>판단</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>유효</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>기간</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>56일</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
       <t>그보다</t>
     </r>
     <r>
@@ -9101,125 +8849,6 @@
         <rFont val="Carlito"/>
       </rPr>
       <t>않는다</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>오래된</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>기록이</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>지금의</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>단계를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>좌우하지</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>않게</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>한다</t>
     </r>
   </si>
   <si>
@@ -16073,32 +15702,1241 @@
       </rPr>
       <t>행</t>
     </r>
+  </si>
+  <si>
+    <t>채소 반찬을 먹은 정도(본인 판단). 중량·먹는 순서 아님</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>{지난 끼니}엔 채소 반찬을 얼마나 드셨나요?</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>충분히 먹음</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>본인이 느낀 양만 관찰. 400g 달성·혈당 개선으로 해석 금지</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>오래된</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>기록이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>지금의</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>단계를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>좌우하지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않게</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>한다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끝난</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 4</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>건을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>모으는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>데</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>보통</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 12~24</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>일이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>걸려</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>그</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 2</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>배</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이상</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>상태</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>기준</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 28</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>일의</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 2</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>배</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>으로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>잡았다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>정해진</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>근거</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>값이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아니며</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>앱</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>출시</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>실제</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>사용</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>데이터를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>보고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>조정한다</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>축</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표만</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>센다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>앱을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>열지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>날과</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>안내만</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>나간</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>날은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>없어</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>대상이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아니다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>부담</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>줄이기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>풀은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축과</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>단계가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>없어</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>애초에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>단계</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>계산</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>대상이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아니다</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>단백질: {끼니}엔 단백질류(고기·생선·달걀 등)를 드셨나요?
 채소: {끼니}엔 채소 반찬을 얼마나 드셨나요? 답 충분히 먹음 · 조금 먹음 · 먹지 않음
 단 음료·간식: {끼니} 전후 단 음료·간식은 몇 번이었나요?
-국물: {끼니}엔 국물을 얼마나 드셨나요?
+국물: {끼니}엔 국물을 얼마나 드셨나요? 답 먹지 않음 · 절반 이하 · 절반 넘게
 배부름: {끼니} 후 배부름은 어땠나요?
 야식: 어젯밤 야식은 얼마나 드셨나요? 답 먹지 않음 · 조금 먹음 · 배불리 먹음 (코드 none · light · meal_sized, 점수 없음 그대로)
 식사 규칙 답: 거의 못 먹음
 끼니 이름 뒤 조사를 문장에 미리 써 두고, 치환 뒤 32자 이하로 맞춤</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>채소 반찬을 먹은 정도(본인 판단). 중량·먹는 순서 아님</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>{지난 끼니}엔 채소 반찬을 얼마나 드셨나요?</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>충분히 먹음</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>본인이 느낀 양만 관찰. 400g 달성·혈당 개선으로 해석 금지</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -17146,18 +17984,18 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="140">
+    <row r="50" spans="1:4" ht="154">
       <c r="A50" s="16" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B50" s="16" t="s">
+        <v>1641</v>
+      </c>
+      <c r="C50" s="16" t="s">
+        <v>1664</v>
+      </c>
+      <c r="D50" s="16" t="s">
         <v>1642</v>
-      </c>
-      <c r="B50" s="16" t="s">
-        <v>1643</v>
-      </c>
-      <c r="C50" s="16" t="s">
-        <v>1660</v>
-      </c>
-      <c r="D50" s="16" t="s">
-        <v>1644</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -17176,16 +18014,16 @@
     </row>
     <row r="52" spans="1:4" ht="56">
       <c r="A52" s="16" t="s">
+        <v>1654</v>
+      </c>
+      <c r="B52" s="16" t="s">
+        <v>1655</v>
+      </c>
+      <c r="C52" s="16" t="s">
         <v>1656</v>
       </c>
-      <c r="B52" s="16" t="s">
+      <c r="D52" s="16" t="s">
         <v>1657</v>
-      </c>
-      <c r="C52" s="16" t="s">
-        <v>1658</v>
-      </c>
-      <c r="D52" s="16" t="s">
-        <v>1659</v>
       </c>
     </row>
   </sheetData>
@@ -28903,40 +29741,40 @@
         <v>172</v>
       </c>
       <c r="B145" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C145" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D145" t="s">
         <v>1562</v>
       </c>
-      <c r="C145" t="s">
+      <c r="E145" t="s">
         <v>1563</v>
-      </c>
-      <c r="D145" t="s">
-        <v>1564</v>
-      </c>
-      <c r="E145" t="s">
-        <v>1565</v>
       </c>
       <c r="F145" t="s">
         <v>1554</v>
       </c>
       <c r="G145" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="H145">
         <v>11</v>
       </c>
       <c r="I145" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="J145" t="s">
         <v>977</v>
       </c>
       <c r="L145" t="s">
-        <v>1568</v>
+        <v>1566</v>
       </c>
       <c r="M145" t="s">
         <v>1471</v>
       </c>
       <c r="N145" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O145" t="s">
         <v>1472</v>
@@ -28953,28 +29791,28 @@
         <v>173</v>
       </c>
       <c r="B146" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C146" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D146" t="s">
         <v>1562</v>
       </c>
-      <c r="C146" t="s">
+      <c r="E146" t="s">
         <v>1563</v>
       </c>
-      <c r="D146" t="s">
-        <v>1564</v>
-      </c>
-      <c r="E146" t="s">
-        <v>1565</v>
-      </c>
       <c r="F146" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="G146" t="s">
-        <v>1571</v>
+        <v>1569</v>
       </c>
       <c r="H146">
         <v>8</v>
       </c>
       <c r="I146" t="s">
-        <v>1572</v>
+        <v>1570</v>
       </c>
       <c r="J146" t="s">
         <v>977</v>
@@ -28983,7 +29821,7 @@
         <v>1473</v>
       </c>
       <c r="N146" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O146" t="s">
         <v>1474</v>
@@ -29000,28 +29838,28 @@
         <v>174</v>
       </c>
       <c r="B147" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C147" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D147" t="s">
         <v>1562</v>
       </c>
-      <c r="C147" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D147" t="s">
-        <v>1564</v>
-      </c>
       <c r="E147" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="F147" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="G147" t="s">
-        <v>1574</v>
+        <v>1572</v>
       </c>
       <c r="H147">
         <v>10</v>
       </c>
       <c r="I147" t="s">
-        <v>1575</v>
+        <v>1573</v>
       </c>
       <c r="J147" t="s">
         <v>977</v>
@@ -29030,7 +29868,7 @@
         <v>1510</v>
       </c>
       <c r="N147" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O147" t="s">
         <v>1475</v>
@@ -29047,28 +29885,28 @@
         <v>175</v>
       </c>
       <c r="B148" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C148" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D148" t="s">
         <v>1562</v>
       </c>
-      <c r="C148" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D148" t="s">
-        <v>1564</v>
-      </c>
       <c r="E148" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="F148" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="G148" t="s">
-        <v>1576</v>
+        <v>1574</v>
       </c>
       <c r="H148">
         <v>11</v>
       </c>
       <c r="I148" t="s">
-        <v>1577</v>
+        <v>1575</v>
       </c>
       <c r="J148" t="s">
         <v>977</v>
@@ -29077,7 +29915,7 @@
         <v>1476</v>
       </c>
       <c r="N148" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O148" t="s">
         <v>1477</v>
@@ -29094,28 +29932,28 @@
         <v>176</v>
       </c>
       <c r="B149" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C149" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D149" t="s">
         <v>1562</v>
       </c>
-      <c r="C149" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D149" t="s">
-        <v>1564</v>
-      </c>
       <c r="E149" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="F149" t="s">
         <v>1554</v>
       </c>
       <c r="G149" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="H149">
         <v>10</v>
       </c>
       <c r="I149" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="J149" t="s">
         <v>977</v>
@@ -29124,7 +29962,7 @@
         <v>1478</v>
       </c>
       <c r="N149" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O149" t="s">
         <v>1479</v>
@@ -29141,28 +29979,28 @@
         <v>177</v>
       </c>
       <c r="B150" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C150" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D150" t="s">
         <v>1562</v>
       </c>
-      <c r="C150" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D150" t="s">
-        <v>1564</v>
-      </c>
       <c r="E150" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="F150" t="s">
         <v>1554</v>
       </c>
       <c r="G150" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="H150">
         <v>11</v>
       </c>
       <c r="I150" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="J150" t="s">
         <v>977</v>
@@ -29171,7 +30009,7 @@
         <v>1480</v>
       </c>
       <c r="N150" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O150" t="s">
         <v>1481</v>
@@ -29188,28 +30026,28 @@
         <v>178</v>
       </c>
       <c r="B151" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C151" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D151" t="s">
         <v>1562</v>
       </c>
-      <c r="C151" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D151" t="s">
-        <v>1564</v>
-      </c>
       <c r="E151" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="F151" t="s">
         <v>1554</v>
       </c>
       <c r="G151" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
       <c r="H151">
         <v>10</v>
       </c>
       <c r="I151" t="s">
-        <v>1584</v>
+        <v>1582</v>
       </c>
       <c r="J151" t="s">
         <v>977</v>
@@ -29218,7 +30056,7 @@
         <v>1480</v>
       </c>
       <c r="N151" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O151" t="s">
         <v>1482</v>
@@ -29235,28 +30073,28 @@
         <v>179</v>
       </c>
       <c r="B152" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C152" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D152" t="s">
         <v>1562</v>
       </c>
-      <c r="C152" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D152" t="s">
-        <v>1564</v>
-      </c>
       <c r="E152" t="s">
-        <v>1585</v>
+        <v>1583</v>
       </c>
       <c r="F152" t="s">
         <v>1554</v>
       </c>
       <c r="G152" t="s">
-        <v>1586</v>
+        <v>1584</v>
       </c>
       <c r="H152">
         <v>12</v>
       </c>
       <c r="I152" t="s">
-        <v>1587</v>
+        <v>1585</v>
       </c>
       <c r="J152" t="s">
         <v>977</v>
@@ -29265,7 +30103,7 @@
         <v>1483</v>
       </c>
       <c r="N152" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O152" t="s">
         <v>1484</v>
@@ -29282,28 +30120,28 @@
         <v>180</v>
       </c>
       <c r="B153" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C153" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D153" t="s">
         <v>1562</v>
       </c>
-      <c r="C153" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D153" t="s">
-        <v>1564</v>
-      </c>
       <c r="E153" t="s">
-        <v>1588</v>
+        <v>1586</v>
       </c>
       <c r="F153" t="s">
         <v>1554</v>
       </c>
       <c r="G153" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
       <c r="H153">
         <v>12</v>
       </c>
       <c r="I153" t="s">
-        <v>1590</v>
+        <v>1588</v>
       </c>
       <c r="J153" t="s">
         <v>977</v>
@@ -29312,7 +30150,7 @@
         <v>1485</v>
       </c>
       <c r="N153" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O153" t="s">
         <v>1486</v>
@@ -29329,28 +30167,28 @@
         <v>181</v>
       </c>
       <c r="B154" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C154" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D154" t="s">
         <v>1562</v>
       </c>
-      <c r="C154" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D154" t="s">
-        <v>1564</v>
-      </c>
       <c r="E154" t="s">
+        <v>1589</v>
+      </c>
+      <c r="F154" t="s">
+        <v>1590</v>
+      </c>
+      <c r="G154" t="s">
         <v>1591</v>
-      </c>
-      <c r="F154" t="s">
-        <v>1592</v>
-      </c>
-      <c r="G154" t="s">
-        <v>1593</v>
       </c>
       <c r="H154">
         <v>12</v>
       </c>
       <c r="I154" t="s">
-        <v>1594</v>
+        <v>1592</v>
       </c>
       <c r="J154" t="s">
         <v>977</v>
@@ -29359,7 +30197,7 @@
         <v>1473</v>
       </c>
       <c r="N154" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O154" t="s">
         <v>1487</v>
@@ -29376,28 +30214,28 @@
         <v>182</v>
       </c>
       <c r="B155" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C155" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D155" t="s">
         <v>1562</v>
       </c>
-      <c r="C155" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D155" t="s">
-        <v>1564</v>
-      </c>
       <c r="E155" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="F155" t="s">
-        <v>1592</v>
+        <v>1590</v>
       </c>
       <c r="G155" t="s">
-        <v>1595</v>
+        <v>1593</v>
       </c>
       <c r="H155">
         <v>11</v>
       </c>
       <c r="I155" t="s">
-        <v>1596</v>
+        <v>1594</v>
       </c>
       <c r="J155" t="s">
         <v>977</v>
@@ -29406,7 +30244,7 @@
         <v>1471</v>
       </c>
       <c r="N155" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O155" t="s">
         <v>1488</v>
@@ -29423,37 +30261,37 @@
         <v>183</v>
       </c>
       <c r="B156" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C156" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D156" t="s">
         <v>1562</v>
       </c>
-      <c r="C156" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D156" t="s">
-        <v>1564</v>
-      </c>
       <c r="E156" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="F156" t="s">
         <v>1554</v>
       </c>
       <c r="G156" t="s">
-        <v>1597</v>
+        <v>1595</v>
       </c>
       <c r="H156">
         <v>10</v>
       </c>
       <c r="I156" t="s">
-        <v>1598</v>
+        <v>1596</v>
       </c>
       <c r="J156" t="s">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="M156" t="s">
         <v>1473</v>
       </c>
       <c r="N156" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O156" t="s">
         <v>1489</v>
@@ -29470,40 +30308,40 @@
         <v>184</v>
       </c>
       <c r="B157" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C157" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D157" t="s">
         <v>1562</v>
       </c>
-      <c r="C157" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D157" t="s">
-        <v>1564</v>
-      </c>
       <c r="E157" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="F157" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="G157" t="s">
-        <v>1600</v>
+        <v>1598</v>
       </c>
       <c r="H157">
         <v>10</v>
       </c>
       <c r="I157" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="J157" t="s">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="L157" t="s">
-        <v>1602</v>
+        <v>1600</v>
       </c>
       <c r="M157" t="s">
         <v>1471</v>
       </c>
       <c r="N157" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O157" t="s">
         <v>1490</v>
@@ -29520,40 +30358,40 @@
         <v>185</v>
       </c>
       <c r="B158" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C158" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D158" t="s">
         <v>1562</v>
       </c>
-      <c r="C158" t="s">
+      <c r="E158" t="s">
         <v>1563</v>
-      </c>
-      <c r="D158" t="s">
-        <v>1564</v>
-      </c>
-      <c r="E158" t="s">
-        <v>1565</v>
       </c>
       <c r="F158" t="s">
         <v>1554</v>
       </c>
       <c r="G158" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="H158">
         <v>10</v>
       </c>
       <c r="I158" t="s">
-        <v>1604</v>
+        <v>1602</v>
       </c>
       <c r="J158" t="s">
         <v>977</v>
       </c>
       <c r="L158" t="s">
-        <v>1568</v>
+        <v>1566</v>
       </c>
       <c r="M158" t="s">
         <v>1471</v>
       </c>
       <c r="N158" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O158" t="s">
         <v>1491</v>
@@ -29570,28 +30408,28 @@
         <v>186</v>
       </c>
       <c r="B159" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C159" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D159" t="s">
         <v>1562</v>
       </c>
-      <c r="C159" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D159" t="s">
-        <v>1564</v>
-      </c>
       <c r="E159" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="F159" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="G159" t="s">
-        <v>1605</v>
+        <v>1603</v>
       </c>
       <c r="H159">
         <v>10</v>
       </c>
       <c r="I159" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="J159" t="s">
         <v>977</v>
@@ -29600,7 +30438,7 @@
         <v>1478</v>
       </c>
       <c r="N159" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O159" t="s">
         <v>1492</v>
@@ -29617,28 +30455,28 @@
         <v>187</v>
       </c>
       <c r="B160" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C160" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D160" t="s">
         <v>1562</v>
       </c>
-      <c r="C160" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D160" t="s">
-        <v>1564</v>
-      </c>
       <c r="E160" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="F160" t="s">
         <v>1554</v>
       </c>
       <c r="G160" t="s">
-        <v>1607</v>
+        <v>1605</v>
       </c>
       <c r="H160">
         <v>9</v>
       </c>
       <c r="I160" t="s">
-        <v>1608</v>
+        <v>1606</v>
       </c>
       <c r="J160" t="s">
         <v>977</v>
@@ -29647,7 +30485,7 @@
         <v>1493</v>
       </c>
       <c r="N160" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O160" t="s">
         <v>1494</v>
@@ -29664,28 +30502,28 @@
         <v>188</v>
       </c>
       <c r="B161" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C161" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D161" t="s">
         <v>1562</v>
       </c>
-      <c r="C161" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D161" t="s">
-        <v>1564</v>
-      </c>
       <c r="E161" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="F161" t="s">
         <v>1554</v>
       </c>
       <c r="G161" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="H161">
         <v>10</v>
       </c>
       <c r="I161" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="J161" t="s">
         <v>977</v>
@@ -29694,7 +30532,7 @@
         <v>1476</v>
       </c>
       <c r="N161" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O161" t="s">
         <v>1495</v>
@@ -29711,28 +30549,28 @@
         <v>189</v>
       </c>
       <c r="B162" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C162" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D162" t="s">
         <v>1562</v>
       </c>
-      <c r="C162" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D162" t="s">
-        <v>1564</v>
-      </c>
       <c r="E162" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="F162" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="G162" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
       <c r="H162">
         <v>11</v>
       </c>
       <c r="I162" t="s">
-        <v>1612</v>
+        <v>1610</v>
       </c>
       <c r="J162" t="s">
         <v>977</v>
@@ -29741,7 +30579,7 @@
         <v>1476</v>
       </c>
       <c r="N162" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O162" t="s">
         <v>1496</v>
@@ -29758,28 +30596,28 @@
         <v>190</v>
       </c>
       <c r="B163" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C163" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D163" t="s">
         <v>1562</v>
       </c>
-      <c r="C163" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D163" t="s">
-        <v>1564</v>
-      </c>
       <c r="E163" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="F163" t="s">
-        <v>1592</v>
+        <v>1590</v>
       </c>
       <c r="G163" t="s">
-        <v>1613</v>
+        <v>1611</v>
       </c>
       <c r="H163">
         <v>8</v>
       </c>
       <c r="I163" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="J163" t="s">
         <v>977</v>
@@ -29788,7 +30626,7 @@
         <v>1476</v>
       </c>
       <c r="N163" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O163" t="s">
         <v>1497</v>
@@ -29805,28 +30643,28 @@
         <v>191</v>
       </c>
       <c r="B164" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C164" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D164" t="s">
         <v>1562</v>
       </c>
-      <c r="C164" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D164" t="s">
-        <v>1564</v>
-      </c>
       <c r="E164" t="s">
-        <v>1585</v>
+        <v>1583</v>
       </c>
       <c r="F164" t="s">
         <v>1554</v>
       </c>
       <c r="G164" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
       <c r="H164">
         <v>10</v>
       </c>
       <c r="I164" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
       <c r="J164" t="s">
         <v>977</v>
@@ -29835,7 +30673,7 @@
         <v>1104</v>
       </c>
       <c r="N164" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O164" t="s">
         <v>1498</v>
@@ -29852,28 +30690,28 @@
         <v>192</v>
       </c>
       <c r="B165" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C165" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D165" t="s">
         <v>1562</v>
       </c>
-      <c r="C165" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D165" t="s">
-        <v>1564</v>
-      </c>
       <c r="E165" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="F165" t="s">
         <v>1554</v>
       </c>
       <c r="G165" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="H165">
         <v>11</v>
       </c>
       <c r="I165" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="J165" t="s">
         <v>977</v>
@@ -29882,7 +30720,7 @@
         <v>1480</v>
       </c>
       <c r="N165" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O165" t="s">
         <v>1499</v>
@@ -29899,28 +30737,28 @@
         <v>193</v>
       </c>
       <c r="B166" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C166" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D166" t="s">
         <v>1562</v>
       </c>
-      <c r="C166" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D166" t="s">
-        <v>1564</v>
-      </c>
       <c r="E166" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="F166" t="s">
-        <v>1592</v>
+        <v>1590</v>
       </c>
       <c r="G166" t="s">
-        <v>1619</v>
+        <v>1617</v>
       </c>
       <c r="H166">
         <v>11</v>
       </c>
       <c r="I166" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="J166" t="s">
         <v>977</v>
@@ -29929,7 +30767,7 @@
         <v>1480</v>
       </c>
       <c r="N166" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O166" t="s">
         <v>1500</v>
@@ -29946,28 +30784,28 @@
         <v>195</v>
       </c>
       <c r="B167" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C167" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D167" t="s">
         <v>1562</v>
       </c>
-      <c r="C167" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D167" t="s">
-        <v>1564</v>
-      </c>
       <c r="E167" t="s">
-        <v>1588</v>
+        <v>1586</v>
       </c>
       <c r="F167" t="s">
         <v>1554</v>
       </c>
       <c r="G167" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="H167">
         <v>11</v>
       </c>
       <c r="I167" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="J167" t="s">
         <v>977</v>
@@ -29976,7 +30814,7 @@
         <v>1485</v>
       </c>
       <c r="N167" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O167" t="s">
         <v>1501</v>
@@ -29993,25 +30831,25 @@
         <v>196</v>
       </c>
       <c r="B168" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C168" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D168" t="s">
         <v>1562</v>
-      </c>
-      <c r="C168" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D168" t="s">
-        <v>1564</v>
       </c>
       <c r="F168" t="s">
         <v>1554</v>
       </c>
       <c r="G168" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="H168">
         <v>8</v>
       </c>
       <c r="I168" t="s">
-        <v>1624</v>
+        <v>1622</v>
       </c>
       <c r="J168" t="s">
         <v>977</v>
@@ -30020,7 +30858,7 @@
         <v>1476</v>
       </c>
       <c r="N168" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O168" t="s">
         <v>1502</v>
@@ -30037,28 +30875,28 @@
         <v>197</v>
       </c>
       <c r="B169" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C169" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D169" t="s">
         <v>1562</v>
       </c>
-      <c r="C169" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D169" t="s">
-        <v>1564</v>
-      </c>
       <c r="E169" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="F169" t="s">
-        <v>1592</v>
+        <v>1590</v>
       </c>
       <c r="G169" t="s">
-        <v>1625</v>
+        <v>1623</v>
       </c>
       <c r="H169">
         <v>10</v>
       </c>
       <c r="I169" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
       <c r="J169" t="s">
         <v>977</v>
@@ -30067,7 +30905,7 @@
         <v>1471</v>
       </c>
       <c r="N169" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O169" t="s">
         <v>1505</v>
@@ -30084,28 +30922,28 @@
         <v>198</v>
       </c>
       <c r="B170" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C170" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D170" t="s">
         <v>1562</v>
       </c>
-      <c r="C170" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D170" t="s">
-        <v>1564</v>
-      </c>
       <c r="E170" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="F170" t="s">
         <v>1554</v>
       </c>
       <c r="G170" t="s">
-        <v>1627</v>
+        <v>1625</v>
       </c>
       <c r="H170">
         <v>10</v>
       </c>
       <c r="I170" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="J170" t="s">
         <v>977</v>
@@ -30114,7 +30952,7 @@
         <v>1473</v>
       </c>
       <c r="N170" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O170" t="s">
         <v>1506</v>
@@ -30131,40 +30969,40 @@
         <v>199</v>
       </c>
       <c r="B171" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C171" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D171" t="s">
         <v>1562</v>
       </c>
-      <c r="C171" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D171" t="s">
-        <v>1564</v>
-      </c>
       <c r="E171" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="F171" t="s">
         <v>1554</v>
       </c>
       <c r="G171" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
       <c r="H171">
         <v>10</v>
       </c>
       <c r="I171" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
       <c r="J171" t="s">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="L171" t="s">
-        <v>1568</v>
+        <v>1566</v>
       </c>
       <c r="M171" t="s">
         <v>1473</v>
       </c>
       <c r="N171" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O171" t="s">
         <v>1507</v>
@@ -30181,28 +31019,28 @@
         <v>200</v>
       </c>
       <c r="B172" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C172" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D172" t="s">
         <v>1562</v>
       </c>
-      <c r="C172" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D172" t="s">
-        <v>1564</v>
-      </c>
       <c r="E172" t="s">
-        <v>1585</v>
+        <v>1583</v>
       </c>
       <c r="F172" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="G172" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
       <c r="H172">
         <v>11</v>
       </c>
       <c r="I172" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="J172" t="s">
         <v>977</v>
@@ -30211,7 +31049,7 @@
         <v>1104</v>
       </c>
       <c r="N172" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O172" t="s">
         <v>1508</v>
@@ -30228,28 +31066,28 @@
         <v>201</v>
       </c>
       <c r="B173" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C173" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D173" t="s">
         <v>1562</v>
       </c>
-      <c r="C173" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D173" t="s">
-        <v>1564</v>
-      </c>
       <c r="E173" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="F173" t="s">
-        <v>1592</v>
+        <v>1590</v>
       </c>
       <c r="G173" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="H173">
         <v>7</v>
       </c>
       <c r="I173" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="J173" t="s">
         <v>977</v>
@@ -30258,7 +31096,7 @@
         <v>1476</v>
       </c>
       <c r="N173" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="O173" t="s">
         <v>1509</v>
@@ -30376,10 +31214,10 @@
         <v>99</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>1645</v>
+        <v>1643</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>1653</v>
+        <v>1651</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>100</v>
@@ -30420,19 +31258,19 @@
         <v>107</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>1661</v>
+        <v>1658</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>1651</v>
+        <v>1649</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>1650</v>
+        <v>1648</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>108</v>
@@ -30441,7 +31279,7 @@
         <v>109</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>110</v>
@@ -30479,7 +31317,7 @@
         <v>115</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>1646</v>
+        <v>1644</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>116</v>
@@ -30535,10 +31373,10 @@
         <v>125</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>1635</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>126</v>
+        <v>1633</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>1648</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>1375</v>
@@ -30588,19 +31426,19 @@
         <v>132</v>
       </c>
       <c r="C6" s="13" t="s">
+        <v>1647</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>1634</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>1648</v>
+      </c>
+      <c r="F6" s="13" t="s">
         <v>1649</v>
       </c>
-      <c r="D6" s="13" t="s">
-        <v>1636</v>
-      </c>
-      <c r="E6" s="13" t="s">
+      <c r="G6" s="13" t="s">
         <v>1650</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>1651</v>
-      </c>
-      <c r="G6" s="13" t="s">
-        <v>1652</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>133</v>
@@ -30609,7 +31447,7 @@
         <v>134</v>
       </c>
       <c r="J6" s="13" t="s">
-        <v>1637</v>
+        <v>1635</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>135</v>
@@ -30621,10 +31459,10 @@
         <v>113</v>
       </c>
       <c r="N6" s="13" t="s">
-        <v>1638</v>
+        <v>1636</v>
       </c>
       <c r="O6" s="13" t="s">
-        <v>1639</v>
+        <v>1637</v>
       </c>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
@@ -30641,7 +31479,7 @@
         <v>137</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>1647</v>
+        <v>1645</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>138</v>
@@ -30697,7 +31535,7 @@
         <v>146</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>1640</v>
+        <v>1638</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>147</v>
@@ -30753,7 +31591,7 @@
         <v>156</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>1641</v>
+        <v>1639</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>126</v>
@@ -32181,7 +33019,7 @@
         <v>321</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>1654</v>
+        <v>1652</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>322</v>
@@ -32378,7 +33216,7 @@
         <v>364</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>1648</v>
+        <v>1646</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>365</v>
@@ -33012,7 +33850,7 @@
         <v>495</v>
       </c>
       <c r="F63" s="12" t="s">
-        <v>1655</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -33112,7 +33950,7 @@
         <v>1445</v>
       </c>
       <c r="F68" s="12" t="s">
-        <v>1558</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -33123,16 +33961,16 @@
         <v>42</v>
       </c>
       <c r="C69" s="12" t="s">
+        <v>1558</v>
+      </c>
+      <c r="D69" s="12" t="s">
         <v>1559</v>
-      </c>
-      <c r="D69" s="12" t="s">
-        <v>1560</v>
       </c>
       <c r="E69" s="12" t="s">
         <v>1445</v>
       </c>
       <c r="F69" s="12" t="s">
-        <v>1561</v>
+        <v>1662</v>
       </c>
     </row>
   </sheetData>

--- a/files/diet-reference-config-v1.0.0.xlsx
+++ b/files/diet-reference-config-v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C27A6596-E3F4-4B21-9D86-4DBC3044A2D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5935E65-1F87-408B-AA43-EB3374BAB0E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5482,14 +5482,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>마지막 단계 변경 이후 그 축의 끝난 축 목표 최근 4건 중 3건 완료. 끝난 축 목표가 3건 미만이면 판단하지 않음</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기존 완료 재사용 금지. 하루 1회 조정. 단계는 실천 부담 날짜가 아니라 그 축의 끝난 목표 횟수로 센다.</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>동일 축의 축 목표가 완료되지 않은 채 끝난 것 연속 2건</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -5948,17 +5940,928 @@
   </si>
   <si>
     <r>
-      <t>마지막</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
+      <t>설정</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> CFG-010 · CFG-011 · CFG-070 · CFG-071 · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>설정파라미터</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 5</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>행</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>추가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>검증규칙</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> V-42</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>관찰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>중인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>단계를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>올리지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않는다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개선</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>필요인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>기본까지만</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>연결</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>없으면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>전체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>같은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>순서로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>본다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CFG-006</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>같은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 28</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>창에서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>센다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CFG-007. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이보다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>적으면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>관찰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>중</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CFG-008. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>최근</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>유효</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>응답</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>건이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>분모</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CFG-009. 7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>건을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>못</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>채우면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>양호</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아님</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CFG-008. CFG-003</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>같은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>분모</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CFG-009. CFG-003</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>같은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>상한</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>둘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>참일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>때만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>양호</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>결합</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>대상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>설정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> ID</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>그</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 4</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>건</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>중</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>완료가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 3</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>건</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이상이면</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
     </r>
     <r>
       <rPr>
@@ -5986,235 +6889,574 @@
         <color rgb="FFFF0000"/>
         <rFont val="Carlito"/>
       </rPr>
+      <t>올린다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>56일보다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>오래된</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>세지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않는다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>단계</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>단계</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>상승</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>전제</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>상태가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>관찰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>중이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아닐</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>것</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>단계</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
       <t>변경</t>
     </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>이후</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>그</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>관찰이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끝나기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>전에는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>난이도를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>올리지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않는다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>개선</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>필요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <rFont val="Carlito"/>
       </rPr>
       <t>축의</t>
     </r>
     <r>
       <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>끝난</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>목표</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>최근</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 4</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>건</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>중</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 3</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>건</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>완료</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>세는</t>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>단계</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>상한</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>기본</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>실제로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>못</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>하고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>있는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>도전</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>주지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않는다</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>단계</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>계산</t>
     </r>
     <r>
       <rPr>
@@ -6234,2459 +7476,6 @@
         <rFont val="Carlito"/>
       </rPr>
       <t>대상</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>(CFG-070)</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>과</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>유효</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>기간</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 56</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>일</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">(CFG-071) </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>추가</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>설정</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> CFG-010 · CFG-011 · CFG-070 · CFG-071 · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>설정파라미터</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 5</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>행</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>추가</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>검증규칙</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> V-42</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>관찰</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>중인</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축은</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>단계를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>올리지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>않는다</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개선</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>필요인</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축은</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>기본까지만</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>연결</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>없으면</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>전체</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>같은</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>순서로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>본다</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>CFG-006</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>과</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>같은</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 28</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>일</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>창에서</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>센다</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">CFG-007. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>이보다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>적으면</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>관찰</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>중</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">CFG-008. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>최근</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>유효</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>응답</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>건이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>분모</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>CFG-009. 7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>건을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>못</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>채우면</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>양호</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>아님</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>CFG-008. CFG-003</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>과</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>같은</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>분모</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>CFG-009. CFG-003</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>과</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>같은</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>상한</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>둘</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>참일</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>때만</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>양호</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>결합</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대상</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>설정</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> ID</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>마지막</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>단계</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>변경</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>이후</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>그</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축의</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>끝난</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>목표</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>중</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>최근</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 4</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>건을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>본다</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>그</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 4</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>건</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>중</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>완료가</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 3</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>건</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>이상이면</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 1</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>단계</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>올린다</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>끝난</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>목표가</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 3</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>건</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>미만이면</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>판단하지</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>않는다</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>끝난</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>목표</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>최근</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 2</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>건이</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>연속</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>미완료면</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 1</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>단계</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>내린다</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>56일보다</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>오래된</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>목표는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>세지</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>않는다</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>단계</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>단계</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>상승</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>전제</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>상태가</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>관찰</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>중이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>아닐</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>것</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>목표</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>단계</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>변경</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>관찰이</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>끝나기</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>전에는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>난이도를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>올리지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>않는다</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개선</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>필요</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축의</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>단계</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>상한</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>기본</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>실제로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>못</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>하고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>있는</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축에</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>도전</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>문구를</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>주지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>않는다</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>단계</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>계산</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>대상</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>실제로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>만들어진</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>목표</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">(pool_type=AXIS_STAGE, goal_state=CREATED) </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>중</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>끝난</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>것만</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>센다</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>안내만</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>회복</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>부담</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>줄이기</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>목표는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>올리기에도</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>내리기에도</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>세지</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>않는다</t>
     </r>
   </si>
   <si>
@@ -15717,696 +14506,6 @@
   </si>
   <si>
     <t>본인이 느낀 양만 관찰. 400g 달성·혈당 개선으로 해석 금지</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>오래된</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>기록이</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>지금의</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>단계를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>좌우하지</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>않게</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>한다</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>끝난</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>목표</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 4</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>건을</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>모으는</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>데</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>보통</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 12~24</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>일이</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>걸려</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>그</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 2</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>배</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>이상</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>축</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>상태</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>기준</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 28</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>일의</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 2</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>배</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>으로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>잡았다</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>정해진</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>근거</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>값이</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>아니며</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>앱</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>출시</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>이후</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>실제</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>사용</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>데이터를</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>보고</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>조정한다</t>
-    </r>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
@@ -16937,6 +15036,1758 @@
 야식: 어젯밤 야식은 얼마나 드셨나요? 답 먹지 않음 · 조금 먹음 · 배불리 먹음 (코드 none · light · meal_sized, 점수 없음 그대로)
 식사 규칙 답: 거의 못 먹음
 끼니 이름 뒤 조사를 문장에 미리 써 두고, 치환 뒤 32자 이하로 맞춤</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>마지막 단계 변경 이후 그 축의 확정된 축 목표 최근 4건 중 3건 완료. 세는 대상(CFG-070)과 유효 기간 56일(CFG-071) 추가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>마지막</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>단계</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>변경</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>그</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축의</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>확정된</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>중</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>최근</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 4</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>건을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>본다</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>확정된</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 3</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>건</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>미만이면</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>판단하지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않는다</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>확정된</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>최근</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 2</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>건이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>연속</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>미완료면</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>단계</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>내린다</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>마지막 단계 변경 이후 그 축의 확정된 축 목표 최근 4건 중 3건 완료. 확정된 축 목표가 3건 미만이면 판단하지 않음</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기존 완료 재사용 금지. 하루 1회 조정. 단계는 실천 부담 날짜가 아니라 그 축의 확정된 목표 횟수로 센다.</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>실제로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>만들어진</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(pool_type=AXIS_STAGE, goal_state=CREATED) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>중</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>어제까지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>결과</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>완료</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>미완료</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>정해진</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>것만</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>센다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>오늘</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아직</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>완료할</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>있어</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>제외</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>안내만</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>부담</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>줄이기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>올리기에도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>내리기에도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>세지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않는다</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>오래된</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>기록이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>지금의</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>단계를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>좌우하지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않게</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>한다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>확정된</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 4</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>건을</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>모으는</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>데</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>보통</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 12~24</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>일이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>걸려</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>그</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 2</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>배</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이상</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>상태</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>기준</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 28</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>일의</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 2</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>배</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>으로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>잡았다</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>정해진</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>근거</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>값이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아니며</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>앱</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>출시</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>실제</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>사용</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>데이터를</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>보고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>조정한다</t>
+    </r>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -17962,68 +17813,68 @@
     <row r="44" spans="1:3" ht="24" customHeight="1"/>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>1522</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>1523</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
+        <v>1522</v>
+      </c>
+      <c r="B49" t="s">
+        <v>1523</v>
+      </c>
+      <c r="C49" t="s">
         <v>1524</v>
       </c>
-      <c r="B49" t="s">
+      <c r="D49" t="s">
         <v>1525</v>
-      </c>
-      <c r="C49" t="s">
-        <v>1526</v>
-      </c>
-      <c r="D49" t="s">
-        <v>1527</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="154">
       <c r="A50" s="16" t="s">
-        <v>1640</v>
+        <v>1633</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>1641</v>
+        <v>1634</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>1664</v>
+        <v>1656</v>
       </c>
       <c r="D50" s="16" t="s">
-        <v>1642</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="12" t="s">
+        <v>1526</v>
+      </c>
+      <c r="B51" s="12" t="s">
+        <v>1527</v>
+      </c>
+      <c r="C51" s="12" t="s">
+        <v>1657</v>
+      </c>
+      <c r="D51" s="12" t="s">
         <v>1528</v>
-      </c>
-      <c r="B51" s="12" t="s">
-        <v>1529</v>
-      </c>
-      <c r="C51" s="12" t="s">
-        <v>1530</v>
-      </c>
-      <c r="D51" s="12" t="s">
-        <v>1531</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="56">
       <c r="A52" s="16" t="s">
-        <v>1654</v>
+        <v>1647</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>1655</v>
+        <v>1648</v>
       </c>
       <c r="C52" s="16" t="s">
-        <v>1656</v>
+        <v>1649</v>
       </c>
       <c r="D52" s="16" t="s">
-        <v>1657</v>
+        <v>1650</v>
       </c>
     </row>
   </sheetData>
@@ -29741,40 +29592,40 @@
         <v>172</v>
       </c>
       <c r="B145" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C145" t="s">
-        <v>1561</v>
+        <v>1554</v>
       </c>
       <c r="D145" t="s">
-        <v>1562</v>
+        <v>1555</v>
       </c>
       <c r="E145" t="s">
-        <v>1563</v>
+        <v>1556</v>
       </c>
       <c r="F145" t="s">
-        <v>1554</v>
+        <v>1548</v>
       </c>
       <c r="G145" t="s">
-        <v>1564</v>
+        <v>1557</v>
       </c>
       <c r="H145">
         <v>11</v>
       </c>
       <c r="I145" t="s">
-        <v>1565</v>
+        <v>1558</v>
       </c>
       <c r="J145" t="s">
         <v>977</v>
       </c>
       <c r="L145" t="s">
-        <v>1566</v>
+        <v>1559</v>
       </c>
       <c r="M145" t="s">
         <v>1471</v>
       </c>
       <c r="N145" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O145" t="s">
         <v>1472</v>
@@ -29791,28 +29642,28 @@
         <v>173</v>
       </c>
       <c r="B146" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C146" t="s">
+        <v>1554</v>
+      </c>
+      <c r="D146" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E146" t="s">
+        <v>1556</v>
+      </c>
+      <c r="F146" t="s">
         <v>1561</v>
       </c>
-      <c r="D146" t="s">
+      <c r="G146" t="s">
         <v>1562</v>
-      </c>
-      <c r="E146" t="s">
-        <v>1563</v>
-      </c>
-      <c r="F146" t="s">
-        <v>1568</v>
-      </c>
-      <c r="G146" t="s">
-        <v>1569</v>
       </c>
       <c r="H146">
         <v>8</v>
       </c>
       <c r="I146" t="s">
-        <v>1570</v>
+        <v>1563</v>
       </c>
       <c r="J146" t="s">
         <v>977</v>
@@ -29821,7 +29672,7 @@
         <v>1473</v>
       </c>
       <c r="N146" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O146" t="s">
         <v>1474</v>
@@ -29838,28 +29689,28 @@
         <v>174</v>
       </c>
       <c r="B147" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C147" t="s">
+        <v>1554</v>
+      </c>
+      <c r="D147" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E147" t="s">
+        <v>1564</v>
+      </c>
+      <c r="F147" t="s">
         <v>1561</v>
       </c>
-      <c r="D147" t="s">
-        <v>1562</v>
-      </c>
-      <c r="E147" t="s">
-        <v>1571</v>
-      </c>
-      <c r="F147" t="s">
-        <v>1568</v>
-      </c>
       <c r="G147" t="s">
-        <v>1572</v>
+        <v>1565</v>
       </c>
       <c r="H147">
         <v>10</v>
       </c>
       <c r="I147" t="s">
-        <v>1573</v>
+        <v>1566</v>
       </c>
       <c r="J147" t="s">
         <v>977</v>
@@ -29868,7 +29719,7 @@
         <v>1510</v>
       </c>
       <c r="N147" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O147" t="s">
         <v>1475</v>
@@ -29885,28 +29736,28 @@
         <v>175</v>
       </c>
       <c r="B148" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C148" t="s">
+        <v>1554</v>
+      </c>
+      <c r="D148" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E148" t="s">
+        <v>1564</v>
+      </c>
+      <c r="F148" t="s">
         <v>1561</v>
       </c>
-      <c r="D148" t="s">
-        <v>1562</v>
-      </c>
-      <c r="E148" t="s">
-        <v>1571</v>
-      </c>
-      <c r="F148" t="s">
-        <v>1568</v>
-      </c>
       <c r="G148" t="s">
-        <v>1574</v>
+        <v>1567</v>
       </c>
       <c r="H148">
         <v>11</v>
       </c>
       <c r="I148" t="s">
-        <v>1575</v>
+        <v>1568</v>
       </c>
       <c r="J148" t="s">
         <v>977</v>
@@ -29915,7 +29766,7 @@
         <v>1476</v>
       </c>
       <c r="N148" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O148" t="s">
         <v>1477</v>
@@ -29932,28 +29783,28 @@
         <v>176</v>
       </c>
       <c r="B149" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C149" t="s">
-        <v>1561</v>
+        <v>1554</v>
       </c>
       <c r="D149" t="s">
-        <v>1562</v>
+        <v>1555</v>
       </c>
       <c r="E149" t="s">
-        <v>1571</v>
+        <v>1564</v>
       </c>
       <c r="F149" t="s">
-        <v>1554</v>
+        <v>1548</v>
       </c>
       <c r="G149" t="s">
-        <v>1576</v>
+        <v>1569</v>
       </c>
       <c r="H149">
         <v>10</v>
       </c>
       <c r="I149" t="s">
-        <v>1577</v>
+        <v>1570</v>
       </c>
       <c r="J149" t="s">
         <v>977</v>
@@ -29962,7 +29813,7 @@
         <v>1478</v>
       </c>
       <c r="N149" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O149" t="s">
         <v>1479</v>
@@ -29979,28 +29830,28 @@
         <v>177</v>
       </c>
       <c r="B150" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C150" t="s">
-        <v>1561</v>
+        <v>1554</v>
       </c>
       <c r="D150" t="s">
-        <v>1562</v>
+        <v>1555</v>
       </c>
       <c r="E150" t="s">
-        <v>1578</v>
+        <v>1571</v>
       </c>
       <c r="F150" t="s">
-        <v>1554</v>
+        <v>1548</v>
       </c>
       <c r="G150" t="s">
-        <v>1579</v>
+        <v>1572</v>
       </c>
       <c r="H150">
         <v>11</v>
       </c>
       <c r="I150" t="s">
-        <v>1580</v>
+        <v>1573</v>
       </c>
       <c r="J150" t="s">
         <v>977</v>
@@ -30009,7 +29860,7 @@
         <v>1480</v>
       </c>
       <c r="N150" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O150" t="s">
         <v>1481</v>
@@ -30026,28 +29877,28 @@
         <v>178</v>
       </c>
       <c r="B151" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C151" t="s">
-        <v>1561</v>
+        <v>1554</v>
       </c>
       <c r="D151" t="s">
-        <v>1562</v>
+        <v>1555</v>
       </c>
       <c r="E151" t="s">
-        <v>1578</v>
+        <v>1571</v>
       </c>
       <c r="F151" t="s">
-        <v>1554</v>
+        <v>1548</v>
       </c>
       <c r="G151" t="s">
-        <v>1581</v>
+        <v>1574</v>
       </c>
       <c r="H151">
         <v>10</v>
       </c>
       <c r="I151" t="s">
-        <v>1582</v>
+        <v>1575</v>
       </c>
       <c r="J151" t="s">
         <v>977</v>
@@ -30056,7 +29907,7 @@
         <v>1480</v>
       </c>
       <c r="N151" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O151" t="s">
         <v>1482</v>
@@ -30073,28 +29924,28 @@
         <v>179</v>
       </c>
       <c r="B152" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C152" t="s">
-        <v>1561</v>
+        <v>1554</v>
       </c>
       <c r="D152" t="s">
-        <v>1562</v>
+        <v>1555</v>
       </c>
       <c r="E152" t="s">
-        <v>1583</v>
+        <v>1576</v>
       </c>
       <c r="F152" t="s">
-        <v>1554</v>
+        <v>1548</v>
       </c>
       <c r="G152" t="s">
-        <v>1584</v>
+        <v>1577</v>
       </c>
       <c r="H152">
         <v>12</v>
       </c>
       <c r="I152" t="s">
-        <v>1585</v>
+        <v>1578</v>
       </c>
       <c r="J152" t="s">
         <v>977</v>
@@ -30103,7 +29954,7 @@
         <v>1483</v>
       </c>
       <c r="N152" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O152" t="s">
         <v>1484</v>
@@ -30120,28 +29971,28 @@
         <v>180</v>
       </c>
       <c r="B153" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C153" t="s">
-        <v>1561</v>
+        <v>1554</v>
       </c>
       <c r="D153" t="s">
-        <v>1562</v>
+        <v>1555</v>
       </c>
       <c r="E153" t="s">
-        <v>1586</v>
+        <v>1579</v>
       </c>
       <c r="F153" t="s">
-        <v>1554</v>
+        <v>1548</v>
       </c>
       <c r="G153" t="s">
-        <v>1587</v>
+        <v>1580</v>
       </c>
       <c r="H153">
         <v>12</v>
       </c>
       <c r="I153" t="s">
-        <v>1588</v>
+        <v>1581</v>
       </c>
       <c r="J153" t="s">
         <v>977</v>
@@ -30150,7 +30001,7 @@
         <v>1485</v>
       </c>
       <c r="N153" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O153" t="s">
         <v>1486</v>
@@ -30167,28 +30018,28 @@
         <v>181</v>
       </c>
       <c r="B154" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C154" t="s">
-        <v>1561</v>
+        <v>1554</v>
       </c>
       <c r="D154" t="s">
-        <v>1562</v>
+        <v>1555</v>
       </c>
       <c r="E154" t="s">
-        <v>1589</v>
+        <v>1582</v>
       </c>
       <c r="F154" t="s">
-        <v>1590</v>
+        <v>1583</v>
       </c>
       <c r="G154" t="s">
-        <v>1591</v>
+        <v>1584</v>
       </c>
       <c r="H154">
         <v>12</v>
       </c>
       <c r="I154" t="s">
-        <v>1592</v>
+        <v>1585</v>
       </c>
       <c r="J154" t="s">
         <v>977</v>
@@ -30197,7 +30048,7 @@
         <v>1473</v>
       </c>
       <c r="N154" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O154" t="s">
         <v>1487</v>
@@ -30214,28 +30065,28 @@
         <v>182</v>
       </c>
       <c r="B155" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C155" t="s">
-        <v>1561</v>
+        <v>1554</v>
       </c>
       <c r="D155" t="s">
-        <v>1562</v>
+        <v>1555</v>
       </c>
       <c r="E155" t="s">
-        <v>1589</v>
+        <v>1582</v>
       </c>
       <c r="F155" t="s">
-        <v>1590</v>
+        <v>1583</v>
       </c>
       <c r="G155" t="s">
-        <v>1593</v>
+        <v>1586</v>
       </c>
       <c r="H155">
         <v>11</v>
       </c>
       <c r="I155" t="s">
-        <v>1594</v>
+        <v>1587</v>
       </c>
       <c r="J155" t="s">
         <v>977</v>
@@ -30244,7 +30095,7 @@
         <v>1471</v>
       </c>
       <c r="N155" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O155" t="s">
         <v>1488</v>
@@ -30261,37 +30112,37 @@
         <v>183</v>
       </c>
       <c r="B156" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C156" t="s">
-        <v>1561</v>
+        <v>1554</v>
       </c>
       <c r="D156" t="s">
-        <v>1562</v>
+        <v>1555</v>
       </c>
       <c r="E156" t="s">
-        <v>1589</v>
+        <v>1582</v>
       </c>
       <c r="F156" t="s">
-        <v>1554</v>
+        <v>1548</v>
       </c>
       <c r="G156" t="s">
-        <v>1595</v>
+        <v>1588</v>
       </c>
       <c r="H156">
         <v>10</v>
       </c>
       <c r="I156" t="s">
-        <v>1596</v>
+        <v>1589</v>
       </c>
       <c r="J156" t="s">
-        <v>1597</v>
+        <v>1590</v>
       </c>
       <c r="M156" t="s">
         <v>1473</v>
       </c>
       <c r="N156" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O156" t="s">
         <v>1489</v>
@@ -30308,40 +30159,40 @@
         <v>184</v>
       </c>
       <c r="B157" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C157" t="s">
+        <v>1554</v>
+      </c>
+      <c r="D157" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E157" t="s">
+        <v>1582</v>
+      </c>
+      <c r="F157" t="s">
         <v>1561</v>
       </c>
-      <c r="D157" t="s">
-        <v>1562</v>
-      </c>
-      <c r="E157" t="s">
-        <v>1589</v>
-      </c>
-      <c r="F157" t="s">
-        <v>1568</v>
-      </c>
       <c r="G157" t="s">
-        <v>1598</v>
+        <v>1591</v>
       </c>
       <c r="H157">
         <v>10</v>
       </c>
       <c r="I157" t="s">
-        <v>1599</v>
+        <v>1592</v>
       </c>
       <c r="J157" t="s">
-        <v>1597</v>
+        <v>1590</v>
       </c>
       <c r="L157" t="s">
-        <v>1600</v>
+        <v>1593</v>
       </c>
       <c r="M157" t="s">
         <v>1471</v>
       </c>
       <c r="N157" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O157" t="s">
         <v>1490</v>
@@ -30358,40 +30209,40 @@
         <v>185</v>
       </c>
       <c r="B158" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C158" t="s">
-        <v>1561</v>
+        <v>1554</v>
       </c>
       <c r="D158" t="s">
-        <v>1562</v>
+        <v>1555</v>
       </c>
       <c r="E158" t="s">
-        <v>1563</v>
+        <v>1556</v>
       </c>
       <c r="F158" t="s">
-        <v>1554</v>
+        <v>1548</v>
       </c>
       <c r="G158" t="s">
-        <v>1601</v>
+        <v>1594</v>
       </c>
       <c r="H158">
         <v>10</v>
       </c>
       <c r="I158" t="s">
-        <v>1602</v>
+        <v>1595</v>
       </c>
       <c r="J158" t="s">
         <v>977</v>
       </c>
       <c r="L158" t="s">
-        <v>1566</v>
+        <v>1559</v>
       </c>
       <c r="M158" t="s">
         <v>1471</v>
       </c>
       <c r="N158" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O158" t="s">
         <v>1491</v>
@@ -30408,28 +30259,28 @@
         <v>186</v>
       </c>
       <c r="B159" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C159" t="s">
+        <v>1554</v>
+      </c>
+      <c r="D159" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E159" t="s">
+        <v>1564</v>
+      </c>
+      <c r="F159" t="s">
         <v>1561</v>
       </c>
-      <c r="D159" t="s">
-        <v>1562</v>
-      </c>
-      <c r="E159" t="s">
-        <v>1571</v>
-      </c>
-      <c r="F159" t="s">
-        <v>1568</v>
-      </c>
       <c r="G159" t="s">
-        <v>1603</v>
+        <v>1596</v>
       </c>
       <c r="H159">
         <v>10</v>
       </c>
       <c r="I159" t="s">
-        <v>1604</v>
+        <v>1597</v>
       </c>
       <c r="J159" t="s">
         <v>977</v>
@@ -30438,7 +30289,7 @@
         <v>1478</v>
       </c>
       <c r="N159" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O159" t="s">
         <v>1492</v>
@@ -30455,28 +30306,28 @@
         <v>187</v>
       </c>
       <c r="B160" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C160" t="s">
-        <v>1561</v>
+        <v>1554</v>
       </c>
       <c r="D160" t="s">
-        <v>1562</v>
+        <v>1555</v>
       </c>
       <c r="E160" t="s">
-        <v>1571</v>
+        <v>1564</v>
       </c>
       <c r="F160" t="s">
-        <v>1554</v>
+        <v>1548</v>
       </c>
       <c r="G160" t="s">
-        <v>1605</v>
+        <v>1598</v>
       </c>
       <c r="H160">
         <v>9</v>
       </c>
       <c r="I160" t="s">
-        <v>1606</v>
+        <v>1599</v>
       </c>
       <c r="J160" t="s">
         <v>977</v>
@@ -30485,7 +30336,7 @@
         <v>1493</v>
       </c>
       <c r="N160" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O160" t="s">
         <v>1494</v>
@@ -30502,28 +30353,28 @@
         <v>188</v>
       </c>
       <c r="B161" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C161" t="s">
-        <v>1561</v>
+        <v>1554</v>
       </c>
       <c r="D161" t="s">
-        <v>1562</v>
+        <v>1555</v>
       </c>
       <c r="E161" t="s">
-        <v>1571</v>
+        <v>1564</v>
       </c>
       <c r="F161" t="s">
-        <v>1554</v>
+        <v>1548</v>
       </c>
       <c r="G161" t="s">
-        <v>1607</v>
+        <v>1600</v>
       </c>
       <c r="H161">
         <v>10</v>
       </c>
       <c r="I161" t="s">
-        <v>1608</v>
+        <v>1601</v>
       </c>
       <c r="J161" t="s">
         <v>977</v>
@@ -30532,7 +30383,7 @@
         <v>1476</v>
       </c>
       <c r="N161" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O161" t="s">
         <v>1495</v>
@@ -30549,28 +30400,28 @@
         <v>189</v>
       </c>
       <c r="B162" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C162" t="s">
+        <v>1554</v>
+      </c>
+      <c r="D162" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E162" t="s">
+        <v>1564</v>
+      </c>
+      <c r="F162" t="s">
         <v>1561</v>
       </c>
-      <c r="D162" t="s">
-        <v>1562</v>
-      </c>
-      <c r="E162" t="s">
-        <v>1571</v>
-      </c>
-      <c r="F162" t="s">
-        <v>1568</v>
-      </c>
       <c r="G162" t="s">
-        <v>1609</v>
+        <v>1602</v>
       </c>
       <c r="H162">
         <v>11</v>
       </c>
       <c r="I162" t="s">
-        <v>1610</v>
+        <v>1603</v>
       </c>
       <c r="J162" t="s">
         <v>977</v>
@@ -30579,7 +30430,7 @@
         <v>1476</v>
       </c>
       <c r="N162" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O162" t="s">
         <v>1496</v>
@@ -30596,28 +30447,28 @@
         <v>190</v>
       </c>
       <c r="B163" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C163" t="s">
-        <v>1561</v>
+        <v>1554</v>
       </c>
       <c r="D163" t="s">
-        <v>1562</v>
+        <v>1555</v>
       </c>
       <c r="E163" t="s">
-        <v>1571</v>
+        <v>1564</v>
       </c>
       <c r="F163" t="s">
-        <v>1590</v>
+        <v>1583</v>
       </c>
       <c r="G163" t="s">
-        <v>1611</v>
+        <v>1604</v>
       </c>
       <c r="H163">
         <v>8</v>
       </c>
       <c r="I163" t="s">
-        <v>1612</v>
+        <v>1605</v>
       </c>
       <c r="J163" t="s">
         <v>977</v>
@@ -30626,7 +30477,7 @@
         <v>1476</v>
       </c>
       <c r="N163" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O163" t="s">
         <v>1497</v>
@@ -30643,28 +30494,28 @@
         <v>191</v>
       </c>
       <c r="B164" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C164" t="s">
-        <v>1561</v>
+        <v>1554</v>
       </c>
       <c r="D164" t="s">
-        <v>1562</v>
+        <v>1555</v>
       </c>
       <c r="E164" t="s">
-        <v>1583</v>
+        <v>1576</v>
       </c>
       <c r="F164" t="s">
-        <v>1554</v>
+        <v>1548</v>
       </c>
       <c r="G164" t="s">
-        <v>1613</v>
+        <v>1606</v>
       </c>
       <c r="H164">
         <v>10</v>
       </c>
       <c r="I164" t="s">
-        <v>1614</v>
+        <v>1607</v>
       </c>
       <c r="J164" t="s">
         <v>977</v>
@@ -30673,7 +30524,7 @@
         <v>1104</v>
       </c>
       <c r="N164" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O164" t="s">
         <v>1498</v>
@@ -30690,28 +30541,28 @@
         <v>192</v>
       </c>
       <c r="B165" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C165" t="s">
-        <v>1561</v>
+        <v>1554</v>
       </c>
       <c r="D165" t="s">
-        <v>1562</v>
+        <v>1555</v>
       </c>
       <c r="E165" t="s">
-        <v>1578</v>
+        <v>1571</v>
       </c>
       <c r="F165" t="s">
-        <v>1554</v>
+        <v>1548</v>
       </c>
       <c r="G165" t="s">
-        <v>1615</v>
+        <v>1608</v>
       </c>
       <c r="H165">
         <v>11</v>
       </c>
       <c r="I165" t="s">
-        <v>1616</v>
+        <v>1609</v>
       </c>
       <c r="J165" t="s">
         <v>977</v>
@@ -30720,7 +30571,7 @@
         <v>1480</v>
       </c>
       <c r="N165" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O165" t="s">
         <v>1499</v>
@@ -30737,28 +30588,28 @@
         <v>193</v>
       </c>
       <c r="B166" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C166" t="s">
-        <v>1561</v>
+        <v>1554</v>
       </c>
       <c r="D166" t="s">
-        <v>1562</v>
+        <v>1555</v>
       </c>
       <c r="E166" t="s">
-        <v>1578</v>
+        <v>1571</v>
       </c>
       <c r="F166" t="s">
-        <v>1590</v>
+        <v>1583</v>
       </c>
       <c r="G166" t="s">
-        <v>1617</v>
+        <v>1610</v>
       </c>
       <c r="H166">
         <v>11</v>
       </c>
       <c r="I166" t="s">
-        <v>1618</v>
+        <v>1611</v>
       </c>
       <c r="J166" t="s">
         <v>977</v>
@@ -30767,7 +30618,7 @@
         <v>1480</v>
       </c>
       <c r="N166" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O166" t="s">
         <v>1500</v>
@@ -30784,28 +30635,28 @@
         <v>195</v>
       </c>
       <c r="B167" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C167" t="s">
-        <v>1561</v>
+        <v>1554</v>
       </c>
       <c r="D167" t="s">
-        <v>1562</v>
+        <v>1555</v>
       </c>
       <c r="E167" t="s">
-        <v>1586</v>
+        <v>1579</v>
       </c>
       <c r="F167" t="s">
-        <v>1554</v>
+        <v>1548</v>
       </c>
       <c r="G167" t="s">
-        <v>1619</v>
+        <v>1612</v>
       </c>
       <c r="H167">
         <v>11</v>
       </c>
       <c r="I167" t="s">
-        <v>1620</v>
+        <v>1613</v>
       </c>
       <c r="J167" t="s">
         <v>977</v>
@@ -30814,7 +30665,7 @@
         <v>1485</v>
       </c>
       <c r="N167" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O167" t="s">
         <v>1501</v>
@@ -30831,25 +30682,25 @@
         <v>196</v>
       </c>
       <c r="B168" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C168" t="s">
-        <v>1561</v>
+        <v>1554</v>
       </c>
       <c r="D168" t="s">
-        <v>1562</v>
+        <v>1555</v>
       </c>
       <c r="F168" t="s">
-        <v>1554</v>
+        <v>1548</v>
       </c>
       <c r="G168" t="s">
-        <v>1621</v>
+        <v>1614</v>
       </c>
       <c r="H168">
         <v>8</v>
       </c>
       <c r="I168" t="s">
-        <v>1622</v>
+        <v>1615</v>
       </c>
       <c r="J168" t="s">
         <v>977</v>
@@ -30858,7 +30709,7 @@
         <v>1476</v>
       </c>
       <c r="N168" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O168" t="s">
         <v>1502</v>
@@ -30875,28 +30726,28 @@
         <v>197</v>
       </c>
       <c r="B169" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C169" t="s">
-        <v>1561</v>
+        <v>1554</v>
       </c>
       <c r="D169" t="s">
-        <v>1562</v>
+        <v>1555</v>
       </c>
       <c r="E169" t="s">
-        <v>1589</v>
+        <v>1582</v>
       </c>
       <c r="F169" t="s">
-        <v>1590</v>
+        <v>1583</v>
       </c>
       <c r="G169" t="s">
-        <v>1623</v>
+        <v>1616</v>
       </c>
       <c r="H169">
         <v>10</v>
       </c>
       <c r="I169" t="s">
-        <v>1624</v>
+        <v>1617</v>
       </c>
       <c r="J169" t="s">
         <v>977</v>
@@ -30905,7 +30756,7 @@
         <v>1471</v>
       </c>
       <c r="N169" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O169" t="s">
         <v>1505</v>
@@ -30922,28 +30773,28 @@
         <v>198</v>
       </c>
       <c r="B170" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C170" t="s">
-        <v>1561</v>
+        <v>1554</v>
       </c>
       <c r="D170" t="s">
-        <v>1562</v>
+        <v>1555</v>
       </c>
       <c r="E170" t="s">
-        <v>1589</v>
+        <v>1582</v>
       </c>
       <c r="F170" t="s">
-        <v>1554</v>
+        <v>1548</v>
       </c>
       <c r="G170" t="s">
-        <v>1625</v>
+        <v>1618</v>
       </c>
       <c r="H170">
         <v>10</v>
       </c>
       <c r="I170" t="s">
-        <v>1626</v>
+        <v>1619</v>
       </c>
       <c r="J170" t="s">
         <v>977</v>
@@ -30952,7 +30803,7 @@
         <v>1473</v>
       </c>
       <c r="N170" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O170" t="s">
         <v>1506</v>
@@ -30969,40 +30820,40 @@
         <v>199</v>
       </c>
       <c r="B171" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C171" t="s">
-        <v>1561</v>
+        <v>1554</v>
       </c>
       <c r="D171" t="s">
-        <v>1562</v>
+        <v>1555</v>
       </c>
       <c r="E171" t="s">
-        <v>1589</v>
+        <v>1582</v>
       </c>
       <c r="F171" t="s">
-        <v>1554</v>
+        <v>1548</v>
       </c>
       <c r="G171" t="s">
-        <v>1627</v>
+        <v>1620</v>
       </c>
       <c r="H171">
         <v>10</v>
       </c>
       <c r="I171" t="s">
-        <v>1628</v>
+        <v>1621</v>
       </c>
       <c r="J171" t="s">
-        <v>1597</v>
+        <v>1590</v>
       </c>
       <c r="L171" t="s">
-        <v>1566</v>
+        <v>1559</v>
       </c>
       <c r="M171" t="s">
         <v>1473</v>
       </c>
       <c r="N171" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O171" t="s">
         <v>1507</v>
@@ -31019,28 +30870,28 @@
         <v>200</v>
       </c>
       <c r="B172" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C172" t="s">
+        <v>1554</v>
+      </c>
+      <c r="D172" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E172" t="s">
+        <v>1576</v>
+      </c>
+      <c r="F172" t="s">
         <v>1561</v>
       </c>
-      <c r="D172" t="s">
-        <v>1562</v>
-      </c>
-      <c r="E172" t="s">
-        <v>1583</v>
-      </c>
-      <c r="F172" t="s">
-        <v>1568</v>
-      </c>
       <c r="G172" t="s">
-        <v>1629</v>
+        <v>1622</v>
       </c>
       <c r="H172">
         <v>11</v>
       </c>
       <c r="I172" t="s">
-        <v>1630</v>
+        <v>1623</v>
       </c>
       <c r="J172" t="s">
         <v>977</v>
@@ -31049,7 +30900,7 @@
         <v>1104</v>
       </c>
       <c r="N172" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O172" t="s">
         <v>1508</v>
@@ -31066,28 +30917,28 @@
         <v>201</v>
       </c>
       <c r="B173" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="C173" t="s">
-        <v>1561</v>
+        <v>1554</v>
       </c>
       <c r="D173" t="s">
-        <v>1562</v>
+        <v>1555</v>
       </c>
       <c r="E173" t="s">
-        <v>1571</v>
+        <v>1564</v>
       </c>
       <c r="F173" t="s">
-        <v>1590</v>
+        <v>1583</v>
       </c>
       <c r="G173" t="s">
-        <v>1631</v>
+        <v>1624</v>
       </c>
       <c r="H173">
         <v>7</v>
       </c>
       <c r="I173" t="s">
-        <v>1632</v>
+        <v>1625</v>
       </c>
       <c r="J173" t="s">
         <v>977</v>
@@ -31096,7 +30947,7 @@
         <v>1476</v>
       </c>
       <c r="N173" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="O173" t="s">
         <v>1509</v>
@@ -31214,10 +31065,10 @@
         <v>99</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>1643</v>
+        <v>1636</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>1651</v>
+        <v>1644</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>100</v>
@@ -31258,19 +31109,19 @@
         <v>107</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>1658</v>
+        <v>1651</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>1659</v>
+        <v>1652</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>1660</v>
+        <v>1653</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>1649</v>
+        <v>1642</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>1648</v>
+        <v>1641</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>108</v>
@@ -31279,7 +31130,7 @@
         <v>109</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>1661</v>
+        <v>1654</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>110</v>
@@ -31317,7 +31168,7 @@
         <v>115</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>1644</v>
+        <v>1637</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>116</v>
@@ -31373,10 +31224,10 @@
         <v>125</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>1633</v>
+        <v>1626</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>1648</v>
+        <v>1641</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>1375</v>
@@ -31426,19 +31277,19 @@
         <v>132</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>1647</v>
+        <v>1640</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>1634</v>
+        <v>1627</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>1648</v>
+        <v>1641</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>1649</v>
+        <v>1642</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>1650</v>
+        <v>1643</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>133</v>
@@ -31447,7 +31298,7 @@
         <v>134</v>
       </c>
       <c r="J6" s="13" t="s">
-        <v>1635</v>
+        <v>1628</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>135</v>
@@ -31459,10 +31310,10 @@
         <v>113</v>
       </c>
       <c r="N6" s="13" t="s">
-        <v>1636</v>
+        <v>1629</v>
       </c>
       <c r="O6" s="13" t="s">
-        <v>1637</v>
+        <v>1630</v>
       </c>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
@@ -31479,7 +31330,7 @@
         <v>137</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>1645</v>
+        <v>1638</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>138</v>
@@ -31535,7 +31386,7 @@
         <v>146</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>1638</v>
+        <v>1631</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>147</v>
@@ -31591,7 +31442,7 @@
         <v>156</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>1639</v>
+        <v>1632</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>126</v>
@@ -32243,7 +32094,7 @@
         <v>1442</v>
       </c>
       <c r="H25" t="s">
-        <v>1532</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -32263,7 +32114,7 @@
         <v>1442</v>
       </c>
       <c r="H26" t="s">
-        <v>1533</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -32283,7 +32134,7 @@
         <v>1453</v>
       </c>
       <c r="H27" t="s">
-        <v>1534</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -32306,7 +32157,7 @@
         <v>1456</v>
       </c>
       <c r="H28" t="s">
-        <v>1535</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -32329,7 +32180,7 @@
         <v>1456</v>
       </c>
       <c r="H29" t="s">
-        <v>1536</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -32352,7 +32203,7 @@
         <v>1456</v>
       </c>
       <c r="H30" t="s">
-        <v>1537</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -32375,7 +32226,7 @@
         <v>1456</v>
       </c>
       <c r="H31" t="s">
-        <v>1538</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -32398,7 +32249,7 @@
         <v>1456</v>
       </c>
       <c r="H32" t="s">
-        <v>1539</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -32421,7 +32272,7 @@
         <v>1456</v>
       </c>
       <c r="H33" t="s">
-        <v>1540</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -32444,7 +32295,7 @@
         <v>1456</v>
       </c>
       <c r="H34" t="s">
-        <v>1541</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -32467,7 +32318,7 @@
         <v>1456</v>
       </c>
       <c r="H35" t="s">
-        <v>1542</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -32475,7 +32326,7 @@
         <v>271</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="C36" s="12" t="s">
         <v>181</v>
@@ -32490,7 +32341,7 @@
         <v>1442</v>
       </c>
       <c r="H36" s="12" t="s">
-        <v>1543</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -32498,7 +32349,7 @@
         <v>271</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="C37" s="12" t="s">
         <v>170</v>
@@ -32513,7 +32364,7 @@
         <v>1442</v>
       </c>
       <c r="H37" s="12" t="s">
-        <v>1544</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -32521,7 +32372,7 @@
         <v>271</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>1519</v>
+        <v>1517</v>
       </c>
       <c r="C38" s="12" t="s">
         <v>170</v>
@@ -32536,7 +32387,7 @@
         <v>1442</v>
       </c>
       <c r="H38" s="12" t="s">
-        <v>1545</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -32544,7 +32395,7 @@
         <v>274</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>1520</v>
+        <v>1518</v>
       </c>
       <c r="C39" s="12" t="s">
         <v>181</v>
@@ -32559,15 +32410,15 @@
         <v>1442</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>1546</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="12" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>1521</v>
+        <v>1519</v>
       </c>
       <c r="C40" s="12" t="s">
         <v>194</v>
@@ -32582,7 +32433,7 @@
         <v>1442</v>
       </c>
       <c r="H40" s="12" t="s">
-        <v>1547</v>
+        <v>1541</v>
       </c>
     </row>
   </sheetData>
@@ -32800,13 +32651,13 @@
         <v>272</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>1512</v>
+        <v>1661</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>273</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>1513</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="24" customHeight="1">
@@ -32820,7 +32671,7 @@
         <v>275</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>1514</v>
+        <v>1512</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>276</v>
@@ -33019,7 +32870,7 @@
         <v>321</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>1652</v>
+        <v>1645</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>322</v>
@@ -33216,7 +33067,7 @@
         <v>364</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>1646</v>
+        <v>1639</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>365</v>
@@ -33850,7 +33701,7 @@
         <v>495</v>
       </c>
       <c r="F63" s="12" t="s">
-        <v>1653</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -33898,19 +33749,19 @@
         <v>1437</v>
       </c>
       <c r="B66" t="s">
-        <v>1548</v>
+        <v>1542</v>
       </c>
       <c r="C66" t="s">
-        <v>1549</v>
+        <v>1543</v>
       </c>
       <c r="D66" t="s">
-        <v>1550</v>
+        <v>1544</v>
       </c>
       <c r="E66" t="s">
-        <v>1551</v>
+        <v>1545</v>
       </c>
       <c r="F66" t="s">
-        <v>1552</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -33918,59 +33769,59 @@
         <v>1438</v>
       </c>
       <c r="B67" t="s">
+        <v>1542</v>
+      </c>
+      <c r="C67" t="s">
+        <v>1547</v>
+      </c>
+      <c r="D67" t="s">
         <v>1548</v>
       </c>
-      <c r="C67" t="s">
-        <v>1553</v>
-      </c>
-      <c r="D67" t="s">
-        <v>1554</v>
-      </c>
       <c r="E67" t="s">
-        <v>1551</v>
+        <v>1545</v>
       </c>
       <c r="F67" t="s">
-        <v>1555</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="12" t="s">
-        <v>1515</v>
+        <v>1513</v>
       </c>
       <c r="B68" s="12" t="s">
         <v>42</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>1556</v>
+        <v>1550</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>1557</v>
+        <v>1663</v>
       </c>
       <c r="E68" s="12" t="s">
         <v>1445</v>
       </c>
       <c r="F68" s="12" t="s">
-        <v>1663</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="12" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="B69" s="12" t="s">
         <v>42</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>1558</v>
+        <v>1551</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>1559</v>
+        <v>1552</v>
       </c>
       <c r="E69" s="12" t="s">
         <v>1445</v>
       </c>
       <c r="F69" s="12" t="s">
-        <v>1662</v>
+        <v>1664</v>
       </c>
     </row>
   </sheetData>

--- a/files/diet-reference-config-v1.0.0.xlsx
+++ b/files/diet-reference-config-v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1962CB96-EACD-4E9A-B2EA-B362B3528EED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05C255A6-7680-4520-B457-C0696D58916F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5216" uniqueCount="1669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5220" uniqueCount="1679">
   <si>
     <t>시트</t>
   </si>
@@ -17760,6 +17760,1949 @@
         <rFont val="Carlito"/>
       </rPr>
       <t>행</t>
+    </r>
+  </si>
+  <si>
+    <t>식사 시각</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>입문</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>보류</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>근거 범위에 맞춰 이유 문장 수정. 10-07 보류: 끼니 규칙 축은 목표 축이 되지 않아 나올 수 없고 「주말도 아침 챙기기」와 겹침</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>근거 범위에 맞춰 이유 문장 수정. 10-07 보류: 식사 시각 질문은 아침에만 묻고 저녁 전용·식후 불가라 나올 수 없음</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>토</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>일</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>요일</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>조건</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>정리</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>출근길에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아침</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>챙기기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>평일</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">): </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>끼니</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>규칙</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>도전</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>→</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>될</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>없어</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>안</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>나옴
+주말에도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아침</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>챙기기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>주말</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">): </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>같은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>이유로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>안</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>나옴
+주말도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아침</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>챙기기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식사</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시각</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>입문</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">): </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>요일</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>조건</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>없음</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>→</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>월요일에도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>나옴
+주말</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>저녁도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>제때</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식사</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시각</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>기본</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">): </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>저녁</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>전용이고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>불가라</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>안</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>나옴</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>출근길에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아침</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>챙기기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식사</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시각</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>입문으로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>옮김</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>평일</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>조건</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>그대로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>주말에도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아침</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>챙기기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>보류</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>주말도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아침</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>챙기기와</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>겹침</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>주말도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아침</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>챙기기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>노출조건에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>주말</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>토</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>일</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>추가
+주말</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>저녁도</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>제때</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>먹기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>보류</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>식사</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시각</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>질문은</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>아침에만</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>묻고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>저녁</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>목표</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>축이</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>되지</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>않음</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>목표문구</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시트</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> DIET-P-0088 E·F</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>열</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, DIET-P-0043·0157 source_status · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>노출조건</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시트</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> DIET-P-0264 · </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>참조설정데이터</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>문구세트</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>시트</t>
     </r>
   </si>
 </sst>
@@ -17893,7 +19836,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -17937,6 +19880,9 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -18342,7 +20288,7 @@
   <sheetPr>
     <tabColor rgb="FF315A7D"/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="22.58203125" customWidth="1"/>
@@ -18861,6 +20807,20 @@
       </c>
       <c r="D53" s="16" t="s">
         <v>1668</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="98">
+      <c r="A54" s="16" t="s">
+        <v>1675</v>
+      </c>
+      <c r="B54" s="16" t="s">
+        <v>1676</v>
+      </c>
+      <c r="C54" s="16" t="s">
+        <v>1677</v>
+      </c>
+      <c r="D54" s="16" t="s">
+        <v>1678</v>
       </c>
     </row>
   </sheetData>
@@ -25109,8 +27069,8 @@
       <c r="B36" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C36" s="8" t="s">
-        <v>1097</v>
+      <c r="C36" s="17" t="s">
+        <v>1671</v>
       </c>
       <c r="D36" s="8" t="s">
         <v>1098</v>
@@ -25140,8 +27100,8 @@
       <c r="M36" s="8" t="s">
         <v>1102</v>
       </c>
-      <c r="N36" s="8" t="s">
-        <v>1103</v>
+      <c r="N36" s="17" t="s">
+        <v>1672</v>
       </c>
       <c r="O36" s="8" t="s">
         <v>977</v>
@@ -26625,11 +28585,11 @@
       <c r="D66" s="8" t="s">
         <v>1098</v>
       </c>
-      <c r="E66" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="F66" s="8" t="s">
-        <v>1108</v>
+      <c r="E66" s="17" t="s">
+        <v>1669</v>
+      </c>
+      <c r="F66" s="17" t="s">
+        <v>1670</v>
       </c>
       <c r="G66" s="10" t="s">
         <v>1353</v>
@@ -28227,8 +30187,8 @@
       <c r="B98" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C98" s="8" t="s">
-        <v>1097</v>
+      <c r="C98" s="17" t="s">
+        <v>1671</v>
       </c>
       <c r="D98" s="8" t="s">
         <v>1098</v>
@@ -28256,8 +30216,8 @@
       <c r="M98" s="8" t="s">
         <v>1135</v>
       </c>
-      <c r="N98" s="8" t="s">
-        <v>1103</v>
+      <c r="N98" s="17" t="s">
+        <v>1673</v>
       </c>
       <c r="O98" s="8" t="s">
         <v>1047</v>
@@ -31735,8 +33695,8 @@
       <c r="I169" t="s">
         <v>1615</v>
       </c>
-      <c r="J169" t="s">
-        <v>975</v>
+      <c r="J169" s="12" t="s">
+        <v>1674</v>
       </c>
       <c r="M169" t="s">
         <v>1469</v>

--- a/files/diet-reference-config-v1.0.0.xlsx
+++ b/files/diet-reference-config-v1.0.0.xlsx
@@ -36793,22 +36793,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement i="0"/>
-        </ext>
-      </extLst>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement i="0"/>
-        </ext>
-      </extLst>
     </xf>
   </cellXfs>
   <cellStyles count="2">

--- a/files/diet-reference-config-v1.0.0.xlsx
+++ b/files/diet-reference-config-v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97927BD5-47F8-45E8-97D3-7FA4A7EFF76E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7640342-68B3-43C8-B704-896C793E85E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5475" uniqueCount="1738">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5557" uniqueCount="1759">
   <si>
     <t>시트</t>
   </si>
@@ -26516,13 +26516,78 @@
   </si>
   <si>
     <t>노출조건 시트 DIET-P-0007 · 0011 · 0037 · 0087 · 0095 · 0110 · 0124 · 0165 · 0182 · 0183 · 0198 · 0199 · 0225 time_code · 참조설정데이터 노출조건 시트</t>
+  </si>
+  <si>
+    <t>2026-02-16</t>
+  </si>
+  <si>
+    <t>설 연휴</t>
+  </si>
+  <si>
+    <t>기획 확정(10-08). 공식 공고 확인 전</t>
+  </si>
+  <si>
+    <t>2026-10-08</t>
+  </si>
+  <si>
+    <t>2026-02-17</t>
+  </si>
+  <si>
+    <t>2026-02-18</t>
+  </si>
+  <si>
+    <t>2026-09-24</t>
+  </si>
+  <si>
+    <t>추석 연휴</t>
+  </si>
+  <si>
+    <t>2026-09-25</t>
+  </si>
+  <si>
+    <t>2026-09-26</t>
+  </si>
+  <si>
+    <t>2027-02-05</t>
+  </si>
+  <si>
+    <t>2027-02-06</t>
+  </si>
+  <si>
+    <t>2027-02-07</t>
+  </si>
+  <si>
+    <t>2027-02-08</t>
+  </si>
+  <si>
+    <t>2027-09-14</t>
+  </si>
+  <si>
+    <t>2027-09-15</t>
+  </si>
+  <si>
+    <t>2027-09-16</t>
+  </si>
+  <si>
+    <t>명절 날짜 목록 · 끼니 규칙 축 열기</t>
+  </si>
+  <si>
+    <t>명절 날짜 목록(달력일자 시트)이 비어 있어 명절·연휴 문구 6개가 한 번도 나올 수 없었음
+끼니 규칙 축 문구 14개는 목표 축이 될 수 없다고 적혀 있었음</t>
+  </si>
+  <si>
+    <t>달력일자 시트에 설·추석 연휴 13일(2026 설 2/16~18 · 추석 9/24~26, 2027 설 2/5~8 · 추석 9/14~16)을 넣고, 명절·연휴 문구는 이 날짜에만 나온다
+끼니 규칙 축도 일반 축으로 본다: 그날 질문 축 · 직접 선택 연결 축에 통과 문구가 없을 때 끼니 규칙 축 문구가 후보가 된다</t>
+  </si>
+  <si>
+    <t>달력일자 시트 2~14행 · 구현기준 R-03 · R-08 · R-10 · 검증규칙 V-39 · V-50 · 참조설정데이터 달력일자 시트</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -26598,6 +26663,11 @@
       <color rgb="FF000000"/>
       <name val="Carlito"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Carlito"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -26641,7 +26711,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -26709,6 +26779,11 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -28830,7 +28905,7 @@
   <sheetPr>
     <tabColor rgb="FF315A7D"/>
   </sheetPr>
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="4" width="60.58203125" customWidth="1"/>
@@ -29396,6 +29471,20 @@
         <v>1737</v>
       </c>
     </row>
+    <row r="52" spans="1:4" ht="52">
+      <c r="A52" s="8" t="s">
+        <v>1755</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>1756</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>1757</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>1758</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -29404,7 +29493,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="3" width="14.58203125" customWidth="1"/>
@@ -29434,12 +29523,264 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="18"/>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
+      <c r="A2" s="25" t="s">
+        <v>773</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>1738</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>899</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>1739</v>
+      </c>
+      <c r="E2" s="20" t="s">
+        <v>1740</v>
+      </c>
+      <c r="F2" s="25" t="s">
+        <v>1741</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="26" t="s">
+        <v>773</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>1742</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>899</v>
+      </c>
+      <c r="D3" s="27" t="s">
+        <v>1739</v>
+      </c>
+      <c r="E3" s="27" t="s">
+        <v>1740</v>
+      </c>
+      <c r="F3" s="26" t="s">
+        <v>1741</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="26" t="s">
+        <v>773</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>1743</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>899</v>
+      </c>
+      <c r="D4" s="27" t="s">
+        <v>1739</v>
+      </c>
+      <c r="E4" s="27" t="s">
+        <v>1740</v>
+      </c>
+      <c r="F4" s="26" t="s">
+        <v>1741</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="26" t="s">
+        <v>773</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>1744</v>
+      </c>
+      <c r="C5" s="27" t="s">
+        <v>899</v>
+      </c>
+      <c r="D5" s="27" t="s">
+        <v>1745</v>
+      </c>
+      <c r="E5" s="27" t="s">
+        <v>1740</v>
+      </c>
+      <c r="F5" s="26" t="s">
+        <v>1741</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="26" t="s">
+        <v>773</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>1746</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>899</v>
+      </c>
+      <c r="D6" s="27" t="s">
+        <v>1745</v>
+      </c>
+      <c r="E6" s="27" t="s">
+        <v>1740</v>
+      </c>
+      <c r="F6" s="26" t="s">
+        <v>1741</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="26" t="s">
+        <v>773</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>1747</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>899</v>
+      </c>
+      <c r="D7" s="27" t="s">
+        <v>1745</v>
+      </c>
+      <c r="E7" s="27" t="s">
+        <v>1740</v>
+      </c>
+      <c r="F7" s="26" t="s">
+        <v>1741</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="26" t="s">
+        <v>773</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>1748</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>899</v>
+      </c>
+      <c r="D8" s="27" t="s">
+        <v>1739</v>
+      </c>
+      <c r="E8" s="27" t="s">
+        <v>1740</v>
+      </c>
+      <c r="F8" s="26" t="s">
+        <v>1741</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="26" t="s">
+        <v>773</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>1749</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>899</v>
+      </c>
+      <c r="D9" s="27" t="s">
+        <v>1739</v>
+      </c>
+      <c r="E9" s="27" t="s">
+        <v>1740</v>
+      </c>
+      <c r="F9" s="26" t="s">
+        <v>1741</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="26" t="s">
+        <v>773</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>1750</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>899</v>
+      </c>
+      <c r="D10" s="27" t="s">
+        <v>1739</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>1740</v>
+      </c>
+      <c r="F10" s="26" t="s">
+        <v>1741</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="26" t="s">
+        <v>773</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>1751</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>899</v>
+      </c>
+      <c r="D11" s="27" t="s">
+        <v>1739</v>
+      </c>
+      <c r="E11" s="27" t="s">
+        <v>1740</v>
+      </c>
+      <c r="F11" s="26" t="s">
+        <v>1741</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="26" t="s">
+        <v>773</v>
+      </c>
+      <c r="B12" s="26" t="s">
+        <v>1752</v>
+      </c>
+      <c r="C12" s="27" t="s">
+        <v>899</v>
+      </c>
+      <c r="D12" s="27" t="s">
+        <v>1745</v>
+      </c>
+      <c r="E12" s="27" t="s">
+        <v>1740</v>
+      </c>
+      <c r="F12" s="26" t="s">
+        <v>1741</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="26" t="s">
+        <v>773</v>
+      </c>
+      <c r="B13" s="26" t="s">
+        <v>1753</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>899</v>
+      </c>
+      <c r="D13" s="27" t="s">
+        <v>1745</v>
+      </c>
+      <c r="E13" s="27" t="s">
+        <v>1740</v>
+      </c>
+      <c r="F13" s="26" t="s">
+        <v>1741</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="26" t="s">
+        <v>773</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>1754</v>
+      </c>
+      <c r="C14" s="27" t="s">
+        <v>899</v>
+      </c>
+      <c r="D14" s="27" t="s">
+        <v>1745</v>
+      </c>
+      <c r="E14" s="27" t="s">
+        <v>1740</v>
+      </c>
+      <c r="F14" s="26" t="s">
+        <v>1741</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>

--- a/files/diet-reference-config-v1.0.0.xlsx
+++ b/files/diet-reference-config-v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7640342-68B3-43C8-B704-896C793E85E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBBA5790-E564-4A80-BE21-752D87043F7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26576,11 +26576,12 @@
 끼니 규칙 축 문구 14개는 목표 축이 될 수 없다고 적혀 있었음</t>
   </si>
   <si>
-    <t>달력일자 시트에 설·추석 연휴 13일(2026 설 2/16~18 · 추석 9/24~26, 2027 설 2/5~8 · 추석 9/14~16)을 넣고, 명절·연휴 문구는 이 날짜에만 나온다
+    <t>달력일자 시트 2~14행 · 구현기준 R-03 · R-08 · R-10 · 검증규칙 V-39 · V-50 · 참조설정데이터 달력일자 시트</t>
+  </si>
+  <si>
+    <t>달력일자 시트에 설·추석 연휴 13일(2026 설 2/16~18 · 추석 9/24~26, 2027 설 2/5~8 · 추석 9/14~16)을 넣고, 명절·연휴 문구는 이 날짜에만 나오고, 그 날짜에는 다른 문구보다 먼저 쓴다
 끼니 규칙 축도 일반 축으로 본다: 그날 질문 축 · 직접 선택 연결 축에 통과 문구가 없을 때 끼니 규칙 축 문구가 후보가 된다</t>
-  </si>
-  <si>
-    <t>달력일자 시트 2~14행 · 구현기준 R-03 · R-08 · R-10 · 검증규칙 V-39 · V-50 · 참조설정데이터 달력일자 시트</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -29471,7 +29472,7 @@
         <v>1737</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="52">
+    <row r="52" spans="1:4" ht="65">
       <c r="A52" s="8" t="s">
         <v>1755</v>
       </c>
@@ -29479,10 +29480,10 @@
         <v>1756</v>
       </c>
       <c r="C52" s="8" t="s">
+        <v>1758</v>
+      </c>
+      <c r="D52" s="8" t="s">
         <v>1757</v>
-      </c>
-      <c r="D52" s="8" t="s">
-        <v>1758</v>
       </c>
     </row>
   </sheetData>

--- a/files/diet-reference-config-v1.0.0.xlsx
+++ b/files/diet-reference-config-v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{768A1CE9-0F11-4F68-9366-4FC526DCD996}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67F63235-CDE0-478D-97DC-0C542F684407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-810" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10173" uniqueCount="2897">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10183" uniqueCount="2897">
   <si>
     <t>시트</t>
   </si>
@@ -54220,8 +54220,12 @@
       <c r="N173" s="19" t="s">
         <v>1716</v>
       </c>
-      <c r="O173" s="9"/>
-      <c r="P173" s="9"/>
+      <c r="O173" s="17" t="s">
+        <v>1683</v>
+      </c>
+      <c r="P173" s="17" t="s">
+        <v>99</v>
+      </c>
       <c r="Q173" s="9"/>
     </row>
     <row r="174" spans="1:17" ht="26">
@@ -54265,8 +54269,12 @@
       <c r="N174" s="19" t="s">
         <v>1716</v>
       </c>
-      <c r="O174" s="9"/>
-      <c r="P174" s="9"/>
+      <c r="O174" s="17" t="s">
+        <v>1685</v>
+      </c>
+      <c r="P174" s="17" t="s">
+        <v>99</v>
+      </c>
       <c r="Q174" s="9"/>
     </row>
     <row r="175" spans="1:17">
@@ -54310,8 +54318,12 @@
       <c r="N175" s="19" t="s">
         <v>1716</v>
       </c>
-      <c r="O175" s="9"/>
-      <c r="P175" s="9"/>
+      <c r="O175" s="17" t="s">
+        <v>1686</v>
+      </c>
+      <c r="P175" s="17" t="s">
+        <v>99</v>
+      </c>
       <c r="Q175" s="9"/>
     </row>
     <row r="176" spans="1:17">
@@ -54353,8 +54365,12 @@
       <c r="N176" s="19" t="s">
         <v>1723</v>
       </c>
-      <c r="O176" s="9"/>
-      <c r="P176" s="9"/>
+      <c r="O176" s="17" t="s">
+        <v>1687</v>
+      </c>
+      <c r="P176" s="17" t="s">
+        <v>99</v>
+      </c>
       <c r="Q176" s="9"/>
     </row>
     <row r="177" spans="1:17">
@@ -54396,8 +54412,12 @@
       <c r="N177" s="19" t="s">
         <v>1723</v>
       </c>
-      <c r="O177" s="9"/>
-      <c r="P177" s="9"/>
+      <c r="O177" s="17" t="s">
+        <v>1688</v>
+      </c>
+      <c r="P177" s="17" t="s">
+        <v>99</v>
+      </c>
       <c r="Q177" s="9"/>
     </row>
     <row r="178" spans="1:17">

--- a/files/diet-reference-config-v1.0.0.xlsx
+++ b/files/diet-reference-config-v1.0.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4FE51CC-647E-4FA9-82DA-406AB208F470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B23D7012-60D1-4938-8CB8-EA275F44964C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31230" yWindow="1420" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2660" yWindow="2660" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="안내" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10600" uniqueCount="3311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10604" uniqueCount="3315">
   <si>
     <t>시트</t>
   </si>
@@ -31104,6 +31104,22 @@
   </si>
   <si>
     <t>평소 양은 영양 적정량이 아니다. 「거의 못 먹거나 거름」은 거의 못 먹은 끼니와 거른 끼니를 나누지 않는다.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>세 번째 선택지 문구 바꿈</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>축정의 「끼니 규칙」 답 3번이 「거의 못 먹음」. 안내 「고정 문항의 한계」에 「거의 못 먹음과 결식은 분리 추정하지 않는다」</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>답 3번을 「거의 못 먹거나 거름」으로 바꿈(데이터계약과 같은 값). 안내 문장은 「「거의 못 먹거나 거름」은 거의 못 먹은 끼니와 거른 끼니를 나누지 않는다」로 고침</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>축정의 끼니 규칙 행 · 안내 「고정 문항의 한계」</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -33445,7 +33461,7 @@
   <sheetPr>
     <tabColor rgb="FF315A7D"/>
   </sheetPr>
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="4" width="60.58203125" customWidth="1"/>
@@ -34023,6 +34039,20 @@
       </c>
       <c r="D52" s="26" t="s">
         <v>3308</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="39">
+      <c r="A53" s="26" t="s">
+        <v>3311</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>3312</v>
+      </c>
+      <c r="C53" s="26" t="s">
+        <v>3313</v>
+      </c>
+      <c r="D53" s="26" t="s">
+        <v>3314</v>
       </c>
     </row>
   </sheetData>

--- a/files/diet-reference-config-v1.0.0.xlsx
+++ b/files/diet-reference-config-v1.0.0.xlsx
@@ -2167,7 +2167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="60.58203125" customWidth="1" min="1" max="4"/>
@@ -3014,6 +3014,28 @@
       <c r="D54" s="26" t="inlineStr">
         <is>
           <t>축정의 9~10행 · 설정값 · 설정파라미터 · 안내 시트 표</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="26" t="inlineStr">
+        <is>
+          <t>식후 행동 판정 기준 추가 (10-14)</t>
+        </is>
+      </c>
+      <c r="B55" s="26" t="inlineStr">
+        <is>
+          <t>식후에 걸었는지 판정 기준이 없었음</t>
+        </is>
+      </c>
+      <c r="C55" s="26" t="inlineStr">
+        <is>
+          <t>설정값 CFG-086~088(5분 초과 이어 걷기 · 300보 · 운동 기록) 추가. 데이터계약 R-12와 같은 값</t>
+        </is>
+      </c>
+      <c r="D55" s="26" t="inlineStr">
+        <is>
+          <t>설정값 · 설정파라미터</t>
         </is>
       </c>
     </row>
@@ -55302,7 +55324,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="10.58203125" customWidth="1" min="1" max="1"/>
@@ -57457,6 +57479,114 @@
       <c r="H59" s="18" t="inlineStr">
         <is>
           <t>12:00~12:30 답 비율</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="18" t="inlineStr">
+        <is>
+          <t>CFG-086</t>
+        </is>
+      </c>
+      <c r="B60" s="18" t="inlineStr">
+        <is>
+          <t>POST_MEAL_STREAK_MINUTES</t>
+        </is>
+      </c>
+      <c r="C60" s="18" t="inlineStr">
+        <is>
+          <t>GT</t>
+        </is>
+      </c>
+      <c r="D60" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="E60" s="4" t="n"/>
+      <c r="F60" s="18" t="inlineStr">
+        <is>
+          <t>MINUTE</t>
+        </is>
+      </c>
+      <c r="G60" s="18" t="inlineStr">
+        <is>
+          <t>SOURCE_ATOM</t>
+        </is>
+      </c>
+      <c r="H60" s="18" t="inlineStr">
+        <is>
+          <t>5분을 넘어야 함</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="18" t="inlineStr">
+        <is>
+          <t>CFG-086</t>
+        </is>
+      </c>
+      <c r="B61" s="18" t="inlineStr">
+        <is>
+          <t>POST_MEAL_STREAK_STEPS_PER_MINUTE</t>
+        </is>
+      </c>
+      <c r="C61" s="18" t="inlineStr">
+        <is>
+          <t>GTE</t>
+        </is>
+      </c>
+      <c r="D61" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="E61" s="4" t="n"/>
+      <c r="F61" s="18" t="inlineStr">
+        <is>
+          <t>COUNT</t>
+        </is>
+      </c>
+      <c r="G61" s="18" t="inlineStr">
+        <is>
+          <t>SOURCE_ATOM</t>
+        </is>
+      </c>
+      <c r="H61" s="18" t="inlineStr">
+        <is>
+          <t>분당 걸음</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="18" t="inlineStr">
+        <is>
+          <t>CFG-087</t>
+        </is>
+      </c>
+      <c r="B62" s="18" t="inlineStr">
+        <is>
+          <t>POST_MEAL_TOTAL_STEPS</t>
+        </is>
+      </c>
+      <c r="C62" s="18" t="inlineStr">
+        <is>
+          <t>GTE</t>
+        </is>
+      </c>
+      <c r="D62" s="18" t="n">
+        <v>300</v>
+      </c>
+      <c r="E62" s="4" t="n"/>
+      <c r="F62" s="18" t="inlineStr">
+        <is>
+          <t>COUNT</t>
+        </is>
+      </c>
+      <c r="G62" s="18" t="inlineStr">
+        <is>
+          <t>SOURCE_ATOM</t>
+        </is>
+      </c>
+      <c r="H62" s="18" t="inlineStr">
+        <is>
+          <t>관찰 시간 합계</t>
         </is>
       </c>
     </row>
@@ -57475,7 +57605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:F86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="10.58203125" customWidth="1" min="1" max="1"/>
@@ -60089,6 +60219,102 @@
         </is>
       </c>
       <c r="F83" s="16" t="inlineStr">
+        <is>
+          <t>maiReport_식이_식사시각질문_v1.0.0.html (2026-10-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="18" t="inlineStr">
+        <is>
+          <t>CFG-086</t>
+        </is>
+      </c>
+      <c r="B84" s="18" t="inlineStr">
+        <is>
+          <t>식후 행동</t>
+        </is>
+      </c>
+      <c r="C84" s="18" t="inlineStr">
+        <is>
+          <t>식후 이어 걷기 기준</t>
+        </is>
+      </c>
+      <c r="D84" s="16" t="inlineStr">
+        <is>
+          <t>5분 초과 · 분당 20보 이상</t>
+        </is>
+      </c>
+      <c r="E84" s="18" t="inlineStr">
+        <is>
+          <t>식후 관찰 시간 안에 분당 20보 이상이 5분 넘게 이어지면 「걸었음」. 임시값</t>
+        </is>
+      </c>
+      <c r="F84" s="16" t="inlineStr">
+        <is>
+          <t>maiReport_식이_식사시각질문_v1.0.0.html (2026-10-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="18" t="inlineStr">
+        <is>
+          <t>CFG-087</t>
+        </is>
+      </c>
+      <c r="B85" s="18" t="inlineStr">
+        <is>
+          <t>식후 행동</t>
+        </is>
+      </c>
+      <c r="C85" s="18" t="inlineStr">
+        <is>
+          <t>식후 합계 걸음 기준</t>
+        </is>
+      </c>
+      <c r="D85" s="16" t="inlineStr">
+        <is>
+          <t>300보</t>
+        </is>
+      </c>
+      <c r="E85" s="18" t="inlineStr">
+        <is>
+          <t>식후 관찰 시간 안 합계 300보 이상이면 「걸었음」. 임시값</t>
+        </is>
+      </c>
+      <c r="F85" s="16" t="inlineStr">
+        <is>
+          <t>maiReport_식이_식사시각질문_v1.0.0.html (2026-10-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="18" t="inlineStr">
+        <is>
+          <t>CFG-088</t>
+        </is>
+      </c>
+      <c r="B86" s="18" t="inlineStr">
+        <is>
+          <t>식후 행동</t>
+        </is>
+      </c>
+      <c r="C86" s="18" t="inlineStr">
+        <is>
+          <t>식후 운동 기록 인정</t>
+        </is>
+      </c>
+      <c r="D86" s="16" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E86" s="18" t="inlineStr">
+        <is>
+          <t>관찰 시간 안에 운동 기록이 시작되면 「걸었음」</t>
+        </is>
+      </c>
+      <c r="F86" s="16" t="inlineStr">
         <is>
           <t>maiReport_식이_식사시각질문_v1.0.0.html (2026-10-14)</t>
         </is>

--- a/files/diet-reference-config-v1.0.0.xlsx
+++ b/files/diet-reference-config-v1.0.0.xlsx
@@ -57391,7 +57391,7 @@
         </is>
       </c>
       <c r="D57" s="18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E57" s="4" t="n"/>
       <c r="F57" s="18" t="inlineStr">
@@ -57406,7 +57406,7 @@
       </c>
       <c r="H57" s="18" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>전체. 보통 5, 많으면 6</t>
         </is>
       </c>
     </row>
@@ -60146,7 +60146,7 @@
       </c>
       <c r="D81" s="16" t="inlineStr">
         <is>
-          <t>최대 1 · 식이 최대 3 · 전체 최대 5</t>
+          <t>최대 1 · 식이 최대 3 · 전체 최대 5~6</t>
         </is>
       </c>
       <c r="E81" s="18" t="inlineStr">

--- a/files/diet-reference-config-v1.0.0.xlsx
+++ b/files/diet-reference-config-v1.0.0.xlsx
@@ -3008,7 +3008,7 @@
       </c>
       <c r="C54" s="26" t="inlineStr">
         <is>
-          <t>축정의에 이어 묻는 질문 2행(DIET-Q-08 점심·저녁 「{끼니}은 언제쯤 드셨어요?」 · DIET-Q-09 「아침은 몇 시쯤 드셨어요?」, 축 아님 · 점수 없음) 추가. 설정값 · 설정파라미터에 CFG-072~085(버튼 간격 · 내림 · 멈춤 시각 · 끼니 시작 기본값 · 아침 경계 · 추정 임시값 · 질문 수) 추가(데이터계약과 같은 값)</t>
+          <t>축정의에 이어 묻는 질문 2행(DIET-Q-08 점심·저녁 「{끼니}은 언제쯤 드셨어요?」 · DIET-Q-09 「아침은 몇 시쯤 드셨어요?」, 축 아님 · 점수 없음) 추가. 설정값 · 설정파라미터에 CFG-072~085(버튼 간격 · 내림 · 선택지 상한 시각 · 끼니 시작 기본값 · 아침 경계 · 추정 임시값 · 질문 수) 추가(데이터계약과 같은 값)</t>
         </is>
       </c>
       <c r="D54" s="26" t="inlineStr">
@@ -55277,7 +55277,7 @@
       </c>
       <c r="J11" s="28" t="inlineStr">
         <is>
-          <t>버튼은 7시 · 8시 정각 고정(아침 질문은 멈춤 시각 9시를 늘 지난 뒤). 점수 · 등급 없음. 회전 후보 아님</t>
+          <t>버튼은 7시 · 8시 정각 고정(아침 질문은 선택지 상한 시각 9시를 늘 지난 뒤). 점수 · 등급 없음. 회전 후보 아님</t>
         </is>
       </c>
       <c r="K11" s="27" t="inlineStr">
@@ -59853,7 +59853,7 @@
       </c>
       <c r="C72" s="18" t="inlineStr">
         <is>
-          <t>멈춤 시각 · 아침</t>
+          <t>선택지 상한 시각 · 아침</t>
         </is>
       </c>
       <c r="D72" s="16" t="inlineStr">
@@ -59885,7 +59885,7 @@
       </c>
       <c r="C73" s="18" t="inlineStr">
         <is>
-          <t>멈춤 시각 · 점심</t>
+          <t>선택지 상한 시각 · 점심</t>
         </is>
       </c>
       <c r="D73" s="16" t="inlineStr">
@@ -59917,7 +59917,7 @@
       </c>
       <c r="C74" s="18" t="inlineStr">
         <is>
-          <t>멈춤 시각 · 저녁</t>
+          <t>선택지 상한 시각 · 저녁</t>
         </is>
       </c>
       <c r="D74" s="16" t="inlineStr">

--- a/files/diet-reference-config-v1.0.0.xlsx
+++ b/files/diet-reference-config-v1.0.0.xlsx
@@ -2167,7 +2167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:D56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="60.58203125" customWidth="1" min="1" max="4"/>
@@ -3036,6 +3036,28 @@
       <c r="D55" s="26" t="inlineStr">
         <is>
           <t>설정값 · 설정파라미터</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="26" t="inlineStr">
+        <is>
+          <t>시각 단계 선택지 글자 · 어제 저녁 질문 (10-14)</t>
+        </is>
+      </c>
+      <c r="B56" s="26" t="inlineStr">
+        <is>
+          <t>선택지 큰 글자가 시각이라 길고, 어제 저녁은 묻지 않았음</t>
+        </is>
+      </c>
+      <c r="C56" s="26" t="inlineStr">
+        <is>
+          <t>축정의 9행 선택지를 「1시간 이내 / 1~2시간 전 / 그보다 전」으로, 11행 어제 저녁(DIET-Q-10) 추가, 설정값 CFG-089</t>
+        </is>
+      </c>
+      <c r="D56" s="26" t="inlineStr">
+        <is>
+          <t>축정의 · 설정값 · 설정파라미터</t>
         </is>
       </c>
     </row>
@@ -54377,7 +54399,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:R12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="10.58203125" customWidth="1" min="1" max="1"/>
@@ -55174,22 +55196,22 @@
       </c>
       <c r="E10" s="27" t="inlineStr">
         <is>
-          <t>{t0} 이후 (1시간 이내)</t>
+          <t>1시간 이내 (작은 글씨 {t0} 이후)</t>
         </is>
       </c>
       <c r="F10" s="27" t="inlineStr">
         <is>
-          <t>{t1}~{t0} (1~2시간 전)</t>
+          <t>1~2시간 전 (작은 글씨 {t1}~{t0})</t>
         </is>
       </c>
       <c r="G10" s="27" t="inlineStr">
         <is>
-          <t>{t1} 이전 (그보다 전)</t>
+          <t>그보다 전 (작은 글씨 {t1} 이전)</t>
         </is>
       </c>
       <c r="H10" s="27" t="inlineStr">
         <is>
-          <t>오늘 점심 · 오늘 저녁. 고정 질문에 「충분히 먹음 · 적게 · 몇 입만」으로 답한 바로 뒤. 어제 저녁 · 「못 먹거나 거름」 · 건강 앱 식사 기록이 있으면 묻지 않음</t>
+          <t>오늘 점심 · 오늘 저녁. 고정 질문에 「충분히 먹음 · 적게 · 몇 입만」으로 답한 바로 뒤. 「못 먹거나 거름」 · 건강 앱 식사 기록이 있으면 묻지 않음</t>
         </is>
       </c>
       <c r="I10" s="27" t="inlineStr">
@@ -55308,6 +55330,84 @@
       <c r="P11" s="27" t="n"/>
       <c r="Q11" s="27" t="n"/>
       <c r="R11" s="27" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="27" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="27" t="inlineStr">
+        <is>
+          <t>식사 시각 단계 (축 아님 · 이어 묻기)</t>
+        </is>
+      </c>
+      <c r="C12" s="28" t="inlineStr">
+        <is>
+          <t>어제 저녁을 먹은 시각의 대략 범위</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>어제 저녁은 몇 시쯤 드셨어요?</t>
+        </is>
+      </c>
+      <c r="E12" s="27" t="inlineStr">
+        <is>
+          <t>7시 이전</t>
+        </is>
+      </c>
+      <c r="F12" s="27" t="inlineStr">
+        <is>
+          <t>7시~8시</t>
+        </is>
+      </c>
+      <c r="G12" s="27" t="inlineStr">
+        <is>
+          <t>8시 이후</t>
+        </is>
+      </c>
+      <c r="H12" s="27" t="inlineStr">
+        <is>
+          <t>어제 저녁(00~10시 진입). 조건은 위와 같음. 어젯밤 이미 답했으면 다시 묻지 않음</t>
+        </is>
+      </c>
+      <c r="I12" s="27" t="inlineStr">
+        <is>
+          <t>일상안정(최근 7일 식후 행동) 입력</t>
+        </is>
+      </c>
+      <c r="J12" s="28" t="inlineStr">
+        <is>
+          <t>저녁 7시 · 8시 정각 고정. 점수 · 등급 없음. 회전 후보 아님</t>
+        </is>
+      </c>
+      <c r="K12" s="27" t="inlineStr">
+        <is>
+          <t>DIET-Q-10</t>
+        </is>
+      </c>
+      <c r="L12" s="27" t="inlineStr">
+        <is>
+          <t>1.0.0</t>
+        </is>
+      </c>
+      <c r="M12" s="27" t="inlineStr">
+        <is>
+          <t>before_7</t>
+        </is>
+      </c>
+      <c r="N12" s="27" t="inlineStr">
+        <is>
+          <t>seven_to_eight</t>
+        </is>
+      </c>
+      <c r="O12" s="27" t="inlineStr">
+        <is>
+          <t>after_8</t>
+        </is>
+      </c>
+      <c r="P12" s="27" t="n"/>
+      <c r="Q12" s="27" t="n"/>
+      <c r="R12" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -55324,7 +55424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="10.58203125" customWidth="1" min="1" max="1"/>
@@ -57587,6 +57687,120 @@
       <c r="H62" s="18" t="inlineStr">
         <is>
           <t>관찰 시간 합계</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="18" t="inlineStr">
+        <is>
+          <t>CFG-089</t>
+        </is>
+      </c>
+      <c r="B63" s="18" t="inlineStr">
+        <is>
+          <t>YESTERDAY_DINNER_BOUND</t>
+        </is>
+      </c>
+      <c r="C63" s="18" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="D63" s="18" t="n"/>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="F63" s="18" t="inlineStr">
+        <is>
+          <t>LOCAL_TIME</t>
+        </is>
+      </c>
+      <c r="G63" s="18" t="inlineStr">
+        <is>
+          <t>SOURCE_ATOM</t>
+        </is>
+      </c>
+      <c r="H63" s="18" t="inlineStr">
+        <is>
+          <t>첫 경계</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="18" t="inlineStr">
+        <is>
+          <t>CFG-089</t>
+        </is>
+      </c>
+      <c r="B64" s="18" t="inlineStr">
+        <is>
+          <t>YESTERDAY_DINNER_BOUND</t>
+        </is>
+      </c>
+      <c r="C64" s="18" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="D64" s="18" t="n"/>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="F64" s="18" t="inlineStr">
+        <is>
+          <t>LOCAL_TIME</t>
+        </is>
+      </c>
+      <c r="G64" s="18" t="inlineStr">
+        <is>
+          <t>SOURCE_ATOM</t>
+        </is>
+      </c>
+      <c r="H64" s="18" t="inlineStr">
+        <is>
+          <t>둘째 경계</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="18" t="inlineStr">
+        <is>
+          <t>CFG-089</t>
+        </is>
+      </c>
+      <c r="B65" s="18" t="inlineStr">
+        <is>
+          <t>YESTERDAY_DINNER_END</t>
+        </is>
+      </c>
+      <c r="C65" s="18" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="D65" s="18" t="n"/>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="F65" s="18" t="inlineStr">
+        <is>
+          <t>LOCAL_TIME</t>
+        </is>
+      </c>
+      <c r="G65" s="18" t="inlineStr">
+        <is>
+          <t>SOURCE_ATOM</t>
+        </is>
+      </c>
+      <c r="H65" s="18" t="inlineStr">
+        <is>
+          <t>「8시 이후」 범위 끝</t>
         </is>
       </c>
     </row>
@@ -57605,7 +57819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F86"/>
+  <dimension ref="A1:F87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="10.58203125" customWidth="1" min="1" max="1"/>
@@ -60315,6 +60529,38 @@
         </is>
       </c>
       <c r="F86" s="16" t="inlineStr">
+        <is>
+          <t>maiReport_식이_식사시각질문_v1.0.0.html (2026-10-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="18" t="inlineStr">
+        <is>
+          <t>CFG-089</t>
+        </is>
+      </c>
+      <c r="B87" s="18" t="inlineStr">
+        <is>
+          <t>식사 시각</t>
+        </is>
+      </c>
+      <c r="C87" s="18" t="inlineStr">
+        <is>
+          <t>어제 저녁 고정 경계</t>
+        </is>
+      </c>
+      <c r="D87" s="16" t="inlineStr">
+        <is>
+          <t>19:00 · 20:00 · 끝 22:00</t>
+        </is>
+      </c>
+      <c r="E87" s="18" t="inlineStr">
+        <is>
+          <t>어제 저녁 선택지 「7시 이전 / 7시~8시 / 8시 이후」</t>
+        </is>
+      </c>
+      <c r="F87" s="16" t="inlineStr">
         <is>
           <t>maiReport_식이_식사시각질문_v1.0.0.html (2026-10-14)</t>
         </is>

--- a/files/diet-reference-config-v1.0.0.xlsx
+++ b/files/diet-reference-config-v1.0.0.xlsx
@@ -3052,7 +3052,7 @@
       </c>
       <c r="C56" s="26" t="inlineStr">
         <is>
-          <t>축정의 9행 선택지를 「1시간 이내 / 1~2시간 전 / 그보다 전」으로, 11행 어제 저녁(DIET-Q-10) 추가, 설정값 CFG-089</t>
+          <t>축정의 9행 선택지를 「1시간 전 / 2시간 전 / 그보다 전」으로, 11행 어제 저녁(DIET-Q-10) 추가, 설정값 CFG-089</t>
         </is>
       </c>
       <c r="D56" s="26" t="inlineStr">
@@ -55196,12 +55196,12 @@
       </c>
       <c r="E10" s="27" t="inlineStr">
         <is>
-          <t>1시간 이내 (작은 글씨 {t0} 이후)</t>
+          <t>1시간 전 (작은 글씨 {t0} 이후)</t>
         </is>
       </c>
       <c r="F10" s="27" t="inlineStr">
         <is>
-          <t>1~2시간 전 (작은 글씨 {t1}~{t0})</t>
+          <t>2시간 전 (작은 글씨 {t1}~{t0})</t>
         </is>
       </c>
       <c r="G10" s="27" t="inlineStr">

--- a/files/diet-reference-config-v1.0.0.xlsx
+++ b/files/diet-reference-config-v1.0.0.xlsx
@@ -2167,7 +2167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:D57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="60.58203125" customWidth="1" min="1" max="4"/>
@@ -3056,6 +3056,28 @@
         </is>
       </c>
       <c r="D56" s="26" t="inlineStr">
+        <is>
+          <t>축정의 · 설정값 · 설정파라미터</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="26" t="inlineStr">
+        <is>
+          <t>저녁 선택지 (10-14)</t>
+        </is>
+      </c>
+      <c r="B57" s="26" t="inlineStr">
+        <is>
+          <t>저녁 9시 뒤 · 이른 저녁이 선택지에 안 들어갔음</t>
+        </is>
+      </c>
+      <c r="C57" s="26" t="inlineStr">
+        <is>
+          <t>축정의 12행 저녁 9시 뒤 고정 선택지(DIET-Q-11) 추가, 11행 어제 저녁 선택지를 「7시 이전 / 7시~9시 / 9시 이후」로, 설정값 CFG-077 · 089 · 090</t>
+        </is>
+      </c>
+      <c r="D57" s="26" t="inlineStr">
         <is>
           <t>축정의 · 설정값 · 설정파라미터</t>
         </is>
@@ -54399,7 +54421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R12"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="10.58203125" customWidth="1" min="1" max="1"/>
@@ -55196,22 +55218,22 @@
       </c>
       <c r="E10" s="27" t="inlineStr">
         <is>
-          <t>1시간 전 (작은 글씨 {t0} 이후)</t>
+          <t>1시간 전</t>
         </is>
       </c>
       <c r="F10" s="27" t="inlineStr">
         <is>
-          <t>2시간 전 (작은 글씨 {t1}~{t0})</t>
+          <t>2시간 전</t>
         </is>
       </c>
       <c r="G10" s="27" t="inlineStr">
         <is>
-          <t>그보다 전 (작은 글씨 {t1} 이전)</t>
+          <t>그보다 전</t>
         </is>
       </c>
       <c r="H10" s="27" t="inlineStr">
         <is>
-          <t>오늘 점심 · 오늘 저녁. 고정 질문에 「충분히 먹음 · 적게 · 몇 입만」으로 답한 바로 뒤. 「못 먹거나 거름」 · 건강 앱 식사 기록이 있으면 묻지 않음</t>
+          <t>오늘 점심 · 오늘 저녁(오후 9시까지 답할 때). 고정 질문에 「충분히 먹음 · 적게 · 몇 입만」으로 답한 바로 뒤. 「못 먹거나 거름」 · 건강 앱 식사 기록이 있으면 묻지 않음</t>
         </is>
       </c>
       <c r="I10" s="27" t="inlineStr">
@@ -55221,7 +55243,7 @@
       </c>
       <c r="J10" s="28" t="inlineStr">
         <is>
-          <t>버튼은 답한 시각(10분 내림)에서 1시간씩 거꾸로. 점심 14시 · 저녁 21시를 넘으면 멈춤. 점수 · 등급 없음. 회전 후보 아님</t>
+          <t>시각 구간은 답한 시각(10분 내림)에서 1시간씩 거꾸로(저장용). 점심은 오후 2시가 지나면 2시에 답한 것과 같은 선택지. 하한 점심 12시 · 저녁 4시. 점수 · 등급 없음</t>
         </is>
       </c>
       <c r="K10" s="27" t="inlineStr">
@@ -55357,12 +55379,12 @@
       </c>
       <c r="F12" s="27" t="inlineStr">
         <is>
-          <t>7시~8시</t>
+          <t>7시~9시</t>
         </is>
       </c>
       <c r="G12" s="27" t="inlineStr">
         <is>
-          <t>8시 이후</t>
+          <t>9시 이후</t>
         </is>
       </c>
       <c r="H12" s="27" t="inlineStr">
@@ -55377,7 +55399,7 @@
       </c>
       <c r="J12" s="28" t="inlineStr">
         <is>
-          <t>저녁 7시 · 8시 정각 고정. 점수 · 등급 없음. 회전 후보 아님</t>
+          <t>저녁 7시 · 9시 정각 고정(범위 17~19 · 19~21 · 21~23시). 점수 · 등급 없음</t>
         </is>
       </c>
       <c r="K12" s="27" t="inlineStr">
@@ -55397,17 +55419,95 @@
       </c>
       <c r="N12" s="27" t="inlineStr">
         <is>
-          <t>seven_to_eight</t>
+          <t>seven_to_nine</t>
         </is>
       </c>
       <c r="O12" s="27" t="inlineStr">
         <is>
-          <t>after_8</t>
+          <t>after_9</t>
         </is>
       </c>
       <c r="P12" s="27" t="n"/>
       <c r="Q12" s="27" t="n"/>
       <c r="R12" s="27" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="27" t="inlineStr">
+        <is>
+          <t>식사 시각 단계 (축 아님 · 이어 묻기)</t>
+        </is>
+      </c>
+      <c r="C13" s="28" t="inlineStr">
+        <is>
+          <t>저녁을 먹은 시각의 대략 범위(오후 9시 뒤에 답할 때)</t>
+        </is>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>저녁은 몇 시쯤 드셨어요?</t>
+        </is>
+      </c>
+      <c r="E13" s="27" t="inlineStr">
+        <is>
+          <t>7시 이전</t>
+        </is>
+      </c>
+      <c r="F13" s="27" t="inlineStr">
+        <is>
+          <t>7시~9시</t>
+        </is>
+      </c>
+      <c r="G13" s="27" t="inlineStr">
+        <is>
+          <t>9시 이후</t>
+        </is>
+      </c>
+      <c r="H13" s="27" t="inlineStr">
+        <is>
+          <t>오늘 저녁을 오후 9시가 지나서 답할 때. 조건은 위와 같음</t>
+        </is>
+      </c>
+      <c r="I13" s="27" t="inlineStr">
+        <is>
+          <t>자기돌봄 · 일상안정의 식후 행동 판정 입력</t>
+        </is>
+      </c>
+      <c r="J13" s="28" t="inlineStr">
+        <is>
+          <t>1시간 칸 3개로는 5시 · 10시 식사를 다 덮을 수 없어 늦게 답한 날은 2시간 칸. 어제 저녁과 같은 선택지</t>
+        </is>
+      </c>
+      <c r="K13" s="27" t="inlineStr">
+        <is>
+          <t>DIET-Q-11</t>
+        </is>
+      </c>
+      <c r="L13" s="27" t="inlineStr">
+        <is>
+          <t>1.0.0</t>
+        </is>
+      </c>
+      <c r="M13" s="27" t="inlineStr">
+        <is>
+          <t>before_7</t>
+        </is>
+      </c>
+      <c r="N13" s="27" t="inlineStr">
+        <is>
+          <t>seven_to_nine</t>
+        </is>
+      </c>
+      <c r="O13" s="27" t="inlineStr">
+        <is>
+          <t>after_9</t>
+        </is>
+      </c>
+      <c r="P13" s="27" t="n"/>
+      <c r="Q13" s="27" t="n"/>
+      <c r="R13" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -55424,7 +55524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="10.58203125" customWidth="1" min="1" max="1"/>
@@ -57163,7 +57263,7 @@
       <c r="D48" s="18" t="n"/>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="F48" s="18" t="inlineStr">
@@ -57698,7 +57798,7 @@
       </c>
       <c r="B63" s="18" t="inlineStr">
         <is>
-          <t>YESTERDAY_DINNER_BOUND</t>
+          <t>DINNER_FIXED_BOUND</t>
         </is>
       </c>
       <c r="C63" s="18" t="inlineStr">
@@ -57736,7 +57836,7 @@
       </c>
       <c r="B64" s="18" t="inlineStr">
         <is>
-          <t>YESTERDAY_DINNER_BOUND</t>
+          <t>DINNER_FIXED_BOUND</t>
         </is>
       </c>
       <c r="C64" s="18" t="inlineStr">
@@ -57747,7 +57847,7 @@
       <c r="D64" s="18" t="n"/>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="F64" s="18" t="inlineStr">
@@ -57774,7 +57874,7 @@
       </c>
       <c r="B65" s="18" t="inlineStr">
         <is>
-          <t>YESTERDAY_DINNER_END</t>
+          <t>DINNER_FIXED_END</t>
         </is>
       </c>
       <c r="C65" s="18" t="inlineStr">
@@ -57785,7 +57885,7 @@
       <c r="D65" s="18" t="n"/>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="F65" s="18" t="inlineStr">
@@ -57801,6 +57901,82 @@
       <c r="H65" s="18" t="inlineStr">
         <is>
           <t>「8시 이후」 범위 끝</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="18" t="inlineStr">
+        <is>
+          <t>CFG-090</t>
+        </is>
+      </c>
+      <c r="B66" s="18" t="inlineStr">
+        <is>
+          <t>MEAL_TIME_FLOOR</t>
+        </is>
+      </c>
+      <c r="C66" s="18" t="inlineStr">
+        <is>
+          <t>GTE</t>
+        </is>
+      </c>
+      <c r="D66" s="18" t="n"/>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F66" s="18" t="inlineStr">
+        <is>
+          <t>LOCAL_TIME</t>
+        </is>
+      </c>
+      <c r="G66" s="18" t="inlineStr">
+        <is>
+          <t>SOURCE_ATOM</t>
+        </is>
+      </c>
+      <c r="H66" s="18" t="inlineStr">
+        <is>
+          <t>DINNER 선택지 하한</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="18" t="inlineStr">
+        <is>
+          <t>CFG-090</t>
+        </is>
+      </c>
+      <c r="B67" s="18" t="inlineStr">
+        <is>
+          <t>MEAL_TIME_FLOOR</t>
+        </is>
+      </c>
+      <c r="C67" s="18" t="inlineStr">
+        <is>
+          <t>GTE</t>
+        </is>
+      </c>
+      <c r="D67" s="18" t="n"/>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F67" s="18" t="inlineStr">
+        <is>
+          <t>LOCAL_TIME</t>
+        </is>
+      </c>
+      <c r="G67" s="18" t="inlineStr">
+        <is>
+          <t>SOURCE_ATOM</t>
+        </is>
+      </c>
+      <c r="H67" s="18" t="inlineStr">
+        <is>
+          <t>LUNCH 선택지 하한</t>
         </is>
       </c>
     </row>
@@ -57819,7 +57995,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F87"/>
+  <dimension ref="A1:F88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="10.58203125" customWidth="1" min="1" max="1"/>
@@ -60168,7 +60344,7 @@
       </c>
       <c r="D75" s="16" t="inlineStr">
         <is>
-          <t>아침 06:00 · 점심 11:00 · 저녁 17:00</t>
+          <t>아침 06:00 · 점심 11:00 · 저녁 16:00</t>
         </is>
       </c>
       <c r="E75" s="18" t="inlineStr">
@@ -60547,20 +60723,52 @@
       </c>
       <c r="C87" s="18" t="inlineStr">
         <is>
-          <t>어제 저녁 고정 경계</t>
+          <t>저녁 고정 선택지 경계</t>
         </is>
       </c>
       <c r="D87" s="16" t="inlineStr">
         <is>
-          <t>19:00 · 20:00 · 끝 22:00</t>
+          <t>19:00 · 21:00 · 끝 23:00</t>
         </is>
       </c>
       <c r="E87" s="18" t="inlineStr">
         <is>
-          <t>어제 저녁 선택지 「7시 이전 / 7시~8시 / 8시 이후」</t>
+          <t>저녁 9시 뒤 · 어제 저녁 선택지 「7시 이전 / 7시~9시 / 9시 이후」</t>
         </is>
       </c>
       <c r="F87" s="16" t="inlineStr">
+        <is>
+          <t>maiReport_식이_식사시각질문_v1.0.0.html (2026-10-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="18" t="inlineStr">
+        <is>
+          <t>CFG-090</t>
+        </is>
+      </c>
+      <c r="B88" s="18" t="inlineStr">
+        <is>
+          <t>식사 시각</t>
+        </is>
+      </c>
+      <c r="C88" s="18" t="inlineStr">
+        <is>
+          <t>선택지 하한 시각 · 저녁</t>
+        </is>
+      </c>
+      <c r="D88" s="16" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E88" s="18" t="inlineStr">
+        <is>
+          <t>저녁 선택지 구간이 4시 아래로 내려가지 않음(점심은 12시)</t>
+        </is>
+      </c>
+      <c r="F88" s="16" t="inlineStr">
         <is>
           <t>maiReport_식이_식사시각질문_v1.0.0.html (2026-10-14)</t>
         </is>

--- a/files/diet-reference-config-v1.0.0.xlsx
+++ b/files/diet-reference-config-v1.0.0.xlsx
@@ -55524,7 +55524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H67"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="10.58203125" customWidth="1" min="1" max="1"/>
@@ -57977,6 +57977,44 @@
       <c r="H67" s="18" t="inlineStr">
         <is>
           <t>LUNCH 선택지 하한</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="18" t="inlineStr">
+        <is>
+          <t>CFG-078</t>
+        </is>
+      </c>
+      <c r="B68" s="18" t="inlineStr">
+        <is>
+          <t>BREAKFAST_END</t>
+        </is>
+      </c>
+      <c r="C68" s="18" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="D68" s="18" t="n"/>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F68" s="18" t="inlineStr">
+        <is>
+          <t>LOCAL_TIME</t>
+        </is>
+      </c>
+      <c r="G68" s="18" t="inlineStr">
+        <is>
+          <t>SOURCE_ATOM</t>
+        </is>
+      </c>
+      <c r="H68" s="18" t="inlineStr">
+        <is>
+          <t>「8시 이후」 범위 끝(아침 끝 기본값)</t>
         </is>
       </c>
     </row>
@@ -60376,12 +60414,12 @@
       </c>
       <c r="D76" s="16" t="inlineStr">
         <is>
-          <t>07:00 · 08:00</t>
+          <t>07:00 · 08:00 · 끝 10:00</t>
         </is>
       </c>
       <c r="E76" s="18" t="inlineStr">
         <is>
-          <t>아침 버튼 「7시 이전 / 7시~8시 / 8시 이후」</t>
+          <t>아침 선택지 「7시 이전 / 7시~8시 / 8시 이후」. 「8시 이후」는 10:00까지</t>
         </is>
       </c>
       <c r="F76" s="16" t="inlineStr">

--- a/files/diet-reference-config-v1.0.0.xlsx
+++ b/files/diet-reference-config-v1.0.0.xlsx
@@ -3052,7 +3052,7 @@
       </c>
       <c r="C56" s="26" t="inlineStr">
         <is>
-          <t>축정의 9행 선택지를 「1시간 전 / 2시간 전 / 그보다 전」으로, 11행 어제 저녁(DIET-Q-10) 추가, 설정값 CFG-089</t>
+          <t>축정의 9행 선택지를 「1시간 이내 / 2시간 전 / 그보다 전」으로, 11행 어제 저녁(DIET-Q-10) 추가, 설정값 CFG-089</t>
         </is>
       </c>
       <c r="D56" s="26" t="inlineStr">
@@ -55218,7 +55218,7 @@
       </c>
       <c r="E10" s="27" t="inlineStr">
         <is>
-          <t>1시간 전</t>
+          <t>1시간 이내</t>
         </is>
       </c>
       <c r="F10" s="27" t="inlineStr">

--- a/files/diet-reference-config-v1.0.0.xlsx
+++ b/files/diet-reference-config-v1.0.0.xlsx
@@ -3052,7 +3052,7 @@
       </c>
       <c r="C56" s="26" t="inlineStr">
         <is>
-          <t>축정의 9행 선택지를 「1시간 이내 / 2시간 전 / 그보다 전」으로, 11행 어제 저녁(DIET-Q-10) 추가, 설정값 CFG-089</t>
+          <t>축정의 9행 선택지를 「1시간 이내 / 1~2시간 전 / 그보다 전」으로, 11행 어제 저녁(DIET-Q-10) 추가, 설정값 CFG-089</t>
         </is>
       </c>
       <c r="D56" s="26" t="inlineStr">
@@ -55223,7 +55223,7 @@
       </c>
       <c r="F10" s="27" t="inlineStr">
         <is>
-          <t>2시간 전</t>
+          <t>1~2시간 전</t>
         </is>
       </c>
       <c r="G10" s="27" t="inlineStr">

--- a/files/diet-reference-config-v1.0.0.xlsx
+++ b/files/diet-reference-config-v1.0.0.xlsx
@@ -55524,7 +55524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="10.58203125" customWidth="1" min="1" max="1"/>
@@ -57462,7 +57462,7 @@
       </c>
       <c r="H53" s="18" t="inlineStr">
         <is>
-          <t>넘으면 걸음 단서 없을 때 UNKNOWN</t>
+          <t>「…이후」 칸은 끼니 끝 기본값(CFG-091)까지로 보므로 보통 넘지 않음. 넘으면 2시간까지만 봄</t>
         </is>
       </c>
     </row>
@@ -58015,6 +58015,120 @@
       <c r="H68" s="18" t="inlineStr">
         <is>
           <t>「8시 이후」 범위 끝(아침 끝 기본값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="18" t="inlineStr">
+        <is>
+          <t>CFG-091</t>
+        </is>
+      </c>
+      <c r="B69" s="18" t="inlineStr">
+        <is>
+          <t>MEAL_END_DEFAULT</t>
+        </is>
+      </c>
+      <c r="C69" s="18" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="D69" s="18" t="n"/>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F69" s="18" t="inlineStr">
+        <is>
+          <t>LOCAL_TIME</t>
+        </is>
+      </c>
+      <c r="G69" s="18" t="inlineStr">
+        <is>
+          <t>SOURCE_ATOM</t>
+        </is>
+      </c>
+      <c r="H69" s="18" t="inlineStr">
+        <is>
+          <t>BREAKFAST</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="18" t="inlineStr">
+        <is>
+          <t>CFG-091</t>
+        </is>
+      </c>
+      <c r="B70" s="18" t="inlineStr">
+        <is>
+          <t>MEAL_END_DEFAULT</t>
+        </is>
+      </c>
+      <c r="C70" s="18" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="D70" s="18" t="n"/>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="F70" s="18" t="inlineStr">
+        <is>
+          <t>LOCAL_TIME</t>
+        </is>
+      </c>
+      <c r="G70" s="18" t="inlineStr">
+        <is>
+          <t>SOURCE_ATOM</t>
+        </is>
+      </c>
+      <c r="H70" s="18" t="inlineStr">
+        <is>
+          <t>LUNCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="18" t="inlineStr">
+        <is>
+          <t>CFG-091</t>
+        </is>
+      </c>
+      <c r="B71" s="18" t="inlineStr">
+        <is>
+          <t>MEAL_END_DEFAULT</t>
+        </is>
+      </c>
+      <c r="C71" s="18" t="inlineStr">
+        <is>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="D71" s="18" t="n"/>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="F71" s="18" t="inlineStr">
+        <is>
+          <t>LOCAL_TIME</t>
+        </is>
+      </c>
+      <c r="G71" s="18" t="inlineStr">
+        <is>
+          <t>SOURCE_ATOM</t>
+        </is>
+      </c>
+      <c r="H71" s="18" t="inlineStr">
+        <is>
+          <t>DINNER</t>
         </is>
       </c>
     </row>
@@ -58033,7 +58147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F88"/>
+  <dimension ref="A1:F89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="10.58203125" customWidth="1" min="1" max="1"/>
@@ -60515,7 +60629,7 @@
       </c>
       <c r="E79" s="18" t="inlineStr">
         <is>
-          <t>범위가 이보다 넓거나 비어 있으면 걸음 단서가 없을 때 모름</t>
+          <t>「…이후」 칸은 끼니 끝 기본값(CFG-091)까지로 봄. 비어 있으면 모름</t>
         </is>
       </c>
       <c r="F79" s="16" t="inlineStr">
@@ -60807,6 +60921,38 @@
         </is>
       </c>
       <c r="F88" s="16" t="inlineStr">
+        <is>
+          <t>maiReport_식이_식사시각질문_v1.0.0.html (2026-10-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="18" t="inlineStr">
+        <is>
+          <t>CFG-091</t>
+        </is>
+      </c>
+      <c r="B89" s="18" t="inlineStr">
+        <is>
+          <t>식사 시각</t>
+        </is>
+      </c>
+      <c r="C89" s="18" t="inlineStr">
+        <is>
+          <t>끼니 끝 기본값</t>
+        </is>
+      </c>
+      <c r="D89" s="16" t="inlineStr">
+        <is>
+          <t>아침 10:00 · 점심 14:00 · 저녁 23:00</t>
+        </is>
+      </c>
+      <c r="E89" s="18" t="inlineStr">
+        <is>
+          <t>끝이 없는 「…이후」 칸의 범위 끝</t>
+        </is>
+      </c>
+      <c r="F89" s="16" t="inlineStr">
         <is>
           <t>maiReport_식이_식사시각질문_v1.0.0.html (2026-10-14)</t>
         </is>

--- a/files/diet-reference-config-v1.0.0.xlsx
+++ b/files/diet-reference-config-v1.0.0.xlsx
@@ -2167,7 +2167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:D58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="60.58203125" customWidth="1" min="1" max="4"/>
@@ -3080,6 +3080,28 @@
       <c r="D57" s="26" t="inlineStr">
         <is>
           <t>축정의 · 설정값 · 설정파라미터</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="26" t="inlineStr">
+        <is>
+          <t>식사 시각 추정 단순화 (10-14)</t>
+        </is>
+      </c>
+      <c r="B58" s="26" t="inlineStr">
+        <is>
+          <t>추정 순서에 걸음 멈춤 단서(CFG-079)와 지난 2주 평소 시각(CFG-080)이 있었음</t>
+        </is>
+      </c>
+      <c r="C58" s="26" t="inlineStr">
+        <is>
+          <t>둘 다 1차에서 뺌. 추정은 건강 앱 식사 기록 → 선택지 범위의 가운데 두 단계. 건강 앱 기록은 끼니 구분이 없고 선택지 추정값은 가운데값이라 평소 시각이 믿을 만하지 않음. 식후 걸음 판정 결과(모의 87~89%)는 그대로</t>
+        </is>
+      </c>
+      <c r="D58" s="26" t="inlineStr">
+        <is>
+          <t>구현기준 R-11 ⑤ · 검증규칙 V-57 · 설정 CFG-079 · 080 사용 안 함 · 필드정의 diet_meal_time</t>
         </is>
       </c>
     </row>
@@ -57390,7 +57412,7 @@
       </c>
       <c r="H51" s="18" t="inlineStr">
         <is>
-          <t>걸음 멈춤 단서</t>
+          <t>사용 안 함(1차)</t>
         </is>
       </c>
     </row>
@@ -57426,7 +57448,7 @@
       </c>
       <c r="H52" s="18" t="inlineStr">
         <is>
-          <t>평소 식사 시각</t>
+          <t>사용 안 함(1차)</t>
         </is>
       </c>
     </row>
@@ -60560,12 +60582,12 @@
       </c>
       <c r="D77" s="16" t="inlineStr">
         <is>
-          <t>15분</t>
+          <t>사용 안 함</t>
         </is>
       </c>
       <c r="E77" s="18" t="inlineStr">
         <is>
-          <t>범위 안에서 걷다가 15분 넘게 멈춘 곳이 하나뿐이면 그 시각(확신 높음). 임시값</t>
+          <t>1차에서 쓰지 않음. 건강 앱 식사 기록은 끼니 구분이 없고 선택지 추정값은 가운데값이라 걸음 멈춤 단서으로 믿을 만한 시각이 나오지 않음. 추정은 건강 앱 기록 → 선택지 범위의 가운데 두 단계</t>
         </is>
       </c>
       <c r="F77" s="16" t="inlineStr">
@@ -60592,12 +60614,12 @@
       </c>
       <c r="D78" s="16" t="inlineStr">
         <is>
-          <t>14일</t>
+          <t>사용 안 함</t>
         </is>
       </c>
       <c r="E78" s="18" t="inlineStr">
         <is>
-          <t>지난 14일 같은 끼니의 추정 시각 중앙값. 임시값</t>
+          <t>1차에서 쓰지 않음. 건강 앱 식사 기록은 끼니 구분이 없고 선택지 추정값은 가운데값이라 평소 식사 시각으로 믿을 만한 시각이 나오지 않음. 추정은 건강 앱 기록 → 선택지 범위의 가운데 두 단계</t>
         </is>
       </c>
       <c r="F78" s="16" t="inlineStr">

--- a/files/diet-reference-config-v1.0.0.xlsx
+++ b/files/diet-reference-config-v1.0.0.xlsx
@@ -60459,7 +60459,7 @@
       </c>
       <c r="E73" s="18" t="inlineStr">
         <is>
-          <t>14시를 넘으면 「오후 1:00 이후 / 12:00~1:00 / 12:00 이전」</t>
+          <t>14시를 넘으면 「오후 1시 이후 / 12시~1시 사이 / 12시 이전」</t>
         </is>
       </c>
       <c r="F73" s="16" t="inlineStr">

--- a/files/diet-reference-config-v1.0.0.xlsx
+++ b/files/diet-reference-config-v1.0.0.xlsx
@@ -60459,7 +60459,7 @@
       </c>
       <c r="E73" s="18" t="inlineStr">
         <is>
-          <t>14시를 넘으면 「오후 1시 이후 / 12시~1시 사이 / 12시 이전」</t>
+          <t>14시를 넘으면 「1시 이후 / 12시~1시 사이 / 12시 이전」</t>
         </is>
       </c>
       <c r="F73" s="16" t="inlineStr">

--- a/files/diet-reference-config-v1.0.0.xlsx
+++ b/files/diet-reference-config-v1.0.0.xlsx
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>오늘도 어제와 비슷한 시간에 아침·점심·저녁 세 끼를 드세요.</t>
+          <t>오늘도 아침·점심·저녁 세 끼를 제때 드세요.</t>
         </is>
       </c>
       <c r="D25" s="4" t="n"/>
@@ -22560,20 +22560,20 @@
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>세 끼 어제처럼 먹기</t>
+          <t>세 끼 제때 먹기</t>
         </is>
       </c>
       <c r="H5" s="8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>오늘도 어제와 비슷한 시간에 아침·점심·저녁 세 끼를 드세요.</t>
+          <t>오늘도 아침·점심·저녁 세 끼를 제때 드세요.</t>
         </is>
       </c>
       <c r="J5" s="14" t="inlineStr">
         <is>
-          <t>식사 시각을 일정하게 계획해 보는 행동이에요.</t>
+          <t>세 끼를 제때 먹도록 계획해 보는 행동이에요.</t>
         </is>
       </c>
       <c r="K5" s="13" t="n"/>
@@ -22586,7 +22586,7 @@
       </c>
       <c r="O5" s="14" t="inlineStr">
         <is>
-          <t>근거 범위에 맞춰 이유 문장 수정</t>
+          <t>근거 범위에 맞춰 이유 문장 수정 · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P5" s="13" t="inlineStr">
@@ -24292,11 +24292,11 @@
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>다음 끼니는 챙기기</t>
+          <t>다음 끼니 잘 챙기기</t>
         </is>
       </c>
       <c r="H27" s="8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
@@ -24326,7 +24326,7 @@
       </c>
       <c r="O27" s="14" t="inlineStr">
         <is>
-          <t>행동 문구 수정; 근거 범위에 맞춰 이유 문장 수정</t>
+          <t>행동 문구 수정; 근거 범위에 맞춰 이유 문장 수정 · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P27" s="13" t="inlineStr">
@@ -25764,20 +25764,20 @@
       </c>
       <c r="G45" s="13" t="inlineStr">
         <is>
-          <t>라면 국물은 남기기</t>
+          <t>국물 음식은 국물 남기기</t>
         </is>
       </c>
       <c r="H45" s="13" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I45" s="14" t="inlineStr">
         <is>
-          <t>라면을 먹을 때 면과 건더기만 먹고 국물은 남기세요.</t>
+          <t>국이나 면 같은 국물 음식은 건더기만 먹고 국물은 남기세요.</t>
         </is>
       </c>
       <c r="J45" s="14" t="inlineStr">
         <is>
-          <t>라면 국물을 남겨 국물 섭취를 줄여요.</t>
+          <t>국물을 남겨 국물 섭취를 줄여요.</t>
         </is>
       </c>
       <c r="K45" s="13" t="inlineStr">
@@ -25798,7 +25798,7 @@
       </c>
       <c r="O45" s="14" t="inlineStr">
         <is>
-          <t>근거 범위에 맞춰 이유 문장 수정</t>
+          <t>근거 범위에 맞춰 이유 문장 수정 · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P45" s="13" t="inlineStr">
@@ -25928,20 +25928,20 @@
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>김치는 먹을 만큼만</t>
+          <t>절임 반찬은 먹을 만큼만</t>
         </is>
       </c>
       <c r="H47" s="8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>김치는 먹을 만큼만 조금 덜어서 드세요.</t>
+          <t>김치·장아찌 같은 절임 반찬은 먹을 만큼만 조금 덜어서 드세요.</t>
         </is>
       </c>
       <c r="J47" s="14" t="inlineStr">
         <is>
-          <t>김치의 양과 다른 짠 반찬을 함께 살펴봐요.</t>
+          <t>절임 반찬의 양과 다른 짠 반찬을 함께 살펴봐요.</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
@@ -25962,7 +25962,7 @@
       </c>
       <c r="O47" s="14" t="inlineStr">
         <is>
-          <t>행동 문구 수정; 근거 범위에 맞춰 이유 문장 수정</t>
+          <t>행동 문구 수정; 근거 범위에 맞춰 이유 문장 수정 · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P47" s="13" t="inlineStr">
@@ -27004,15 +27004,15 @@
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>라면 대신 국수 · 밥</t>
+          <t>튀긴 면 대신 국수 · 밥</t>
         </is>
       </c>
       <c r="H60" s="8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I60" s="4" t="inlineStr">
         <is>
-          <t>라면이 당길 때 기름에 튀기지 않은 국수나 밥으로 바꿔 드세요.</t>
+          <t>기름에 튀긴 면이 당길 때 튀기지 않은 국수나 밥으로 바꿔 드세요.</t>
         </is>
       </c>
       <c r="J60" s="14" t="inlineStr">
@@ -27034,7 +27034,7 @@
       </c>
       <c r="O60" s="14" t="inlineStr">
         <is>
-          <t>근거 범위에 맞춰 이유 문장 수정</t>
+          <t>근거 범위에 맞춰 이유 문장 수정 · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P60" s="13" t="inlineStr">
@@ -28248,20 +28248,20 @@
       </c>
       <c r="G75" s="8" t="inlineStr">
         <is>
-          <t>김치는 접시에 덜기</t>
+          <t>절임 반찬은 접시에 덜기</t>
         </is>
       </c>
       <c r="H75" s="8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>김치는 통째로 두지 말고 먹을 만큼 앞접시에 덜어 드세요.</t>
+          <t>김치 같은 절임 반찬은 통째로 두지 말고 먹을 만큼 앞접시에 덜어 드세요.</t>
         </is>
       </c>
       <c r="J75" s="14" t="inlineStr">
         <is>
-          <t>김치의 실제 양과 전체 식사의 간을 함께 봐요.</t>
+          <t>절임 반찬의 실제 양과 전체 식사의 간을 함께 봐요.</t>
         </is>
       </c>
       <c r="K75" s="13" t="inlineStr">
@@ -28282,7 +28282,7 @@
       </c>
       <c r="O75" s="14" t="inlineStr">
         <is>
-          <t>행동 문구 수정; 근거 범위에 맞춰 이유 문장 수정</t>
+          <t>행동 문구 수정; 근거 범위에 맞춰 이유 문장 수정 · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P75" s="13" t="inlineStr">
@@ -28332,20 +28332,20 @@
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>저녁 어제처럼 먹기</t>
+          <t>저녁은 제때 먹기</t>
         </is>
       </c>
       <c r="H76" s="8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I76" s="4" t="inlineStr">
         <is>
-          <t>오늘 저녁도 어제와 비슷한 시간에 드세요.</t>
+          <t>오늘 저녁도 제때 드세요.</t>
         </is>
       </c>
       <c r="J76" s="14" t="inlineStr">
         <is>
-          <t>생활 일정에 맞춰 저녁 시각을 계획해요.</t>
+          <t>저녁을 제때 먹도록 계획해요.</t>
         </is>
       </c>
       <c r="K76" s="13" t="inlineStr">
@@ -28362,7 +28362,7 @@
       </c>
       <c r="O76" s="14" t="inlineStr">
         <is>
-          <t>근거 범위에 맞춰 이유 문장 수정</t>
+          <t>근거 범위에 맞춰 이유 문장 수정 · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P76" s="13" t="inlineStr">
@@ -28412,11 +28412,11 @@
       </c>
       <c r="G77" s="13" t="inlineStr">
         <is>
-          <t>한 숟갈 양을 절반으로</t>
+          <t>한 숟갈 양, 절반만</t>
         </is>
       </c>
       <c r="H77" s="13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I77" s="14" t="inlineStr">
         <is>
@@ -28446,7 +28446,7 @@
       </c>
       <c r="O77" s="14" t="inlineStr">
         <is>
-          <t>근거 범위에 맞춰 이유 문장 수정</t>
+          <t>근거 범위에 맞춰 이유 문장 수정 · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P77" s="13" t="inlineStr">
@@ -31308,15 +31308,15 @@
       </c>
       <c r="G112" s="8" t="inlineStr">
         <is>
-          <t>혼자여도 상 차려 먹기</t>
+          <t>대충 때우지 않고 차려 먹기</t>
         </is>
       </c>
       <c r="H112" s="8" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I112" s="4" t="inlineStr">
         <is>
-          <t>혼자 먹더라도 대충 때우지 말고 상을 차려서 드세요.</t>
+          <t>간단히 먹더라도 대충 때우지 말고 상을 차려서 드세요.</t>
         </is>
       </c>
       <c r="J112" s="14" t="inlineStr">
@@ -31338,7 +31338,7 @@
       </c>
       <c r="O112" s="14" t="inlineStr">
         <is>
-          <t>근거 범위에 맞춰 이유 문장 수정</t>
+          <t>근거 범위에 맞춰 이유 문장 수정 · 10-19 혼자·가족·도시락 전제 없이 쓰도록</t>
         </is>
       </c>
       <c r="P112" s="13" t="inlineStr">
@@ -31388,15 +31388,15 @@
       </c>
       <c r="G113" s="8" t="inlineStr">
         <is>
-          <t>혼밥도 그릇에 덜기</t>
+          <t>봉지째 말고 그릇에 덜기</t>
         </is>
       </c>
       <c r="H113" s="8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I113" s="4" t="inlineStr">
         <is>
-          <t>혼자 먹을 때도 봉지째 먹지 말고 그릇에 덜어 드세요.</t>
+          <t>봉지째 먹지 말고 그릇에 덜어 드세요.</t>
         </is>
       </c>
       <c r="J113" s="14" t="inlineStr">
@@ -31422,7 +31422,7 @@
       </c>
       <c r="O113" s="14" t="inlineStr">
         <is>
-          <t>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요</t>
+          <t>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요 · 10-19 혼자·가족·도시락 전제 없이 쓰도록</t>
         </is>
       </c>
       <c r="P113" s="13" t="inlineStr">
@@ -31472,20 +31472,20 @@
       </c>
       <c r="G114" s="13" t="inlineStr">
         <is>
-          <t>혼밥에도 채소 한 가지</t>
+          <t>간단히 먹어도 채소 하나</t>
         </is>
       </c>
       <c r="H114" s="13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I114" s="14" t="inlineStr">
         <is>
-          <t>혼자 먹을 때도 채소 반찬을 한 가지 곁들여 드세요.</t>
+          <t>간단히 먹을 때도 채소 반찬을 한 가지 곁들여 드세요.</t>
         </is>
       </c>
       <c r="J114" s="14" t="inlineStr">
         <is>
-          <t>혼자 먹을 때도 채소 반찬을 준비해 봐요.</t>
+          <t>간단한 식사에도 채소 반찬을 준비해 봐요.</t>
         </is>
       </c>
       <c r="K114" s="13" t="inlineStr">
@@ -31506,7 +31506,7 @@
       </c>
       <c r="O114" s="14" t="inlineStr">
         <is>
-          <t>근거 범위에 맞춰 이유 문장 수정</t>
+          <t>근거 범위에 맞춰 이유 문장 수정 · 10-19 혼자·가족·도시락 전제 없이 쓰도록</t>
         </is>
       </c>
       <c r="P114" s="13" t="inlineStr">
@@ -31556,15 +31556,15 @@
       </c>
       <c r="G115" s="8" t="inlineStr">
         <is>
-          <t>혼밥에도 단백질 챙기기</t>
+          <t>간단히 먹어도 단백질</t>
         </is>
       </c>
       <c r="H115" s="8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I115" s="4" t="inlineStr">
         <is>
-          <t>혼자 간단히 먹을 때도 달걀·두부 같은 단백질 식품을 곁들이세요.</t>
+          <t>간단히 먹을 때도 달걀·두부 같은 단백질 식품을 곁들이세요.</t>
         </is>
       </c>
       <c r="J115" s="14" t="inlineStr">
@@ -31590,7 +31590,7 @@
       </c>
       <c r="O115" s="14" t="inlineStr">
         <is>
-          <t>근거 범위에 맞춰 이유 문장 수정</t>
+          <t>근거 범위에 맞춰 이유 문장 수정 · 10-19 혼자·가족·도시락 전제 없이 쓰도록</t>
         </is>
       </c>
       <c r="P115" s="13" t="inlineStr">
@@ -31640,7 +31640,7 @@
       </c>
       <c r="G116" s="13" t="inlineStr">
         <is>
-          <t>도시락에 채소 한 칸</t>
+          <t>채소 반찬 미리 담기</t>
         </is>
       </c>
       <c r="H116" s="13" t="n">
@@ -31648,7 +31648,7 @@
       </c>
       <c r="I116" s="14" t="inlineStr">
         <is>
-          <t>도시락을 쌀 때 한 칸은 채소 반찬으로 채우세요.</t>
+          <t>내일 먹을 채소 반찬을 미리 한 칸 담아 두세요.</t>
         </is>
       </c>
       <c r="J116" s="14" t="inlineStr">
@@ -31674,7 +31674,7 @@
       </c>
       <c r="O116" s="14" t="inlineStr">
         <is>
-          <t>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요</t>
+          <t>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요 · 10-19 혼자·가족·도시락 전제 없이 쓰도록</t>
         </is>
       </c>
       <c r="P116" s="13" t="inlineStr">
@@ -31724,15 +31724,15 @@
       </c>
       <c r="G117" s="13" t="inlineStr">
         <is>
-          <t>도시락에 달걀 하나</t>
+          <t>달걀 반찬 하나 챙기기</t>
         </is>
       </c>
       <c r="H117" s="13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I117" s="14" t="inlineStr">
         <is>
-          <t>도시락에 달걀 반찬을 하나 넣어 가세요.</t>
+          <t>달걀 반찬을 하나 챙겨 드세요.</t>
         </is>
       </c>
       <c r="J117" s="14" t="inlineStr">
@@ -31758,7 +31758,7 @@
       </c>
       <c r="O117" s="14" t="inlineStr">
         <is>
-          <t>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요</t>
+          <t>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요 · 10-19 혼자·가족·도시락 전제 없이 쓰도록</t>
         </is>
       </c>
       <c r="P117" s="13" t="inlineStr">
@@ -31808,15 +31808,15 @@
       </c>
       <c r="G118" s="13" t="inlineStr">
         <is>
-          <t>도시락 국물은 빼기</t>
+          <t>국물 반찬은 빼고 담기</t>
         </is>
       </c>
       <c r="H118" s="13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I118" s="14" t="inlineStr">
         <is>
-          <t>도시락을 쌀 때 국이나 국물 반찬은 빼고 싸세요.</t>
+          <t>반찬을 담을 때 국이나 국물 반찬은 빼고 담으세요.</t>
         </is>
       </c>
       <c r="J118" s="14" t="inlineStr">
@@ -31842,7 +31842,7 @@
       </c>
       <c r="O118" s="14" t="inlineStr">
         <is>
-          <t>근거 범위에 맞춰 이유 문장 수정</t>
+          <t>근거 범위에 맞춰 이유 문장 수정 · 10-19 혼자·가족·도시락 전제 없이 쓰도록</t>
         </is>
       </c>
       <c r="P118" s="13" t="inlineStr">
@@ -31892,20 +31892,20 @@
       </c>
       <c r="G119" s="13" t="inlineStr">
         <is>
-          <t>도시락 반찬은 구이로</t>
+          <t>반찬은 튀김 대신 구이로</t>
         </is>
       </c>
       <c r="H119" s="13" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I119" s="14" t="inlineStr">
         <is>
-          <t>도시락 반찬은 튀김 대신 구이로 만들어 담으세요.</t>
+          <t>반찬은 튀김 대신 구이로 만들어 드세요.</t>
         </is>
       </c>
       <c r="J119" s="14" t="inlineStr">
         <is>
-          <t>도시락 반찬의 조리법을 바꿔 보는 행동이에요.</t>
+          <t>반찬의 조리법을 바꿔 보는 행동이에요.</t>
         </is>
       </c>
       <c r="K119" s="13" t="inlineStr">
@@ -31926,7 +31926,7 @@
       </c>
       <c r="O119" s="14" t="inlineStr">
         <is>
-          <t>근거 범위에 맞춰 이유 문장 수정</t>
+          <t>근거 범위에 맞춰 이유 문장 수정 · 10-19 혼자·가족·도시락 전제 없이 쓰도록</t>
         </is>
       </c>
       <c r="P119" s="13" t="inlineStr">
@@ -31976,20 +31976,20 @@
       </c>
       <c r="G120" s="8" t="inlineStr">
         <is>
-          <t>가족 반찬에 채소 하나</t>
+          <t>상 차릴 때 채소 하나 더</t>
         </is>
       </c>
       <c r="H120" s="8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I120" s="4" t="inlineStr">
         <is>
-          <t>가족과 함께 먹는 상에 채소 반찬을 한 가지 더 올려 보세요.</t>
+          <t>상을 차릴 때 채소 반찬을 한 가지 더 올려 보세요.</t>
         </is>
       </c>
       <c r="J120" s="14" t="inlineStr">
         <is>
-          <t>함께 먹는 반찬이 늘면 나도 늘어요.</t>
+          <t>상에 오르는 채소가 늘면 먹는 채소도 늘어요.</t>
         </is>
       </c>
       <c r="K120" s="13" t="inlineStr">
@@ -32010,7 +32010,7 @@
       </c>
       <c r="O120" s="14" t="inlineStr">
         <is>
-          <t>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요</t>
+          <t>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요 · 10-19 혼자·가족·도시락 전제 없이 쓰도록</t>
         </is>
       </c>
       <c r="P120" s="13" t="inlineStr">
@@ -32060,7 +32060,7 @@
       </c>
       <c r="G121" s="13" t="inlineStr">
         <is>
-          <t>국은 각자 그릇에 덜기</t>
+          <t>국은 그릇에 덜어 먹기</t>
         </is>
       </c>
       <c r="H121" s="13" t="n">
@@ -32068,12 +32068,12 @@
       </c>
       <c r="I121" s="14" t="inlineStr">
         <is>
-          <t>국은 냄비째 떠먹지 말고 각자 그릇에 덜어 드세요.</t>
+          <t>국은 냄비째 떠먹지 말고 그릇에 덜어 드세요.</t>
         </is>
       </c>
       <c r="J121" s="14" t="inlineStr">
         <is>
-          <t>각자 덜어 실제 먹는 양을 살펴봐요.</t>
+          <t>그릇에 덜어 실제 먹는 양을 살펴봐요.</t>
         </is>
       </c>
       <c r="K121" s="13" t="inlineStr">
@@ -32094,7 +32094,7 @@
       </c>
       <c r="O121" s="14" t="inlineStr">
         <is>
-          <t>근거 범위에 맞춰 이유 문장 수정</t>
+          <t>근거 범위에 맞춰 이유 문장 수정 · 10-19 혼자·가족·도시락 전제 없이 쓰도록</t>
         </is>
       </c>
       <c r="P121" s="13" t="inlineStr">
@@ -32224,20 +32224,20 @@
       </c>
       <c r="G123" s="13" t="inlineStr">
         <is>
-          <t>냉면 국물은 반만</t>
+          <t>국물 음식은 절반만</t>
         </is>
       </c>
       <c r="H123" s="13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I123" s="14" t="inlineStr">
         <is>
-          <t>냉면을 먹을 때 국물은 절반만 드세요.</t>
+          <t>국물 음식을 먹을 때 국물은 절반만 드세요.</t>
         </is>
       </c>
       <c r="J123" s="14" t="inlineStr">
         <is>
-          <t>냉면 국물의 섭취량을 줄여 봐요.</t>
+          <t>국물 섭취량을 줄여 봐요.</t>
         </is>
       </c>
       <c r="K123" s="13" t="inlineStr">
@@ -32258,7 +32258,7 @@
       </c>
       <c r="O123" s="14" t="inlineStr">
         <is>
-          <t>근거 범위에 맞춰 이유 문장 수정</t>
+          <t>근거 범위에 맞춰 이유 문장 수정 · 10-19 특정 음식 이름을 음식 종류로 · 10-19 입문 단계는 특정 음식 전제 없이</t>
         </is>
       </c>
       <c r="P123" s="13" t="inlineStr">
@@ -36092,11 +36092,11 @@
       </c>
       <c r="G171" s="8" t="inlineStr">
         <is>
-          <t>오징어·새우로 한 끼</t>
+          <t>해산물로 한 끼</t>
         </is>
       </c>
       <c r="H171" s="8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I171" s="4" t="inlineStr">
         <is>
@@ -36122,7 +36122,7 @@
       </c>
       <c r="O171" s="4" t="inlineStr">
         <is>
-          <t>국내외 학회 가이드라인 근거로 추가. 의학 검수 대기</t>
+          <t>국내외 학회 가이드라인 근거로 추가. 의학 검수 대기 · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P171" s="8" t="inlineStr">
@@ -37657,7 +37657,7 @@
       </c>
       <c r="G191" s="8" t="inlineStr">
         <is>
-          <t>내일 반찬은 두부조림</t>
+          <t>내일 반찬은 두부 요리</t>
         </is>
       </c>
       <c r="H191" s="8">
@@ -37666,12 +37666,12 @@
       </c>
       <c r="I191" s="4" t="inlineStr">
         <is>
-          <t>내일 반찬으로 두부조림을 준비해 보세요.</t>
+          <t>내일 반찬으로 두부조림이나 두부부침을 준비해 보세요.</t>
         </is>
       </c>
       <c r="J191" s="4" t="inlineStr">
         <is>
-          <t>두부조림은 손쉬운 단백질 반찬이에요.</t>
+          <t>두부 반찬은 손쉬운 단백질 반찬이에요.</t>
         </is>
       </c>
       <c r="K191" s="8" t="inlineStr">
@@ -37688,7 +37688,7 @@
       </c>
       <c r="O191" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 14번)</t>
+          <t>10-13 추가(검수표 14번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P191" s="8" t="inlineStr">
@@ -37815,7 +37815,7 @@
       </c>
       <c r="G193" s="8" t="inlineStr">
         <is>
-          <t>내일 반찬은 고등어구이</t>
+          <t>내일 반찬은 생선구이</t>
         </is>
       </c>
       <c r="H193" s="8">
@@ -37824,12 +37824,12 @@
       </c>
       <c r="I193" s="4" t="inlineStr">
         <is>
-          <t>내일 반찬으로 튀김 대신 고등어구이를 준비해 보세요.</t>
+          <t>내일 반찬으로 튀김 대신 고등어 같은 생선구이를 준비해 보세요.</t>
         </is>
       </c>
       <c r="J193" s="4" t="inlineStr">
         <is>
-          <t>고등어구이는 튀김보다 기름이 덜 들어가요.</t>
+          <t>생선구이는 튀김보다 기름이 덜 들어가요.</t>
         </is>
       </c>
       <c r="K193" s="8" t="inlineStr">
@@ -37850,7 +37850,7 @@
       </c>
       <c r="O193" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 16번)</t>
+          <t>10-13 추가(검수표 16번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P193" s="8" t="inlineStr">
@@ -38131,7 +38131,7 @@
       </c>
       <c r="G197" s="8" t="inlineStr">
         <is>
-          <t>내일은 죽 한 그릇</t>
+          <t>내일은 부드러운 한 끼</t>
         </is>
       </c>
       <c r="H197" s="8">
@@ -38140,12 +38140,12 @@
       </c>
       <c r="I197" s="4" t="inlineStr">
         <is>
-          <t>입맛이 없다면 내일 한 끼는 죽 한 그릇으로 드세요.</t>
+          <t>입맛이 없다면 내일 한 끼는 죽처럼 부드러운 음식으로 드세요.</t>
         </is>
       </c>
       <c r="J197" s="4" t="inlineStr">
         <is>
-          <t>죽은 입맛이 없을 때도 먹기 편해요.</t>
+          <t>부드러운 음식은 입맛이 없을 때도 먹기 편해요.</t>
         </is>
       </c>
       <c r="K197" s="8" t="inlineStr">
@@ -38166,7 +38166,7 @@
       </c>
       <c r="O197" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 20번)</t>
+          <t>10-13 추가(검수표 20번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P197" s="8" t="inlineStr">
@@ -39144,7 +39144,7 @@
       </c>
       <c r="G210" s="8" t="inlineStr">
         <is>
-          <t>점심엔 닭가슴살 샐러드</t>
+          <t>점심엔 단백질 샐러드</t>
         </is>
       </c>
       <c r="H210" s="8">
@@ -39153,12 +39153,12 @@
       </c>
       <c r="I210" s="4" t="inlineStr">
         <is>
-          <t>내일 점심은 닭가슴살을 올린 샐러드로 드세요.</t>
+          <t>내일 점심은 닭가슴살이나 달걀을 올린 샐러드로 드세요.</t>
         </is>
       </c>
       <c r="J210" s="4" t="inlineStr">
         <is>
-          <t>닭가슴살 샐러드는 단백질과 채소를 함께 챙겨요.</t>
+          <t>단백질 샐러드는 단백질과 채소를 함께 챙겨요.</t>
         </is>
       </c>
       <c r="K210" s="8" t="inlineStr">
@@ -39175,7 +39175,7 @@
       </c>
       <c r="O210" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 33번)</t>
+          <t>10-13 추가(검수표 33번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P210" s="8" t="inlineStr">
@@ -39691,7 +39691,7 @@
       </c>
       <c r="G217" s="8" t="inlineStr">
         <is>
-          <t>바쁜 날엔 김밥 한 줄</t>
+          <t>바쁜 날엔 간단한 한 끼</t>
         </is>
       </c>
       <c r="H217" s="8">
@@ -39700,12 +39700,12 @@
       </c>
       <c r="I217" s="4" t="inlineStr">
         <is>
-          <t>바빠서 밥 먹을 시간이 없는 날엔 김밥 한 줄이라도 드세요.</t>
+          <t>바빠서 밥 먹을 시간이 없는 날엔 김밥 한 줄처럼 간단한 한 끼라도 드세요.</t>
         </is>
       </c>
       <c r="J217" s="4" t="inlineStr">
         <is>
-          <t>바쁜 날에도 김밥 한 줄이면 끼니를 챙겨요.</t>
+          <t>바쁜 날에도 간단한 한 끼면 끼니를 챙겨요.</t>
         </is>
       </c>
       <c r="K217" s="8" t="inlineStr">
@@ -39722,7 +39722,7 @@
       </c>
       <c r="O217" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 40번)</t>
+          <t>10-13 추가(검수표 40번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P217" s="8" t="inlineStr">
@@ -39845,7 +39845,7 @@
       </c>
       <c r="G219" s="8" t="inlineStr">
         <is>
-          <t>내일 된장국에 애호박</t>
+          <t>내일 국엔 호박 · 버섯</t>
         </is>
       </c>
       <c r="H219" s="8">
@@ -39854,12 +39854,12 @@
       </c>
       <c r="I219" s="4" t="inlineStr">
         <is>
-          <t>내일 된장국을 끓일 때 애호박을 넣어 보세요.</t>
+          <t>내일 국을 끓일 때 애호박이나 버섯을 넣어 보세요.</t>
         </is>
       </c>
       <c r="J219" s="4" t="inlineStr">
         <is>
-          <t>애호박을 넣으면 국 한 그릇에 채소가 더해져요.</t>
+          <t>채소를 넣으면 국 한 그릇에 채소가 더해져요.</t>
         </is>
       </c>
       <c r="K219" s="8" t="inlineStr">
@@ -39876,7 +39876,7 @@
       </c>
       <c r="O219" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 42번)</t>
+          <t>10-13 추가(검수표 42번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P219" s="8" t="inlineStr">
@@ -40854,7 +40854,7 @@
       </c>
       <c r="G232" s="8" t="inlineStr">
         <is>
-          <t>함께 먹는 끼니 정하기</t>
+          <t>하루 한 끼는 여유 있게</t>
         </is>
       </c>
       <c r="H232" s="8">
@@ -40863,12 +40863,12 @@
       </c>
       <c r="I232" s="4" t="inlineStr">
         <is>
-          <t>가족이나 친구와 함께 먹을 끼니를 하루 한 번 정해 보세요.</t>
+          <t>하루 한 끼는 서두르지 않고 여유 있게 먹을 끼니로 정해 보세요.</t>
         </is>
       </c>
       <c r="J232" s="4" t="inlineStr">
         <is>
-          <t>함께 먹으면 천천히, 즐겁게 먹게 돼요.</t>
+          <t>끼니 하나를 정해 두면 천천히 즐겁게 먹게 돼요.</t>
         </is>
       </c>
       <c r="K232" s="8" t="inlineStr">
@@ -40885,7 +40885,7 @@
       </c>
       <c r="O232" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 55번)</t>
+          <t>10-13 추가(검수표 55번) · 10-19 혼자·가족·도시락 전제 없이 쓰도록</t>
         </is>
       </c>
       <c r="P232" s="8" t="inlineStr">
@@ -41320,7 +41320,7 @@
       </c>
       <c r="G238" s="8" t="inlineStr">
         <is>
-          <t>돼지갈비 대신 생선찜</t>
+          <t>양념 고기 대신 생선찜</t>
         </is>
       </c>
       <c r="H238" s="8">
@@ -41329,7 +41329,7 @@
       </c>
       <c r="I238" s="4" t="inlineStr">
         <is>
-          <t>돼지갈비 대신 생선찜을 골라 드세요.</t>
+          <t>양념한 고기구이 대신 생선찜을 골라 드세요.</t>
         </is>
       </c>
       <c r="J238" s="4" t="inlineStr">
@@ -41355,7 +41355,7 @@
       </c>
       <c r="O238" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 61번)</t>
+          <t>10-13 추가(검수표 61번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P238" s="8" t="inlineStr">
@@ -42098,7 +42098,7 @@
       </c>
       <c r="G248" s="8" t="inlineStr">
         <is>
-          <t>라면에 채소 넣기</t>
+          <t>끓일 때 채소 한 줌 넣기</t>
         </is>
       </c>
       <c r="H248" s="8">
@@ -42107,7 +42107,7 @@
       </c>
       <c r="I248" s="4" t="inlineStr">
         <is>
-          <t>라면을 끓일 때 파·양배추 같은 채소를 넣어 드세요.</t>
+          <t>국이나 면을 끓일 때 파·양배추 같은 채소를 한 줌 넣어 드세요.</t>
         </is>
       </c>
       <c r="J248" s="4" t="inlineStr">
@@ -42133,7 +42133,7 @@
       </c>
       <c r="O248" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 71번)</t>
+          <t>10-13 추가(검수표 71번) · 10-19 특정 음식 이름을 음식 종류로 · 10-19 입문 단계는 특정 음식 전제 없이</t>
         </is>
       </c>
       <c r="P248" s="8" t="inlineStr">
@@ -42179,7 +42179,7 @@
       </c>
       <c r="G249" s="8" t="inlineStr">
         <is>
-          <t>채소 많은 김밥 고르기</t>
+          <t>채소 많은 메뉴 고르기</t>
         </is>
       </c>
       <c r="H249" s="8">
@@ -42188,7 +42188,7 @@
       </c>
       <c r="I249" s="4" t="inlineStr">
         <is>
-          <t>김밥을 고를 때 채소가 많이 들어간 것으로 고르세요.</t>
+          <t>김밥이나 도시락을 고를 때 채소가 많이 들어간 것으로 고르세요.</t>
         </is>
       </c>
       <c r="J249" s="4" t="inlineStr">
@@ -42210,7 +42210,7 @@
       </c>
       <c r="O249" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 72번)</t>
+          <t>10-13 추가(검수표 72번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P249" s="8" t="inlineStr">
@@ -43277,7 +43277,7 @@
       </c>
       <c r="G263" s="8" t="inlineStr">
         <is>
-          <t>내일은 맑은 콩나물국</t>
+          <t>내일은 맑은 국으로</t>
         </is>
       </c>
       <c r="H263" s="8">
@@ -43286,12 +43286,12 @@
       </c>
       <c r="I263" s="4" t="inlineStr">
         <is>
-          <t>내일 국은 찌개 대신 맑은 콩나물국으로 끓여 보세요.</t>
+          <t>내일 국은 찌개 대신 콩나물국처럼 맑은 국으로 끓여 보세요.</t>
         </is>
       </c>
       <c r="J263" s="4" t="inlineStr">
         <is>
-          <t>맑은 콩나물국은 찌개보다 덜 짜요.</t>
+          <t>맑은 국은 찌개보다 덜 짜요.</t>
         </is>
       </c>
       <c r="K263" s="8" t="inlineStr">
@@ -43308,7 +43308,7 @@
       </c>
       <c r="O263" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 86번)</t>
+          <t>10-13 추가(검수표 86번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P263" s="8" t="inlineStr">
@@ -44764,7 +44764,7 @@
       </c>
       <c r="G282" s="8" t="inlineStr">
         <is>
-          <t>도시락에 단백질 담기</t>
+          <t>내일 단백질 반찬 담기</t>
         </is>
       </c>
       <c r="H282" s="8">
@@ -44773,12 +44773,12 @@
       </c>
       <c r="I282" s="4" t="inlineStr">
         <is>
-          <t>내일 도시락에 고기·생선·달걀·두부 반찬을 한 가지 담으세요.</t>
+          <t>내일 먹을 고기·생선·달걀·두부 반찬을 한 가지 담아 두세요.</t>
         </is>
       </c>
       <c r="J282" s="4" t="inlineStr">
         <is>
-          <t>도시락에 담으면 밖에서도 단백질을 챙겨요.</t>
+          <t>미리 담아 두면 밖에서도 단백질을 챙겨요.</t>
         </is>
       </c>
       <c r="K282" s="8" t="inlineStr">
@@ -44799,7 +44799,7 @@
       </c>
       <c r="O282" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 105번)</t>
+          <t>10-13 추가(검수표 105번) · 10-19 혼자·가족·도시락 전제 없이 쓰도록</t>
         </is>
       </c>
       <c r="P282" s="8" t="inlineStr">
@@ -44845,7 +44845,7 @@
       </c>
       <c r="G283" s="8" t="inlineStr">
         <is>
-          <t>삼겹살 대신 보쌈</t>
+          <t>구운 고기 대신 삶은 고기</t>
         </is>
       </c>
       <c r="H283" s="8">
@@ -44854,12 +44854,12 @@
       </c>
       <c r="I283" s="4" t="inlineStr">
         <is>
-          <t>구운 삼겹살 대신 삶은 보쌈을 골라 드세요.</t>
+          <t>기름에 구운 고기 대신 보쌈처럼 삶은 고기를 골라 드세요.</t>
         </is>
       </c>
       <c r="J283" s="4" t="inlineStr">
         <is>
-          <t>삶은 고기는 구운 삼겹살보다 기름이 덜해요.</t>
+          <t>삶은 고기는 구운 고기보다 기름이 덜해요.</t>
         </is>
       </c>
       <c r="K283" s="8" t="inlineStr">
@@ -44880,7 +44880,7 @@
       </c>
       <c r="O283" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 106번)</t>
+          <t>10-13 추가(검수표 106번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P283" s="8" t="inlineStr">
@@ -44926,7 +44926,7 @@
       </c>
       <c r="G284" s="8" t="inlineStr">
         <is>
-          <t>잡채 대신 나물무침</t>
+          <t>볶은 반찬 대신 나물무침</t>
         </is>
       </c>
       <c r="H284" s="8">
@@ -44935,12 +44935,12 @@
       </c>
       <c r="I284" s="4" t="inlineStr">
         <is>
-          <t>기름에 볶은 잡채 대신 나물무침을 골라 드세요.</t>
+          <t>기름에 볶은 반찬 대신 나물무침을 골라 드세요.</t>
         </is>
       </c>
       <c r="J284" s="4" t="inlineStr">
         <is>
-          <t>나물무침은 잡채보다 기름을 덜 써요.</t>
+          <t>나물무침은 볶은 반찬보다 기름을 덜 써요.</t>
         </is>
       </c>
       <c r="K284" s="8" t="inlineStr">
@@ -44961,7 +44961,7 @@
       </c>
       <c r="O284" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 107번)</t>
+          <t>10-13 추가(검수표 107번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P284" s="8" t="inlineStr">
@@ -45165,7 +45165,7 @@
       </c>
       <c r="G287" s="8" t="inlineStr">
         <is>
-          <t>내일 반찬은 콩나물무침</t>
+          <t>내일 반찬은 나물무침</t>
         </is>
       </c>
       <c r="H287" s="8">
@@ -45174,12 +45174,12 @@
       </c>
       <c r="I287" s="4" t="inlineStr">
         <is>
-          <t>내일 반찬으로 콩나물무침을 준비해 보세요.</t>
+          <t>내일 반찬으로 콩나물무침 같은 나물무침을 준비해 보세요.</t>
         </is>
       </c>
       <c r="J287" s="4" t="inlineStr">
         <is>
-          <t>콩나물무침은 기름을 거의 쓰지 않아요.</t>
+          <t>나물무침은 기름을 거의 쓰지 않아요.</t>
         </is>
       </c>
       <c r="K287" s="8" t="inlineStr">
@@ -45196,7 +45196,7 @@
       </c>
       <c r="O287" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 110번)</t>
+          <t>10-13 추가(검수표 110번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P287" s="8" t="inlineStr">
@@ -45242,7 +45242,7 @@
       </c>
       <c r="G288" s="8" t="inlineStr">
         <is>
-          <t>제육볶음 대신 수육</t>
+          <t>볶은 고기 대신 수육</t>
         </is>
       </c>
       <c r="H288" s="8">
@@ -45251,7 +45251,7 @@
       </c>
       <c r="I288" s="4" t="inlineStr">
         <is>
-          <t>제육볶음 대신 삶은 수육을 골라 드세요.</t>
+          <t>양념해 볶은 고기 대신 삶은 수육을 골라 드세요.</t>
         </is>
       </c>
       <c r="J288" s="4" t="inlineStr">
@@ -45277,7 +45277,7 @@
       </c>
       <c r="O288" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 111번)</t>
+          <t>10-13 추가(검수표 111번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P288" s="8" t="inlineStr">
@@ -45323,7 +45323,7 @@
       </c>
       <c r="G289" s="8" t="inlineStr">
         <is>
-          <t>돈가스 대신 생선구이</t>
+          <t>튀긴 고기 대신 생선구이</t>
         </is>
       </c>
       <c r="H289" s="8">
@@ -45332,12 +45332,12 @@
       </c>
       <c r="I289" s="4" t="inlineStr">
         <is>
-          <t>돈가스 대신 생선구이를 골라 드세요.</t>
+          <t>튀긴 고기 요리 대신 생선구이를 골라 드세요.</t>
         </is>
       </c>
       <c r="J289" s="4" t="inlineStr">
         <is>
-          <t>생선구이는 돈가스보다 기름이 덜 들어가요.</t>
+          <t>생선구이는 튀긴 고기보다 기름이 덜 들어가요.</t>
         </is>
       </c>
       <c r="K289" s="8" t="inlineStr">
@@ -45358,7 +45358,7 @@
       </c>
       <c r="O289" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 112번)</t>
+          <t>10-13 추가(검수표 112번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P289" s="8" t="inlineStr">
@@ -45404,7 +45404,7 @@
       </c>
       <c r="G290" s="8" t="inlineStr">
         <is>
-          <t>치킨 대신 닭백숙</t>
+          <t>튀긴 닭 대신 삶은 닭</t>
         </is>
       </c>
       <c r="H290" s="8">
@@ -45413,7 +45413,7 @@
       </c>
       <c r="I290" s="4" t="inlineStr">
         <is>
-          <t>튀긴 치킨 대신 삶은 닭백숙을 드세요.</t>
+          <t>튀긴 닭 대신 백숙처럼 삶은 닭을 드세요.</t>
         </is>
       </c>
       <c r="J290" s="4" t="inlineStr">
@@ -45439,7 +45439,7 @@
       </c>
       <c r="O290" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 113번)</t>
+          <t>10-13 추가(검수표 113번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P290" s="8" t="inlineStr">
@@ -45485,7 +45485,7 @@
       </c>
       <c r="G291" s="8" t="inlineStr">
         <is>
-          <t>김치찌개 대신 맑은 국</t>
+          <t>찌개 대신 맑은 국</t>
         </is>
       </c>
       <c r="H291" s="8">
@@ -45494,7 +45494,7 @@
       </c>
       <c r="I291" s="4" t="inlineStr">
         <is>
-          <t>김치찌개 대신 맑게 끓인 국을 골라 드세요.</t>
+          <t>짭짤한 찌개 대신 맑게 끓인 국을 골라 드세요.</t>
         </is>
       </c>
       <c r="J291" s="4" t="inlineStr">
@@ -45516,7 +45516,7 @@
       </c>
       <c r="O291" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 114번)</t>
+          <t>10-13 추가(검수표 114번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P291" s="8" t="inlineStr">
@@ -45562,7 +45562,7 @@
       </c>
       <c r="G292" s="8" t="inlineStr">
         <is>
-          <t>믹스 대신 블랙커피</t>
+          <t>단 커피 대신 블랙커피</t>
         </is>
       </c>
       <c r="H292" s="8">
@@ -45571,12 +45571,12 @@
       </c>
       <c r="I292" s="4" t="inlineStr">
         <is>
-          <t>믹스커피 대신 설탕 없는 블랙커피를 드세요.</t>
+          <t>설탕 든 커피 대신 설탕 없는 블랙커피를 드세요.</t>
         </is>
       </c>
       <c r="J292" s="4" t="inlineStr">
         <is>
-          <t>아메리카노에는 설탕이 들어 있지 않아요.</t>
+          <t>블랙커피에는 설탕이 들어 있지 않아요.</t>
         </is>
       </c>
       <c r="K292" s="8" t="inlineStr">
@@ -45593,7 +45593,7 @@
       </c>
       <c r="O292" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 115번)</t>
+          <t>10-13 추가(검수표 115번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P292" s="8" t="inlineStr">
@@ -45639,7 +45639,7 @@
       </c>
       <c r="G293" s="8" t="inlineStr">
         <is>
-          <t>케이크 대신 요거트</t>
+          <t>단 디저트 대신 요거트</t>
         </is>
       </c>
       <c r="H293" s="8">
@@ -45648,7 +45648,7 @@
       </c>
       <c r="I293" s="4" t="inlineStr">
         <is>
-          <t>케이크 대신 달지 않은 플레인 요거트를 드세요.</t>
+          <t>케이크 같은 단 디저트 대신 달지 않은 플레인 요거트를 드세요.</t>
         </is>
       </c>
       <c r="J293" s="4" t="inlineStr">
@@ -45670,7 +45670,7 @@
       </c>
       <c r="O293" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 116번)</t>
+          <t>10-13 추가(검수표 116번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P293" s="8" t="inlineStr">
@@ -45716,7 +45716,7 @@
       </c>
       <c r="G294" s="8" t="inlineStr">
         <is>
-          <t>짜장면 대신 비빔밥</t>
+          <t>기름진 면 대신 나물밥</t>
         </is>
       </c>
       <c r="H294" s="8">
@@ -45725,12 +45725,12 @@
       </c>
       <c r="I294" s="4" t="inlineStr">
         <is>
-          <t>짜장면 대신 나물이 들어간 비빔밥을 골라 드세요.</t>
+          <t>기름진 면 요리 대신 나물이 들어간 밥을 골라 드세요.</t>
         </is>
       </c>
       <c r="J294" s="4" t="inlineStr">
         <is>
-          <t>비빔밥은 채소를 넉넉히 먹을 수 있어요.</t>
+          <t>나물밥은 채소를 넉넉히 먹을 수 있어요.</t>
         </is>
       </c>
       <c r="K294" s="8" t="inlineStr">
@@ -45747,7 +45747,7 @@
       </c>
       <c r="O294" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 117번)</t>
+          <t>10-13 추가(검수표 117번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P294" s="8" t="inlineStr">
@@ -45874,7 +45874,7 @@
       </c>
       <c r="G296" s="8" t="inlineStr">
         <is>
-          <t>아침엔 누룽지 한 그릇</t>
+          <t>아침엔 따뜻한 한 그릇</t>
         </is>
       </c>
       <c r="H296" s="8">
@@ -45883,12 +45883,12 @@
       </c>
       <c r="I296" s="4" t="inlineStr">
         <is>
-          <t>아침에 따뜻한 누룽지 한 그릇으로 식사를 챙겨 보세요.</t>
+          <t>아침에 누룽지나 죽처럼 따뜻한 한 그릇으로 식사를 챙겨 보세요.</t>
         </is>
       </c>
       <c r="J296" s="4" t="inlineStr">
         <is>
-          <t>따뜻한 누룽지는 아침에 부담 없이 먹기 좋아요.</t>
+          <t>따뜻한 한 그릇은 아침에 부담 없이 먹기 좋아요.</t>
         </is>
       </c>
       <c r="K296" s="8" t="inlineStr">
@@ -45905,7 +45905,7 @@
       </c>
       <c r="O296" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 119번)</t>
+          <t>10-13 추가(검수표 119번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P296" s="8" t="inlineStr">
@@ -46028,7 +46028,7 @@
       </c>
       <c r="G298" s="8" t="inlineStr">
         <is>
-          <t>라면엔 콩나물 한 줌</t>
+          <t>끓일 때 콩나물 한 줌</t>
         </is>
       </c>
       <c r="H298" s="8">
@@ -46037,12 +46037,12 @@
       </c>
       <c r="I298" s="4" t="inlineStr">
         <is>
-          <t>라면을 끓일 때 콩나물을 한 줌 넣어 드세요.</t>
+          <t>국이나 면을 끓일 때 콩나물이나 숙주를 한 줌 넣어 드세요.</t>
         </is>
       </c>
       <c r="J298" s="4" t="inlineStr">
         <is>
-          <t>콩나물을 넣으면 라면에도 채소가 더해져요.</t>
+          <t>콩나물을 넣으면 한 그릇에 채소가 더해져요.</t>
         </is>
       </c>
       <c r="K298" s="8" t="inlineStr">
@@ -46063,7 +46063,7 @@
       </c>
       <c r="O298" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 121번)</t>
+          <t>10-13 추가(검수표 121번) · 10-19 특정 음식 이름을 음식 종류로 · 10-19 입문 단계는 특정 음식 전제 없이</t>
         </is>
       </c>
       <c r="P298" s="8" t="inlineStr">
@@ -46109,7 +46109,7 @@
       </c>
       <c r="G299" s="8" t="inlineStr">
         <is>
-          <t>비빔밥은 나물 듬뿍</t>
+          <t>밥엔 나물 듬뿍</t>
         </is>
       </c>
       <c r="H299" s="8">
@@ -46118,7 +46118,7 @@
       </c>
       <c r="I299" s="4" t="inlineStr">
         <is>
-          <t>비빔밥을 먹을 때 나물을 듬뿍 넣어 드세요.</t>
+          <t>밥을 먹을 때 나물을 듬뿍 곁들여 드세요.</t>
         </is>
       </c>
       <c r="J299" s="4" t="inlineStr">
@@ -46144,7 +46144,7 @@
       </c>
       <c r="O299" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 122번)</t>
+          <t>10-13 추가(검수표 122번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P299" s="8" t="inlineStr">
@@ -46190,7 +46190,7 @@
       </c>
       <c r="G300" s="8" t="inlineStr">
         <is>
-          <t>달걀말이에 부추 넣기</t>
+          <t>달걀 요리에 채소 넣기</t>
         </is>
       </c>
       <c r="H300" s="8">
@@ -46199,12 +46199,12 @@
       </c>
       <c r="I300" s="4" t="inlineStr">
         <is>
-          <t>달걀말이를 만들 때 부추를 썰어 넣어 보세요.</t>
+          <t>달걀말이나 달걀찜을 만들 때 부추·파 같은 채소를 넣어 보세요.</t>
         </is>
       </c>
       <c r="J300" s="4" t="inlineStr">
         <is>
-          <t>부추를 넣으면 반찬 하나에 채소가 더해져요.</t>
+          <t>채소를 넣으면 반찬 하나에 채소가 더해져요.</t>
         </is>
       </c>
       <c r="K300" s="8" t="inlineStr">
@@ -46225,7 +46225,7 @@
       </c>
       <c r="O300" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 123번)</t>
+          <t>10-13 추가(검수표 123번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P300" s="8" t="inlineStr">
@@ -46271,7 +46271,7 @@
       </c>
       <c r="G301" s="8" t="inlineStr">
         <is>
-          <t>라면에 달걀 하나</t>
+          <t>끓일 때 달걀 하나 넣기</t>
         </is>
       </c>
       <c r="H301" s="8">
@@ -46280,12 +46280,12 @@
       </c>
       <c r="I301" s="4" t="inlineStr">
         <is>
-          <t>라면을 끓일 때 달걀을 하나 넣어 드세요.</t>
+          <t>국이나 면을 끓일 때 달걀을 하나 넣어 드세요.</t>
         </is>
       </c>
       <c r="J301" s="4" t="inlineStr">
         <is>
-          <t>달걀을 넣으면 라면에도 단백질이 더해져요.</t>
+          <t>달걀을 넣으면 한 그릇에 단백질이 더해져요.</t>
         </is>
       </c>
       <c r="K301" s="8" t="inlineStr">
@@ -46306,7 +46306,7 @@
       </c>
       <c r="O301" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 124번)</t>
+          <t>10-13 추가(검수표 124번) · 10-19 특정 음식 이름을 음식 종류로 · 10-19 입문 단계는 특정 음식 전제 없이</t>
         </is>
       </c>
       <c r="P301" s="8" t="inlineStr">
@@ -46352,7 +46352,7 @@
       </c>
       <c r="G302" s="8" t="inlineStr">
         <is>
-          <t>김밥은 참치·계란으로</t>
+          <t>간편식엔 참치·달걀</t>
         </is>
       </c>
       <c r="H302" s="8">
@@ -46361,12 +46361,12 @@
       </c>
       <c r="I302" s="4" t="inlineStr">
         <is>
-          <t>김밥을 고를 때 참치나 계란이 든 김밥으로 고르세요.</t>
+          <t>김밥 같은 간편식을 고를 때 참치나 달걀이 든 것으로 고르세요.</t>
         </is>
       </c>
       <c r="J302" s="4" t="inlineStr">
         <is>
-          <t>참치·계란 김밥으로 단백질을 챙겨요.</t>
+          <t>참치나 달걀이 든 간편식으로 단백질을 챙겨요.</t>
         </is>
       </c>
       <c r="K302" s="8" t="inlineStr">
@@ -46383,7 +46383,7 @@
       </c>
       <c r="O302" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 125번)</t>
+          <t>10-13 추가(검수표 125번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P302" s="8" t="inlineStr">
@@ -46506,7 +46506,7 @@
       </c>
       <c r="G304" s="8" t="inlineStr">
         <is>
-          <t>식혜 대신 보리차</t>
+          <t>단 음료 대신 보리차</t>
         </is>
       </c>
       <c r="H304" s="8">
@@ -46515,7 +46515,7 @@
       </c>
       <c r="I304" s="4" t="inlineStr">
         <is>
-          <t>식혜 대신 달지 않은 보리차를 드세요.</t>
+          <t>식혜 같은 단 음료 대신 달지 않은 보리차를 드세요.</t>
         </is>
       </c>
       <c r="J304" s="4" t="inlineStr">
@@ -46541,7 +46541,7 @@
       </c>
       <c r="O304" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 127번)</t>
+          <t>10-13 추가(검수표 127번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P304" s="8" t="inlineStr">
@@ -46587,7 +46587,7 @@
       </c>
       <c r="G305" s="8" t="inlineStr">
         <is>
-          <t>라떼는 시럽 빼고</t>
+          <t>주문할 땐 시럽 빼고</t>
         </is>
       </c>
       <c r="H305" s="8">
@@ -46596,12 +46596,12 @@
       </c>
       <c r="I305" s="4" t="inlineStr">
         <is>
-          <t>라떼를 주문할 때 시럽은 빼 달라고 하세요.</t>
+          <t>음료를 주문할 때 시럽은 빼 달라고 하세요.</t>
         </is>
       </c>
       <c r="J305" s="4" t="inlineStr">
         <is>
-          <t>시럽을 빼면 라떼의 당이 크게 줄어요.</t>
+          <t>시럽을 빼면 음료의 당이 크게 줄어요.</t>
         </is>
       </c>
       <c r="K305" s="8" t="inlineStr">
@@ -46618,7 +46618,7 @@
       </c>
       <c r="O305" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 128번)</t>
+          <t>10-13 추가(검수표 128번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P305" s="8" t="inlineStr">
@@ -46664,7 +46664,7 @@
       </c>
       <c r="G306" s="8" t="inlineStr">
         <is>
-          <t>믹스커피는 반 봉지만</t>
+          <t>커피 설탕은 반만</t>
         </is>
       </c>
       <c r="H306" s="8">
@@ -46673,12 +46673,12 @@
       </c>
       <c r="I306" s="4" t="inlineStr">
         <is>
-          <t>믹스커피를 탈 때 한 봉지 대신 반 봉지만 넣으세요.</t>
+          <t>커피에 넣는 설탕이나 믹스는 평소의 절반만 넣으세요.</t>
         </is>
       </c>
       <c r="J306" s="4" t="inlineStr">
         <is>
-          <t>반 봉지만 타도 단맛은 충분해요.</t>
+          <t>설탕을 반만 넣어도 단맛은 충분해요.</t>
         </is>
       </c>
       <c r="K306" s="8" t="inlineStr">
@@ -46699,7 +46699,7 @@
       </c>
       <c r="O306" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 129번)</t>
+          <t>10-13 추가(검수표 129번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P306" s="8" t="inlineStr">
@@ -46745,7 +46745,7 @@
       </c>
       <c r="G307" s="8" t="inlineStr">
         <is>
-          <t>라면 스프는 반만</t>
+          <t>양념은 절반만 넣기</t>
         </is>
       </c>
       <c r="H307" s="8">
@@ -46754,12 +46754,12 @@
       </c>
       <c r="I307" s="4" t="inlineStr">
         <is>
-          <t>라면을 끓일 때 스프는 절반만 넣으세요.</t>
+          <t>국이나 찌개, 즉석식품의 양념은 절반만 넣으세요.</t>
         </is>
       </c>
       <c r="J307" s="4" t="inlineStr">
         <is>
-          <t>스프를 반만 넣으면 나트륨이 크게 줄어요.</t>
+          <t>양념을 반만 넣으면 나트륨이 크게 줄어요.</t>
         </is>
       </c>
       <c r="K307" s="8" t="inlineStr">
@@ -46780,7 +46780,7 @@
       </c>
       <c r="O307" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 130번)</t>
+          <t>10-13 추가(검수표 130번) · 10-19 특정 음식 이름을 음식 종류로 · 10-19 입문 단계는 특정 음식 전제 없이</t>
         </is>
       </c>
       <c r="P307" s="8" t="inlineStr">
@@ -46826,7 +46826,7 @@
       </c>
       <c r="G308" s="8" t="inlineStr">
         <is>
-          <t>김치는 백김치로</t>
+          <t>절임 반찬은 덜 짠 것으로</t>
         </is>
       </c>
       <c r="H308" s="8">
@@ -46835,12 +46835,12 @@
       </c>
       <c r="I308" s="4" t="inlineStr">
         <is>
-          <t>빨간 김치 대신 백김치를 곁들여 드세요.</t>
+          <t>김치나 장아찌는 백김치처럼 덜 짠 것으로 곁들여 드세요.</t>
         </is>
       </c>
       <c r="J308" s="4" t="inlineStr">
         <is>
-          <t>백김치는 빨간 김치보다 덜 짠 편이에요.</t>
+          <t>덜 짠 절임 반찬을 고르면 나트륨이 줄어요.</t>
         </is>
       </c>
       <c r="K308" s="8" t="inlineStr">
@@ -46857,7 +46857,7 @@
       </c>
       <c r="O308" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 131번)</t>
+          <t>10-13 추가(검수표 131번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P308" s="8" t="inlineStr">
@@ -46903,7 +46903,7 @@
       </c>
       <c r="G309" s="8" t="inlineStr">
         <is>
-          <t>오징어튀김 대신 숙회</t>
+          <t>해물 튀김 대신 숙회</t>
         </is>
       </c>
       <c r="H309" s="8">
@@ -46912,7 +46912,7 @@
       </c>
       <c r="I309" s="4" t="inlineStr">
         <is>
-          <t>오징어튀김 대신 데친 오징어 숙회를 드세요.</t>
+          <t>해물 튀김 대신 데친 숙회를 드세요.</t>
         </is>
       </c>
       <c r="J309" s="4" t="inlineStr">
@@ -46938,7 +46938,7 @@
       </c>
       <c r="O309" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 132번)</t>
+          <t>10-13 추가(검수표 132번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P309" s="8" t="inlineStr">
@@ -46984,7 +46984,7 @@
       </c>
       <c r="G310" s="8" t="inlineStr">
         <is>
-          <t>치킨은 오븐구이로</t>
+          <t>닭은 튀김 대신 구이로</t>
         </is>
       </c>
       <c r="H310" s="8">
@@ -46993,12 +46993,12 @@
       </c>
       <c r="I310" s="4" t="inlineStr">
         <is>
-          <t>치킨은 튀긴 것 대신 오븐에 구운 것으로 고르세요.</t>
+          <t>닭 요리는 튀긴 것 대신 오븐에 구운 것으로 고르세요.</t>
         </is>
       </c>
       <c r="J310" s="4" t="inlineStr">
         <is>
-          <t>오븐구이는 튀긴 치킨보다 기름이 덜해요.</t>
+          <t>오븐구이는 튀긴 닭보다 기름이 덜해요.</t>
         </is>
       </c>
       <c r="K310" s="8" t="inlineStr">
@@ -47019,7 +47019,7 @@
       </c>
       <c r="O310" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 133번)</t>
+          <t>10-13 추가(검수표 133번) · 10-19 특정 음식 이름을 음식 종류로</t>
         </is>
       </c>
       <c r="P310" s="8" t="inlineStr">

--- a/files/diet-reference-config-v1.0.0.xlsx
+++ b/files/diet-reference-config-v1.0.0.xlsx
@@ -33040,20 +33040,20 @@
       </c>
       <c r="G133" s="8" t="inlineStr">
         <is>
-          <t>마실 것 미리 정하기</t>
+          <t>오늘 마실 음료 정하기</t>
         </is>
       </c>
       <c r="H133" s="8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I133" s="4" t="inlineStr">
         <is>
-          <t>카페나 편의점에 가기 전에 무엇을 마실지 미리 정해 두세요.</t>
+          <t>오늘 무엇을 마실지 미리 정해 두세요. 정해 두면 카페나 편의점에서 단 음료를 충동적으로 고르는 일이 줄어요.</t>
         </is>
       </c>
       <c r="J133" s="14" t="inlineStr">
         <is>
-          <t>미리 정해 두면 고르는 순간에 헤매지 않아요.</t>
+          <t>미리 정해 두면 단 음료를 충동적으로 고르지 않게 돼요.</t>
         </is>
       </c>
       <c r="K133" s="13" t="inlineStr">
@@ -33070,7 +33070,7 @@
       </c>
       <c r="O133" s="14" t="inlineStr">
         <is>
-          <t>감량·공복·증량 금지가 걸린 사용자에게 도전 단계 후보가 0이 되던 칸을 채우려고 추가. 성격은 비워 둔다</t>
+          <t>감량·공복·증량 금지가 걸린 사용자에게 도전 단계 후보가 0이 되던 칸을 채우려고 추가. 성격은 비워 둔다 · 10-19 효과가 드러나게 다듬음</t>
         </is>
       </c>
       <c r="P133" s="13" t="inlineStr">
@@ -33680,20 +33680,20 @@
       </c>
       <c r="G141" s="8" t="inlineStr">
         <is>
-          <t>내일 쓸 두부 준비하기</t>
+          <t>내일 두부 반찬 준비하기</t>
         </is>
       </c>
       <c r="H141" s="8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I141" s="4" t="inlineStr">
         <is>
-          <t>내일 반찬으로 쓸 두부가 냉장고에 있는지 확인하고 준비해 두세요.</t>
+          <t>내일 먹을 두부 반찬을 미리 준비해 두세요. 준비해 두면 내일 단백질 반찬을 챙기기 쉬워요.</t>
         </is>
       </c>
       <c r="J141" s="14" t="inlineStr">
         <is>
-          <t>두부를 냉장고에 두면 내일 준비할 재료를 미리 확인할 수 있어요.</t>
+          <t>준비해 두면 내일 단백질 반찬을 챙기기 쉬워요.</t>
         </is>
       </c>
       <c r="K141" s="13" t="inlineStr">
@@ -33710,7 +33710,7 @@
       </c>
       <c r="O141" s="14" t="inlineStr">
         <is>
-          <t>저녁 식사 후에도 실행 가능한 다음 날 준비 행동.</t>
+          <t>저녁 식사 후에도 실행 가능한 다음 날 준비 행동. · 10-19 효과가 드러나게 다듬음</t>
         </is>
       </c>
       <c r="P141" s="13" t="inlineStr">

--- a/files/diet-reference-config-v1.0.0.xlsx
+++ b/files/diet-reference-config-v1.0.0.xlsx
@@ -34084,20 +34084,20 @@
       </c>
       <c r="G146" s="8" t="inlineStr">
         <is>
-          <t>마가린·쇼트닝 빼기</t>
+          <t>트랜스지방 없는 하루</t>
         </is>
       </c>
       <c r="H146" s="8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I146" s="4" t="inlineStr">
         <is>
-          <t>요리할 때 마가린이나 쇼트닝은 쓰지 말고 빼 보세요.</t>
+          <t>오늘 하루는 마가린·쇼트닝처럼 트랜스지방이 든 기름을 쓰지 않고 지내 보세요.</t>
         </is>
       </c>
       <c r="J146" s="4" t="inlineStr">
         <is>
-          <t>트랜스지방이 많은 기름을 빼는 행동이에요.</t>
+          <t>트랜스지방이 든 기름을 하루 쓰지 않는 행동이에요.</t>
         </is>
       </c>
       <c r="K146" s="8" t="inlineStr">
@@ -34114,7 +34114,7 @@
       </c>
       <c r="O146" s="4" t="inlineStr">
         <is>
-          <t>국내외 학회 가이드라인 근거로 추가. 의학 검수 대기</t>
+          <t>국내외 학회 가이드라인 근거로 추가. 의학 검수 대기 · 10-19 「없는 하루」 꼴로</t>
         </is>
       </c>
       <c r="P146" s="8" t="inlineStr">

--- a/files/diet-reference-config-v1.0.0.xlsx
+++ b/files/diet-reference-config-v1.0.0.xlsx
@@ -25019,7 +25019,7 @@
       </c>
       <c r="F36" s="13" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="G36" s="8" t="inlineStr">
@@ -25054,7 +25054,7 @@
       </c>
       <c r="O36" s="14" t="inlineStr">
         <is>
-          <t>근거 범위에 맞춰 이유 문장 수정</t>
+          <t>근거 범위에 맞춰 이유 문장 수정 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="P36" s="13" t="inlineStr">
@@ -25511,7 +25511,7 @@
       </c>
       <c r="F42" s="13" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="G42" s="13" t="inlineStr">
@@ -25550,7 +25550,7 @@
       </c>
       <c r="O42" s="14" t="inlineStr">
         <is>
-          <t>근거 범위에 맞춰 이유 문장 수정</t>
+          <t>근거 범위에 맞춰 이유 문장 수정 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="P42" s="13" t="inlineStr">
@@ -26747,7 +26747,7 @@
       </c>
       <c r="F57" s="13" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="G57" s="8" t="inlineStr">
@@ -26786,7 +26786,7 @@
       </c>
       <c r="O57" s="14" t="inlineStr">
         <is>
-          <t>근거 범위에 맞춰 이유 문장 수정</t>
+          <t>근거 범위에 맞춰 이유 문장 수정 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="P57" s="13" t="inlineStr">
@@ -28991,7 +28991,7 @@
       </c>
       <c r="F84" s="13" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="G84" s="8" t="inlineStr">
@@ -29026,7 +29026,7 @@
       </c>
       <c r="O84" s="14" t="inlineStr">
         <is>
-          <t>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요</t>
+          <t>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="P84" s="13" t="inlineStr">
@@ -35607,7 +35607,7 @@
       </c>
       <c r="F165" s="8" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="G165" s="8" t="inlineStr">
@@ -35642,7 +35642,7 @@
       </c>
       <c r="O165" s="4" t="inlineStr">
         <is>
-          <t>국내외 학회 가이드라인 근거로 추가. 의학 검수 대기</t>
+          <t>국내외 학회 가이드라인 근거로 추가. 의학 검수 대기 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="P165" s="8" t="inlineStr">
@@ -37891,7 +37891,7 @@
       </c>
       <c r="F194" s="8" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="G194" s="8" t="inlineStr">
@@ -37931,7 +37931,7 @@
       </c>
       <c r="O194" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 17번)</t>
+          <t>10-13 추가(검수표 17번) · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="P194" s="8" t="inlineStr">
@@ -38519,7 +38519,7 @@
       </c>
       <c r="F202" s="8" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="G202" s="8" t="inlineStr">
@@ -38559,7 +38559,7 @@
       </c>
       <c r="O202" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 25번)</t>
+          <t>10-13 추가(검수표 25번) · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="P202" s="8" t="inlineStr">
@@ -38600,7 +38600,7 @@
       </c>
       <c r="F203" s="8" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="G203" s="8" t="inlineStr">
@@ -38636,7 +38636,7 @@
       </c>
       <c r="O203" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 26번)</t>
+          <t>10-13 추가(검수표 26번) · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="P203" s="8" t="inlineStr">
@@ -40623,7 +40623,7 @@
       </c>
       <c r="G229" s="8" t="inlineStr">
         <is>
-          <t>저녁은 매일 7시쯤</t>
+          <t>저녁은 매일 같은 시간에</t>
         </is>
       </c>
       <c r="H229" s="8">
@@ -40632,7 +40632,7 @@
       </c>
       <c r="I229" s="4" t="inlineStr">
         <is>
-          <t>매일 저녁 7시쯤 비슷한 시간에 저녁을 드세요.</t>
+          <t>매일 저녁을 정해진 시간에 드세요.</t>
         </is>
       </c>
       <c r="J229" s="4" t="inlineStr">
@@ -40654,7 +40654,7 @@
       </c>
       <c r="O229" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 52번)</t>
+          <t>10-13 추가(검수표 52번) · 10-19 특정 시각 전제 없이</t>
         </is>
       </c>
       <c r="P229" s="8" t="inlineStr">
@@ -44840,7 +44840,7 @@
       </c>
       <c r="F283" s="8" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="G283" s="8" t="inlineStr">
@@ -44880,7 +44880,7 @@
       </c>
       <c r="O283" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 106번) · 10-19 특정 음식 이름을 음식 종류로</t>
+          <t>10-13 추가(검수표 106번) · 10-19 특정 음식 이름을 음식 종류로 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="P283" s="8" t="inlineStr">
@@ -44921,7 +44921,7 @@
       </c>
       <c r="F284" s="8" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="G284" s="8" t="inlineStr">
@@ -44961,7 +44961,7 @@
       </c>
       <c r="O284" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 107번) · 10-19 특정 음식 이름을 음식 종류로</t>
+          <t>10-13 추가(검수표 107번) · 10-19 특정 음식 이름을 음식 종류로 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="P284" s="8" t="inlineStr">
@@ -45237,7 +45237,7 @@
       </c>
       <c r="F288" s="8" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="G288" s="8" t="inlineStr">
@@ -45277,7 +45277,7 @@
       </c>
       <c r="O288" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 111번) · 10-19 특정 음식 이름을 음식 종류로</t>
+          <t>10-13 추가(검수표 111번) · 10-19 특정 음식 이름을 음식 종류로 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="P288" s="8" t="inlineStr">
@@ -45318,7 +45318,7 @@
       </c>
       <c r="F289" s="8" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="G289" s="8" t="inlineStr">
@@ -45358,7 +45358,7 @@
       </c>
       <c r="O289" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 112번) · 10-19 특정 음식 이름을 음식 종류로</t>
+          <t>10-13 추가(검수표 112번) · 10-19 특정 음식 이름을 음식 종류로 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="P289" s="8" t="inlineStr">
@@ -45399,7 +45399,7 @@
       </c>
       <c r="F290" s="8" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="G290" s="8" t="inlineStr">
@@ -45439,7 +45439,7 @@
       </c>
       <c r="O290" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 113번) · 10-19 특정 음식 이름을 음식 종류로</t>
+          <t>10-13 추가(검수표 113번) · 10-19 특정 음식 이름을 음식 종류로 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="P290" s="8" t="inlineStr">
@@ -45480,7 +45480,7 @@
       </c>
       <c r="F291" s="8" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="G291" s="8" t="inlineStr">
@@ -45516,7 +45516,7 @@
       </c>
       <c r="O291" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 114번) · 10-19 특정 음식 이름을 음식 종류로</t>
+          <t>10-13 추가(검수표 114번) · 10-19 특정 음식 이름을 음식 종류로 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="P291" s="8" t="inlineStr">
@@ -45557,7 +45557,7 @@
       </c>
       <c r="F292" s="8" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="G292" s="8" t="inlineStr">
@@ -45593,7 +45593,7 @@
       </c>
       <c r="O292" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 115번) · 10-19 특정 음식 이름을 음식 종류로</t>
+          <t>10-13 추가(검수표 115번) · 10-19 특정 음식 이름을 음식 종류로 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="P292" s="8" t="inlineStr">
@@ -45634,7 +45634,7 @@
       </c>
       <c r="F293" s="8" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="G293" s="8" t="inlineStr">
@@ -45670,7 +45670,7 @@
       </c>
       <c r="O293" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 116번) · 10-19 특정 음식 이름을 음식 종류로</t>
+          <t>10-13 추가(검수표 116번) · 10-19 특정 음식 이름을 음식 종류로 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="P293" s="8" t="inlineStr">
@@ -45711,7 +45711,7 @@
       </c>
       <c r="F294" s="8" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="G294" s="8" t="inlineStr">
@@ -45747,7 +45747,7 @@
       </c>
       <c r="O294" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 117번) · 10-19 특정 음식 이름을 음식 종류로</t>
+          <t>10-13 추가(검수표 117번) · 10-19 특정 음식 이름을 음식 종류로 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="P294" s="8" t="inlineStr">
@@ -46501,7 +46501,7 @@
       </c>
       <c r="F304" s="8" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="G304" s="8" t="inlineStr">
@@ -46541,7 +46541,7 @@
       </c>
       <c r="O304" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 127번) · 10-19 특정 음식 이름을 음식 종류로</t>
+          <t>10-13 추가(검수표 127번) · 10-19 특정 음식 이름을 음식 종류로 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="P304" s="8" t="inlineStr">
@@ -46898,7 +46898,7 @@
       </c>
       <c r="F309" s="8" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="G309" s="8" t="inlineStr">
@@ -46938,7 +46938,7 @@
       </c>
       <c r="O309" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 132번) · 10-19 특정 음식 이름을 음식 종류로</t>
+          <t>10-13 추가(검수표 132번) · 10-19 특정 음식 이름을 음식 종류로 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="P309" s="8" t="inlineStr">
@@ -46979,7 +46979,7 @@
       </c>
       <c r="F310" s="8" t="inlineStr">
         <is>
-          <t>입문</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="G310" s="8" t="inlineStr">
@@ -47019,7 +47019,7 @@
       </c>
       <c r="O310" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 133번) · 10-19 특정 음식 이름을 음식 종류로</t>
+          <t>10-13 추가(검수표 133번) · 10-19 특정 음식 이름을 음식 종류로 · 10-19 「A 대신 B」꼴은 기본 단계로</t>
         </is>
       </c>
       <c r="P310" s="8" t="inlineStr">

--- a/files/diet-reference-config-v1.0.0.xlsx
+++ b/files/diet-reference-config-v1.0.0.xlsx
@@ -2167,7 +2167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D58"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="60.58203125" customWidth="1" min="1" max="4"/>
@@ -2177,7 +2177,7 @@
     <row r="1">
       <c r="A1" s="23" t="inlineStr">
         <is>
-          <t>maiReport 식이 참조·설정 데이터 · v1.3.0</t>
+          <t>maiReport 식이 참조·설정 데이터 · v1.4.0</t>
         </is>
       </c>
       <c r="B1" s="24" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="C1" s="25" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="D1" s="1" t="n"/>
@@ -2195,7 +2195,7 @@
     <row r="2" ht="37.5" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>v1.0.0 발행 뒤 고친 내용을 반영한 v1.3.0입니다. 바뀐 것은 아래 「바뀐 내용」 표에 있습니다. 식이 문구 403개, 질문, 질환 규칙, 설정 기준을 제공합니다. 검진일로부터 3개월 이내 신호만 기존 식이 축에 연결합니다.</t>
+          <t>v1.0.0 발행 뒤 고친 내용을 반영한 v1.4.0입니다. 바뀐 것은 아래 「바뀐 내용」 표에 있습니다. 식이 문구 403개, 질문, 질환 규칙, 설정 기준을 제공합니다. 검진일로부터 3개월 이내 신호만 기존 식이 축에 연결합니다.</t>
         </is>
       </c>
       <c r="B2" s="3" t="n"/>
@@ -2884,7 +2884,7 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>바뀐 내용 · 2026-10-14</t>
+          <t>바뀐 내용 · 2026-10-19</t>
         </is>
       </c>
       <c r="B47" s="4" t="n"/>
@@ -2894,7 +2894,7 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>v1.1.0 · v1.2.0 · v1.3.0에서 바꾼 것. 파일 이름은 v1.0.0 그대로 둔다.</t>
+          <t>v1.1.0 · v1.2.0 · v1.3.0 · v1.4.0에서 바꾼 것. 파일 이름은 v1.0.0 그대로 둔다.</t>
         </is>
       </c>
       <c r="B48" s="4" t="n"/>
@@ -3102,6 +3102,116 @@
       <c r="D58" s="26" t="inlineStr">
         <is>
           <t>구현기준 R-11 ⑤ · 검증규칙 V-57 · 설정 CFG-079 · 080 사용 안 함 · 필드정의 diet_meal_time</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="26" t="inlineStr">
+        <is>
+          <t>문구 일반화 · 특정 음식 (v1.4.0 · 10-19)</t>
+        </is>
+      </c>
+      <c r="B59" s="26" t="inlineStr">
+        <is>
+          <t>「라면 국물은 남기기」「치킨 대신 닭백숙」「김치는 백김치로」처럼 특정 음식 이름이 들어가 그 음식을 안 먹는 사람에게는 어색함</t>
+        </is>
+      </c>
+      <c r="C59" s="26" t="inlineStr">
+        <is>
+          <t>음식 이름을 음식 종류로 바꿈. 예: 라면 국물은 남기기 → 국물 음식은 국물 남기기, 치킨 대신 닭백숙 → 튀긴 닭 대신 삶은 닭, 김치는 백김치로 → 절임 반찬은 덜 짠 것으로. 함께 세 끼 어제처럼 먹기 → 세 끼 제때 먹기, 저녁 어제처럼 먹기 → 저녁은 제때 먹기, 한 숟갈 양을 절반으로 → 한 숟갈 양, 절반만, 다음 끼니는 챙기기 → 다음 끼니 잘 챙기기. 문구 ID · 축 · 단계 · 성격 · 노출조건은 그대로. 대상 DIET-P-0004 · DIET-P-0033 · DIET-P-0054 · DIET-P-0056 · DIET-P-0078 · DIET-P-0107 · DIET-P-0110 · DIET-P-0114 · DIET-P-0215 · DIET-P-0267 · DIET-P-0287 · DIET-P-0289 · DIET-P-0293 · DIET-P-0306 · DIET-P-0313 · DIET-P-0315 · DIET-P-0334 · DIET-P-0344 · DIET-P-0345 · DIET-P-0359 · DIET-P-0379 · DIET-P-0380 · DIET-P-0383 · DIET-P-0384 · DIET-P-0385 · DIET-P-0386 · DIET-P-0387 · DIET-P-0388 · DIET-P-0389 · DIET-P-0390 · DIET-P-0392 · DIET-P-0394 · DIET-P-0395 · DIET-P-0396 · DIET-P-0397 · DIET-P-0398 · DIET-P-0400 · DIET-P-0401 · DIET-P-0402 · DIET-P-0403 · DIET-P-0404 · DIET-P-0405 · DIET-P-0406</t>
+        </is>
+      </c>
+      <c r="D59" s="26" t="inlineStr">
+        <is>
+          <t>문구세트 타일 문구 · 글자수 · 풀어 쓴 문구 · 이유 한 줄 · 적용 메모</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="26" t="inlineStr">
+        <is>
+          <t>문구 일반화 · 혼자 · 가족 · 도시락 (10-19)</t>
+        </is>
+      </c>
+      <c r="B60" s="26" t="inlineStr">
+        <is>
+          <t>「혼밥에도」「도시락에」「가족 반찬에」「함께 먹는 끼니」처럼 혼자 사는지 · 가족이 있는지 · 도시락을 싸는지를 전제함</t>
+        </is>
+      </c>
+      <c r="C60" s="26" t="inlineStr">
+        <is>
+          <t>누구나 쓸 수 있게 바꿈. 예: 혼밥에도 채소 한 가지 → 간단히 먹어도 채소 하나, 도시락에 달걀 하나 → 달걀 반찬 하나 챙기기, 가족 반찬에 채소 하나 → 상 차릴 때 채소 하나 더, 함께 먹는 끼니 정하기 → 하루 한 끼는 여유 있게. 대상 DIET-P-0204 · DIET-P-0205 · DIET-P-0206 · DIET-P-0207 · DIET-P-0208 · DIET-P-0209 · DIET-P-0210 · DIET-P-0211 · DIET-P-0212 · DIET-P-0213 · DIET-P-0328 · DIET-P-0378</t>
+        </is>
+      </c>
+      <c r="D60" s="26" t="inlineStr">
+        <is>
+          <t>문구세트 같은 열</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="26" t="inlineStr">
+        <is>
+          <t>입문 문구 넓히기 (10-19)</t>
+        </is>
+      </c>
+      <c r="B61" s="26" t="inlineStr">
+        <is>
+          <t>입문 단계에 「면 국물은 반만」「면 요리에 달걀 하나」「분말 스프는 반만」처럼 음식 종류가 좁은 문구가 있음</t>
+        </is>
+      </c>
+      <c r="C61" s="26" t="inlineStr">
+        <is>
+          <t>입문은 누구나 바로 할 수 있게 넓게 씀. 예: 국물 음식은 절반만, 끓일 때 달걀 하나 넣기, 양념은 절반만 넣기. 대상 DIET-P-0215 · DIET-P-0344 · DIET-P-0394 · DIET-P-0397 · DIET-P-0403</t>
+        </is>
+      </c>
+      <c r="D61" s="26" t="inlineStr">
+        <is>
+          <t>문구세트 같은 열</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="26" t="inlineStr">
+        <is>
+          <t>문구 다듬기 · 효과가 드러나게 (10-19)</t>
+        </is>
+      </c>
+      <c r="B62" s="26" t="inlineStr">
+        <is>
+          <t>「마실 것 미리 정하기」「내일 쓸 두부 준비하기」「마가린·쇼트닝 빼기」「저녁은 매일 7시쯤」이 무엇을 위한 것인지 모호하거나 특정 시각을 전제함</t>
+        </is>
+      </c>
+      <c r="C62" s="26" t="inlineStr">
+        <is>
+          <t>오늘 마실 음료 정하기 · 내일 두부 반찬 준비하기 · 트랜스지방 없는 하루 · 저녁은 매일 같은 시간에. 앞 둘은 풀어 쓴 문구에 효과 한 문장을 덧붙임(예: 정해 두면 단 음료를 충동적으로 고르는 일이 줄어요). 대상 DIET-P-0231 · DIET-P-0236 · DIET-P-0241 · DIET-P-0325</t>
+        </is>
+      </c>
+      <c r="D62" s="26" t="inlineStr">
+        <is>
+          <t>문구세트 같은 열</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="26" t="inlineStr">
+        <is>
+          <t>입문 「A 대신 B」 → 기본 단계 (10-19)</t>
+        </is>
+      </c>
+      <c r="B63" s="26" t="inlineStr">
+        <is>
+          <t>입문 단계에 「국 대신 나물 반찬」「튀김 대신 구이 · 찜」처럼 무엇을 먹고 있다는 전제가 있는 바꾸기 문구 20개가 있음</t>
+        </is>
+      </c>
+      <c r="C63" s="26" t="inlineStr">
+        <is>
+          <t>20개를 입문 → 기본 단계로 옮김(야식 대신 물 한 잔 · 야식 대신 따뜻한 차는 입문 유지). 문구 ID · 문구 버전 · 축은 그대로. 옮긴 뒤에도 축마다 입문 문구 17개 이상. 대상 DIET-P-0044 · 0050 · 0075 · 0126 · 0260 · 0290 · 0298 · 0299 · 0379 · 0380 · 0384~0390 · 0400 · 0405 · 0406</t>
+        </is>
+      </c>
+      <c r="D63" s="26" t="inlineStr">
+        <is>
+          <t>문구세트 단계(입문 → 기본) · 적용 메모</t>
         </is>
       </c>
     </row>

--- a/files/diet-reference-config-v1.0.0.xlsx
+++ b/files/diet-reference-config-v1.0.0.xlsx
@@ -3179,12 +3179,12 @@
       </c>
       <c r="B62" s="26" t="inlineStr">
         <is>
-          <t>「마실 것 미리 정하기」「내일 쓸 두부 준비하기」「마가린·쇼트닝 빼기」「저녁은 매일 7시쯤」이 무엇을 위한 것인지 모호하거나 특정 시각을 전제함</t>
+          <t>「마실 것 미리 정하기」「내일 쓸 두부 준비하기」「마가린·쇼트닝 빼기」「저녁은 매일 7시쯤」「외식에도 채소 하나 더」가 무엇을 위한 것인지 모호하거나 특정 시각을 전제함</t>
         </is>
       </c>
       <c r="C62" s="26" t="inlineStr">
         <is>
-          <t>오늘 마실 음료 정하기 · 내일 두부 반찬 준비하기 · 트랜스지방 없는 하루 · 저녁은 매일 같은 시간에. 앞 둘은 풀어 쓴 문구에 효과 한 문장을 덧붙임(예: 정해 두면 단 음료를 충동적으로 고르는 일이 줄어요). 대상 DIET-P-0231 · DIET-P-0236 · DIET-P-0241 · DIET-P-0325</t>
+          <t>오늘 마실 음료 정하기 · 내일 두부 반찬 준비하기 · 트랜스지방 없는 하루 · 저녁은 매일 같은 시간에 · 외식 메뉴는 채소 위주로. 앞 둘은 풀어 쓴 문구에 효과 한 문장을 덧붙임(예: 정해 두면 단 음료를 충동적으로 고르는 일이 줄어요). 대상 DIET-P-0046 · DIET-P-0231 · DIET-P-0236 · DIET-P-0241 · DIET-P-0325</t>
         </is>
       </c>
       <c r="D62" s="26" t="inlineStr">
@@ -25298,20 +25298,20 @@
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>외식에도 채소 하나 더</t>
+          <t>외식 메뉴는 채소 위주로</t>
         </is>
       </c>
       <c r="H38" s="8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>밖에서 먹을 때도 채소가 들어간 메뉴나 반찬을 하나 더 골라 보세요.</t>
+          <t>밖에서 먹을 때는 비빔밥 · 쌈밥처럼 채소가 많이 든 메뉴를 골라 보세요.</t>
         </is>
       </c>
       <c r="J38" s="14" t="inlineStr">
         <is>
-          <t>외식할 때 채소 메뉴가 있는지 살펴봐요.</t>
+          <t>채소가 많은 메뉴를 고르면 외식에서도 채소를 챙겨요.</t>
         </is>
       </c>
       <c r="K38" s="13" t="inlineStr">
@@ -25332,7 +25332,7 @@
       </c>
       <c r="O38" s="14" t="inlineStr">
         <is>
-          <t>근거 범위에 맞춰 이유 문장 수정</t>
+          <t>근거 범위에 맞춰 이유 문장 수정 · 10-19 외식 메뉴 고르기로</t>
         </is>
       </c>
       <c r="P38" s="13" t="inlineStr">

--- a/files/diet-reference-config-v1.0.0.xlsx
+++ b/files/diet-reference-config-v1.0.0.xlsx
@@ -3184,7 +3184,7 @@
       </c>
       <c r="C62" s="26" t="inlineStr">
         <is>
-          <t>오늘 마실 음료 정하기 · 내일 두부 반찬 준비하기 · 트랜스지방 없는 하루 · 저녁은 매일 같은 시간에 · 외식 메뉴는 채소 위주로. 앞 둘은 풀어 쓴 문구에 효과 한 문장을 덧붙임(예: 정해 두면 단 음료를 충동적으로 고르는 일이 줄어요). 대상 DIET-P-0046 · DIET-P-0231 · DIET-P-0236 · DIET-P-0241 · DIET-P-0325</t>
+          <t>오늘 마실 음료 정하기 · 내일 두부 반찬 준비하기 · 트랜스지방 없는 하루 · 저녁은 매일 같은 시간에 · 외식 메뉴, 채소 곁들이기. 앞 둘은 풀어 쓴 문구에 효과 한 문장을 덧붙임(예: 정해 두면 단 음료를 충동적으로 고르는 일이 줄어요). 대상 DIET-P-0046 · DIET-P-0231 · DIET-P-0236 · DIET-P-0241 · DIET-P-0325</t>
         </is>
       </c>
       <c r="D62" s="26" t="inlineStr">
@@ -25298,20 +25298,20 @@
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>외식 메뉴는 채소 위주로</t>
+          <t>외식 메뉴, 채소 곁들이기</t>
         </is>
       </c>
       <c r="H38" s="8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>밖에서 먹을 때는 비빔밥 · 쌈밥처럼 채소가 많이 든 메뉴를 골라 보세요.</t>
+          <t>밖에서 먹을 때도 나물 · 쌈 같은 채소 반찬을 곁들여 드세요.</t>
         </is>
       </c>
       <c r="J38" s="14" t="inlineStr">
         <is>
-          <t>채소가 많은 메뉴를 고르면 외식에서도 채소를 챙겨요.</t>
+          <t>채소를 곁들이면 외식에서도 채소를 챙겨요.</t>
         </is>
       </c>
       <c r="K38" s="13" t="inlineStr">
@@ -25332,7 +25332,7 @@
       </c>
       <c r="O38" s="14" t="inlineStr">
         <is>
-          <t>근거 범위에 맞춰 이유 문장 수정 · 10-19 외식 메뉴 고르기로</t>
+          <t>근거 범위에 맞춰 이유 문장 수정 · 10-19 외식 메뉴 고르기로 · 10-19 외식 메뉴에 채소 곁들이기로</t>
         </is>
       </c>
       <c r="P38" s="13" t="inlineStr">

--- a/files/diet-reference-config-v1.0.0.xlsx
+++ b/files/diet-reference-config-v1.0.0.xlsx
@@ -3184,7 +3184,7 @@
       </c>
       <c r="C62" s="26" t="inlineStr">
         <is>
-          <t>오늘 마실 음료 정하기 · 내일 두부 반찬 준비하기 · 트랜스지방 없는 하루 · 저녁은 매일 같은 시간에 · 외식 메뉴, 채소 곁들이기. 앞 둘은 풀어 쓴 문구에 효과 한 문장을 덧붙임(예: 정해 두면 단 음료를 충동적으로 고르는 일이 줄어요). 대상 DIET-P-0046 · DIET-P-0231 · DIET-P-0236 · DIET-P-0241 · DIET-P-0325</t>
+          <t>오늘 마실 음료 정하기 · 내일 두부 반찬 준비하기 · 트랜스지방 없는 하루 · 저녁은 매일 같은 시간에 · 외식 메뉴, 채소 곁들이기 · 먹기 편한 시간 적어보기. 앞 둘은 풀어 쓴 문구에 효과 한 문장을 덧붙임(예: 정해 두면 단 음료를 충동적으로 고르는 일이 줄어요). 대상 DIET-P-0292 · DIET-P-0046 · DIET-P-0231 · DIET-P-0236 · DIET-P-0241 · DIET-P-0325</t>
         </is>
       </c>
       <c r="D62" s="26" t="inlineStr">
@@ -38164,7 +38164,7 @@
       </c>
       <c r="G196" s="8" t="inlineStr">
         <is>
-          <t>먹기 편한 시간 적기</t>
+          <t>먹기 편한 시간 적어보기</t>
         </is>
       </c>
       <c r="H196" s="8">
@@ -38195,7 +38195,7 @@
       </c>
       <c r="O196" s="4" t="inlineStr">
         <is>
-          <t>10-13 추가(검수표 19번)</t>
+          <t>10-13 추가(검수표 19번) · 10-19 「적어보기」로</t>
         </is>
       </c>
       <c r="P196" s="8" t="inlineStr">

--- a/files/diet-reference-config-v1.0.0.xlsx
+++ b/files/diet-reference-config-v1.0.0.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="1520" yWindow="1520" windowWidth="28800" windowHeight="15360" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="760" yWindow="760" windowWidth="28800" windowHeight="15370" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="안내" sheetId="1" state="visible" r:id="rId1"/>
@@ -27,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="21">
     <font>
       <name val="Carlito"/>
       <sz val="11"/>
@@ -74,18 +74,8 @@
       <sz val="10"/>
     </font>
     <font>
-      <name val="Carlito"/>
-      <sz val="10"/>
-    </font>
-    <font>
       <name val="Arial"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Carlito"/>
       <b val="1"/>
       <color rgb="FF000000"/>
       <sz val="10"/>
@@ -107,8 +97,64 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FFFF0000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFF0000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <b val="1"/>
+      <color rgb="FFC00000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFC00000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <b val="1"/>
+      <color rgb="FF1F4E79"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF1F4E79"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <b val="1"/>
+      <color rgb="FF375623"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF375623"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00D92D20"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -136,6 +182,24 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE0E0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -150,7 +214,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
@@ -188,36 +252,36 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="13" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="14" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -225,6 +289,27 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2167,11 +2252,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D63"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="60.58203125" customWidth="1" min="1" max="4"/>
-    <col width="10.58203125" customWidth="1" min="5" max="5"/>
+    <col width="11.58203125" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2891,22 +2976,17 @@
       <c r="C47" s="4" t="n"/>
       <c r="D47" s="4" t="n"/>
     </row>
-    <row r="48">
+    <row r="48" ht="37.5" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>v1.1.0 · v1.2.0 · v1.3.0 · v1.4.0에서 바꾼 것. 파일 이름은 v1.0.0 그대로 둔다.</t>
+          <t>v1.1.0 · v1.2.0 · v1.3.0 · v1.4.0에서 바꾼 것. 파일 이름은 v1.0.0 그대로 둔다. · 최근 것이 위 · 반영 완료 8건은 맨 아래에 숨김(행 번호 사이를 우클릭 → 숨기기 취소)</t>
         </is>
       </c>
       <c r="B48" s="4" t="n"/>
       <c r="C48" s="4" t="n"/>
       <c r="D48" s="4" t="n"/>
     </row>
-    <row r="49">
-      <c r="A49" s="4" t="n"/>
-      <c r="B49" s="4" t="n"/>
-      <c r="C49" s="4" t="n"/>
-      <c r="D49" s="4" t="n"/>
-    </row>
+    <row r="49"/>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
@@ -2928,290 +3008,387 @@
           <t>바뀐 자리</t>
         </is>
       </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="26" t="inlineStr">
-        <is>
-          <t>목표 문구 227개 추가</t>
-        </is>
-      </c>
-      <c r="B51" s="26" t="inlineStr">
-        <is>
-          <t>저녁·새벽 식후 문구 15개 · 입문 문구 부족으로 같은 문구 반복</t>
-        </is>
-      </c>
-      <c r="C51" s="26" t="inlineStr">
-        <is>
-          <t>문구세트 · 노출조건에 DIET-P-0274~0500 227개 추가(데이터계약과 같은 값)</t>
-        </is>
-      </c>
-      <c r="D51" s="26" t="inlineStr">
-        <is>
-          <t>문구세트 · 노출조건 시트 추가 행</t>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>상태</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="52" customHeight="1">
+      <c r="A51" s="31" t="inlineStr">
+        <is>
+          <t>목표 문구 반복 방지 조회 기간 (10-19)</t>
+        </is>
+      </c>
+      <c r="B51" s="31" t="inlineStr">
+        <is>
+          <t>최근 노출 조회 기간이 30일이라, 30일이 지난 문구가 한 번도 안 나온 문구와 같은 줄에 서고 번호가 앞이라 다시 뽑힘. 축 · 단계마다 목록 앞 몇 개만 돌고 문구 393개 중 138개가 1년 내내 안 나옴</t>
+        </is>
+      </c>
+      <c r="C51" s="31" t="inlineStr">
+        <is>
+          <t>조회 기간을 365일로 늘림. 365일 안에 안 나온 문구를 phrase_id 순으로 먼저, 모두 나왔으면 마지막 노출이 가장 오래된 문구를 고름. 고르는 방식은 그대로. 예: 일반 · 13시 · 단 음료 입문 사용자가 1년간 보는 문구 6개 → 11개 전부. 1년 안에 나올 수 있는 문구 255개 → 332개</t>
+        </is>
+      </c>
+      <c r="D51" s="31" t="inlineStr">
+        <is>
+          <t>설정값 CFG-065 · 설정파라미터 CFG-065</t>
+        </is>
+      </c>
+      <c r="E51" s="32" t="inlineStr">
+        <is>
+          <t>변경 필요</t>
         </is>
       </c>
     </row>
     <row r="52" ht="39" customHeight="1">
       <c r="A52" s="26" t="inlineStr">
         <is>
+          <t>식사 시각 추정 단순화 (10-14)</t>
+        </is>
+      </c>
+      <c r="B52" s="26" t="inlineStr">
+        <is>
+          <t>추정 순서에 걸음 멈춤 단서(CFG-079)와 지난 2주 평소 시각(CFG-080)이 있었음</t>
+        </is>
+      </c>
+      <c r="C52" s="26" t="inlineStr">
+        <is>
+          <t>둘 다 1차에서 뺌. 추정은 건강 앱 식사 기록 → 선택지 범위의 가운데 두 단계. 건강 앱 기록은 끼니 구분이 없고 선택지 추정값은 가운데값이라 평소 시각이 믿을 만하지 않음. 식후 걸음 판정 결과(모의 87~89%)는 그대로</t>
+        </is>
+      </c>
+      <c r="D52" s="26" t="inlineStr">
+        <is>
+          <t>구현기준 R-11 ⑤ · 검증규칙 V-57 · 설정 CFG-079 · 080 사용 안 함 · 필드정의 diet_meal_time</t>
+        </is>
+      </c>
+      <c r="E52" s="33" t="inlineStr">
+        <is>
+          <t>전달 전</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="26" customHeight="1">
+      <c r="A53" s="26" t="inlineStr">
+        <is>
+          <t>저녁 선택지 (10-14)</t>
+        </is>
+      </c>
+      <c r="B53" s="26" t="inlineStr">
+        <is>
+          <t>저녁 9시 뒤 · 이른 저녁이 선택지에 안 들어갔음</t>
+        </is>
+      </c>
+      <c r="C53" s="26" t="inlineStr">
+        <is>
+          <t>축정의 12행 저녁 9시 뒤 고정 선택지(DIET-Q-11) 추가, 11행 어제 저녁 선택지를 「7시 이전 / 7시~9시 / 9시 이후」로, 설정값 CFG-077 · 089 · 090</t>
+        </is>
+      </c>
+      <c r="D53" s="26" t="inlineStr">
+        <is>
+          <t>축정의 · 설정값 · 설정파라미터</t>
+        </is>
+      </c>
+      <c r="E53" s="33" t="inlineStr">
+        <is>
+          <t>전달 전</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="26" customHeight="1">
+      <c r="A54" s="26" t="inlineStr">
+        <is>
+          <t>시각 단계 선택지 글자 · 어제 저녁 질문 (10-14)</t>
+        </is>
+      </c>
+      <c r="B54" s="26" t="inlineStr">
+        <is>
+          <t>선택지 큰 글자가 시각이라 길고, 어제 저녁은 묻지 않았음</t>
+        </is>
+      </c>
+      <c r="C54" s="26" t="inlineStr">
+        <is>
+          <t>축정의 9행 선택지를 「1시간 이내 / 1~2시간 전 / 그보다 전」으로, 11행 어제 저녁(DIET-Q-10) 추가, 설정값 CFG-089</t>
+        </is>
+      </c>
+      <c r="D54" s="26" t="inlineStr">
+        <is>
+          <t>축정의 · 설정값 · 설정파라미터</t>
+        </is>
+      </c>
+      <c r="E54" s="33" t="inlineStr">
+        <is>
+          <t>전달 전</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="26" customHeight="1">
+      <c r="A55" s="26" t="inlineStr">
+        <is>
+          <t>식후 행동 판정 기준 추가 (10-14)</t>
+        </is>
+      </c>
+      <c r="B55" s="26" t="inlineStr">
+        <is>
+          <t>식후에 걸었는지 판정 기준이 없었음</t>
+        </is>
+      </c>
+      <c r="C55" s="26" t="inlineStr">
+        <is>
+          <t>설정값 CFG-086~088(5분 초과 이어 걷기 · 300보 · 운동 기록) 추가. 데이터계약 R-12와 같은 값</t>
+        </is>
+      </c>
+      <c r="D55" s="26" t="inlineStr">
+        <is>
+          <t>설정값 · 설정파라미터</t>
+        </is>
+      </c>
+      <c r="E55" s="33" t="inlineStr">
+        <is>
+          <t>전달 전</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="39" customHeight="1">
+      <c r="A56" s="26" t="inlineStr">
+        <is>
+          <t>끼니별 식사 시각 단계 추가 (v1.3.0 · 10-14)</t>
+        </is>
+      </c>
+      <c r="B56" s="26" t="inlineStr">
+        <is>
+          <t>식사 시각을 받는 질문이 없어 자기돌봄 · 일상안정의 식후 행동 칸이 비어 있음</t>
+        </is>
+      </c>
+      <c r="C56" s="26" t="inlineStr">
+        <is>
+          <t>축정의에 이어 묻는 질문 2행(DIET-Q-08 점심·저녁 「{끼니}은 언제쯤 드셨어요?」 · DIET-Q-09 「아침은 몇 시쯤 드셨어요?」, 축 아님 · 점수 없음) 추가. 설정값 · 설정파라미터에 CFG-072~085(버튼 간격 · 내림 · 선택지 상한 시각 · 끼니 시작 기본값 · 아침 경계 · 추정 임시값 · 질문 수) 추가(데이터계약과 같은 값)</t>
+        </is>
+      </c>
+      <c r="D56" s="26" t="inlineStr">
+        <is>
+          <t>축정의 9~10행 · 설정값 · 설정파라미터 · 안내 시트 표</t>
+        </is>
+      </c>
+      <c r="E56" s="33" t="inlineStr">
+        <is>
+          <t>전달 전</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" hidden="1" ht="52" customHeight="1">
+      <c r="A57" s="26" t="inlineStr">
+        <is>
+          <t>입문 「A 대신 B」 → 기본 단계 (10-19)</t>
+        </is>
+      </c>
+      <c r="B57" s="26" t="inlineStr">
+        <is>
+          <t>입문 단계에 「국 대신 나물 반찬」「튀김 대신 구이 · 찜」처럼 무엇을 먹고 있다는 전제가 있는 바꾸기 문구 20개가 있음</t>
+        </is>
+      </c>
+      <c r="C57" s="26" t="inlineStr">
+        <is>
+          <t>20개를 입문 → 기본 단계로 옮김(야식 대신 물 한 잔 · 야식 대신 따뜻한 차는 입문 유지). 문구 ID · 문구 버전 · 축은 그대로. 옮긴 뒤에도 축마다 입문 문구 17개 이상. 대상 DIET-P-0044 · 0050 · 0075 · 0126 · 0260 · 0290 · 0298 · 0299 · 0379 · 0380 · 0384~0390 · 0400 · 0405 · 0406</t>
+        </is>
+      </c>
+      <c r="D57" s="26" t="inlineStr">
+        <is>
+          <t>문구세트 단계(입문 → 기본) · 적용 메모</t>
+        </is>
+      </c>
+      <c r="E57" s="34" t="inlineStr">
+        <is>
+          <t>반영 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" hidden="1" ht="65" customHeight="1">
+      <c r="A58" s="26" t="inlineStr">
+        <is>
+          <t>문구 다듬기 · 효과가 드러나게 (10-19)</t>
+        </is>
+      </c>
+      <c r="B58" s="26" t="inlineStr">
+        <is>
+          <t>「마실 것 미리 정하기」「내일 쓸 두부 준비하기」「마가린·쇼트닝 빼기」「저녁은 매일 7시쯤」「외식에도 채소 하나 더」가 무엇을 위한 것인지 모호하거나 특정 시각을 전제함</t>
+        </is>
+      </c>
+      <c r="C58" s="26" t="inlineStr">
+        <is>
+          <t>오늘 마실 음료 정하기 · 내일 두부 반찬 준비하기 · 트랜스지방 없는 하루 · 저녁은 매일 같은 시간에 · 외식 메뉴, 채소 곁들이기 · 먹기 편한 시간 적어보기. 앞 둘은 풀어 쓴 문구에 효과 한 문장을 덧붙임(예: 정해 두면 단 음료를 충동적으로 고르는 일이 줄어요). 대상 DIET-P-0292 · DIET-P-0046 · DIET-P-0231 · DIET-P-0236 · DIET-P-0241 · DIET-P-0325</t>
+        </is>
+      </c>
+      <c r="D58" s="26" t="inlineStr">
+        <is>
+          <t>문구세트 같은 열</t>
+        </is>
+      </c>
+      <c r="E58" s="34" t="inlineStr">
+        <is>
+          <t>반영 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" hidden="1" ht="39" customHeight="1">
+      <c r="A59" s="26" t="inlineStr">
+        <is>
+          <t>입문 문구 넓히기 (10-19)</t>
+        </is>
+      </c>
+      <c r="B59" s="26" t="inlineStr">
+        <is>
+          <t>입문 단계에 「면 국물은 반만」「면 요리에 달걀 하나」「분말 스프는 반만」처럼 음식 종류가 좁은 문구가 있음</t>
+        </is>
+      </c>
+      <c r="C59" s="26" t="inlineStr">
+        <is>
+          <t>입문은 누구나 바로 할 수 있게 넓게 씀. 예: 국물 음식은 절반만, 끓일 때 달걀 하나 넣기, 양념은 절반만 넣기. 대상 DIET-P-0215 · DIET-P-0344 · DIET-P-0394 · DIET-P-0397 · DIET-P-0403</t>
+        </is>
+      </c>
+      <c r="D59" s="26" t="inlineStr">
+        <is>
+          <t>문구세트 같은 열</t>
+        </is>
+      </c>
+      <c r="E59" s="34" t="inlineStr">
+        <is>
+          <t>반영 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" hidden="1" ht="78" customHeight="1">
+      <c r="A60" s="26" t="inlineStr">
+        <is>
+          <t>문구 일반화 · 혼자 · 가족 · 도시락 (10-19)</t>
+        </is>
+      </c>
+      <c r="B60" s="26" t="inlineStr">
+        <is>
+          <t>「혼밥에도」「도시락에」「가족 반찬에」「함께 먹는 끼니」처럼 혼자 사는지 · 가족이 있는지 · 도시락을 싸는지를 전제함</t>
+        </is>
+      </c>
+      <c r="C60" s="26" t="inlineStr">
+        <is>
+          <t>누구나 쓸 수 있게 바꿈. 예: 혼밥에도 채소 한 가지 → 간단히 먹어도 채소 하나, 도시락에 달걀 하나 → 달걀 반찬 하나 챙기기, 가족 반찬에 채소 하나 → 상 차릴 때 채소 하나 더, 함께 먹는 끼니 정하기 → 하루 한 끼는 여유 있게. 대상 DIET-P-0204 · DIET-P-0205 · DIET-P-0206 · DIET-P-0207 · DIET-P-0208 · DIET-P-0209 · DIET-P-0210 · DIET-P-0211 · DIET-P-0212 · DIET-P-0213 · DIET-P-0328 · DIET-P-0378</t>
+        </is>
+      </c>
+      <c r="D60" s="26" t="inlineStr">
+        <is>
+          <t>문구세트 같은 열</t>
+        </is>
+      </c>
+      <c r="E60" s="34" t="inlineStr">
+        <is>
+          <t>반영 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" hidden="1" ht="182" customHeight="1">
+      <c r="A61" s="26" t="inlineStr">
+        <is>
+          <t>문구 일반화 · 특정 음식 (v1.4.0 · 10-19)</t>
+        </is>
+      </c>
+      <c r="B61" s="26" t="inlineStr">
+        <is>
+          <t>「라면 국물은 남기기」「치킨 대신 닭백숙」「김치는 백김치로」처럼 특정 음식 이름이 들어가 그 음식을 안 먹는 사람에게는 어색함</t>
+        </is>
+      </c>
+      <c r="C61" s="26" t="inlineStr">
+        <is>
+          <t>음식 이름을 음식 종류로 바꿈. 예: 라면 국물은 남기기 → 국물 음식은 국물 남기기, 치킨 대신 닭백숙 → 튀긴 닭 대신 삶은 닭, 김치는 백김치로 → 절임 반찬은 덜 짠 것으로. 함께 세 끼 어제처럼 먹기 → 세 끼 제때 먹기, 저녁 어제처럼 먹기 → 저녁은 제때 먹기, 한 숟갈 양을 절반으로 → 한 숟갈 양, 절반만, 다음 끼니는 챙기기 → 다음 끼니 잘 챙기기. 문구 ID · 축 · 단계 · 성격 · 노출조건은 그대로. 대상 DIET-P-0004 · DIET-P-0033 · DIET-P-0054 · DIET-P-0056 · DIET-P-0078 · DIET-P-0107 · DIET-P-0110 · DIET-P-0114 · DIET-P-0215 · DIET-P-0267 · DIET-P-0287 · DIET-P-0289 · DIET-P-0293 · DIET-P-0306 · DIET-P-0313 · DIET-P-0315 · DIET-P-0334 · DIET-P-0344 · DIET-P-0345 · DIET-P-0359 · DIET-P-0379 · DIET-P-0380 · DIET-P-0383 · DIET-P-0384 · DIET-P-0385 · DIET-P-0386 · DIET-P-0387 · DIET-P-0388 · DIET-P-0389 · DIET-P-0390 · DIET-P-0392 · DIET-P-0394 · DIET-P-0395 · DIET-P-0396 · DIET-P-0397 · DIET-P-0398 · DIET-P-0400 · DIET-P-0401 · DIET-P-0402 · DIET-P-0403 · DIET-P-0404 · DIET-P-0405 · DIET-P-0406</t>
+        </is>
+      </c>
+      <c r="D61" s="26" t="inlineStr">
+        <is>
+          <t>문구세트 타일 문구 · 글자수 · 풀어 쓴 문구 · 이유 한 줄 · 적용 메모</t>
+        </is>
+      </c>
+      <c r="E61" s="34" t="inlineStr">
+        <is>
+          <t>반영 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" hidden="1" ht="39" customHeight="1">
+      <c r="A62" s="26" t="inlineStr">
+        <is>
+          <t>세 번째 선택지 문구 바꿈</t>
+        </is>
+      </c>
+      <c r="B62" s="26" t="inlineStr">
+        <is>
+          <t>축정의 「끼니 규칙」 답 3번이 「거의 못 먹음」. 안내 「고정 문항의 한계」에 「거의 못 먹음과 결식은 분리 추정하지 않는다」</t>
+        </is>
+      </c>
+      <c r="C62" s="26" t="inlineStr">
+        <is>
+          <t>답 3번을 「거의 못 먹거나 거름」으로 바꿈(데이터계약과 같은 값). 안내 문장은 「「거의 못 먹거나 거름」은 거의 못 먹은 끼니와 거른 끼니를 나누지 않는다」로 고침</t>
+        </is>
+      </c>
+      <c r="D62" s="26" t="inlineStr">
+        <is>
+          <t>축정의 끼니 규칙 행 · 안내 「고정 문항의 한계」</t>
+        </is>
+      </c>
+      <c r="E62" s="34" t="inlineStr">
+        <is>
+          <t>반영 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" hidden="1" ht="39" customHeight="1">
+      <c r="A63" s="26" t="inlineStr">
+        <is>
           <t>풀어 쓴 문구 추가 (v1.2.0)</t>
         </is>
       </c>
-      <c r="B52" s="26" t="inlineStr">
+      <c r="B63" s="26" t="inlineStr">
         <is>
           <t>타일 문구가 12자로 짧아 무엇을 하라는 건지 알기 어려운 문구가 있음</t>
         </is>
       </c>
-      <c r="C52" s="26" t="inlineStr">
+      <c r="C63" s="26" t="inlineStr">
         <is>
           <t>문구세트에 「풀어 쓴 문구」 열 추가, 403개 모두 한 문장으로 채움(데이터계약 full_text와 같은 값) / 예: 「세 끼 어제처럼 먹기」 → 「오늘도 어제와 비슷한 시간에 아침·점심·저녁 세 끼를 드세요.」</t>
         </is>
       </c>
-      <c r="D52" s="26" t="inlineStr">
+      <c r="D63" s="26" t="inlineStr">
         <is>
           <t>문구세트 「풀어 쓴 문구」 열 · 열정의 · 안내 열 설명</t>
         </is>
       </c>
-    </row>
-    <row r="53" ht="39" customHeight="1">
-      <c r="A53" s="26" t="inlineStr">
-        <is>
-          <t>세 번째 선택지 문구 바꿈</t>
-        </is>
-      </c>
-      <c r="B53" s="26" t="inlineStr">
-        <is>
-          <t>축정의 「끼니 규칙」 답 3번이 「거의 못 먹음」. 안내 「고정 문항의 한계」에 「거의 못 먹음과 결식은 분리 추정하지 않는다」</t>
-        </is>
-      </c>
-      <c r="C53" s="26" t="inlineStr">
-        <is>
-          <t>답 3번을 「거의 못 먹거나 거름」으로 바꿈(데이터계약과 같은 값). 안내 문장은 「「거의 못 먹거나 거름」은 거의 못 먹은 끼니와 거른 끼니를 나누지 않는다」로 고침</t>
-        </is>
-      </c>
-      <c r="D53" s="26" t="inlineStr">
-        <is>
-          <t>축정의 끼니 규칙 행 · 안내 「고정 문항의 한계」</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="39" customHeight="1">
-      <c r="A54" s="26" t="inlineStr">
-        <is>
-          <t>끼니별 식사 시각 단계 추가 (v1.3.0 · 10-14)</t>
-        </is>
-      </c>
-      <c r="B54" s="26" t="inlineStr">
-        <is>
-          <t>식사 시각을 받는 질문이 없어 자기돌봄 · 일상안정의 식후 행동 칸이 비어 있음</t>
-        </is>
-      </c>
-      <c r="C54" s="26" t="inlineStr">
-        <is>
-          <t>축정의에 이어 묻는 질문 2행(DIET-Q-08 점심·저녁 「{끼니}은 언제쯤 드셨어요?」 · DIET-Q-09 「아침은 몇 시쯤 드셨어요?」, 축 아님 · 점수 없음) 추가. 설정값 · 설정파라미터에 CFG-072~085(버튼 간격 · 내림 · 선택지 상한 시각 · 끼니 시작 기본값 · 아침 경계 · 추정 임시값 · 질문 수) 추가(데이터계약과 같은 값)</t>
-        </is>
-      </c>
-      <c r="D54" s="26" t="inlineStr">
-        <is>
-          <t>축정의 9~10행 · 설정값 · 설정파라미터 · 안내 시트 표</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="26" t="inlineStr">
-        <is>
-          <t>식후 행동 판정 기준 추가 (10-14)</t>
-        </is>
-      </c>
-      <c r="B55" s="26" t="inlineStr">
-        <is>
-          <t>식후에 걸었는지 판정 기준이 없었음</t>
-        </is>
-      </c>
-      <c r="C55" s="26" t="inlineStr">
-        <is>
-          <t>설정값 CFG-086~088(5분 초과 이어 걷기 · 300보 · 운동 기록) 추가. 데이터계약 R-12와 같은 값</t>
-        </is>
-      </c>
-      <c r="D55" s="26" t="inlineStr">
-        <is>
-          <t>설정값 · 설정파라미터</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="26" t="inlineStr">
-        <is>
-          <t>시각 단계 선택지 글자 · 어제 저녁 질문 (10-14)</t>
-        </is>
-      </c>
-      <c r="B56" s="26" t="inlineStr">
-        <is>
-          <t>선택지 큰 글자가 시각이라 길고, 어제 저녁은 묻지 않았음</t>
-        </is>
-      </c>
-      <c r="C56" s="26" t="inlineStr">
-        <is>
-          <t>축정의 9행 선택지를 「1시간 이내 / 1~2시간 전 / 그보다 전」으로, 11행 어제 저녁(DIET-Q-10) 추가, 설정값 CFG-089</t>
-        </is>
-      </c>
-      <c r="D56" s="26" t="inlineStr">
-        <is>
-          <t>축정의 · 설정값 · 설정파라미터</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="26" t="inlineStr">
-        <is>
-          <t>저녁 선택지 (10-14)</t>
-        </is>
-      </c>
-      <c r="B57" s="26" t="inlineStr">
-        <is>
-          <t>저녁 9시 뒤 · 이른 저녁이 선택지에 안 들어갔음</t>
-        </is>
-      </c>
-      <c r="C57" s="26" t="inlineStr">
-        <is>
-          <t>축정의 12행 저녁 9시 뒤 고정 선택지(DIET-Q-11) 추가, 11행 어제 저녁 선택지를 「7시 이전 / 7시~9시 / 9시 이후」로, 설정값 CFG-077 · 089 · 090</t>
-        </is>
-      </c>
-      <c r="D57" s="26" t="inlineStr">
-        <is>
-          <t>축정의 · 설정값 · 설정파라미터</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="26" t="inlineStr">
-        <is>
-          <t>식사 시각 추정 단순화 (10-14)</t>
-        </is>
-      </c>
-      <c r="B58" s="26" t="inlineStr">
-        <is>
-          <t>추정 순서에 걸음 멈춤 단서(CFG-079)와 지난 2주 평소 시각(CFG-080)이 있었음</t>
-        </is>
-      </c>
-      <c r="C58" s="26" t="inlineStr">
-        <is>
-          <t>둘 다 1차에서 뺌. 추정은 건강 앱 식사 기록 → 선택지 범위의 가운데 두 단계. 건강 앱 기록은 끼니 구분이 없고 선택지 추정값은 가운데값이라 평소 시각이 믿을 만하지 않음. 식후 걸음 판정 결과(모의 87~89%)는 그대로</t>
-        </is>
-      </c>
-      <c r="D58" s="26" t="inlineStr">
-        <is>
-          <t>구현기준 R-11 ⑤ · 검증규칙 V-57 · 설정 CFG-079 · 080 사용 안 함 · 필드정의 diet_meal_time</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="26" t="inlineStr">
-        <is>
-          <t>문구 일반화 · 특정 음식 (v1.4.0 · 10-19)</t>
-        </is>
-      </c>
-      <c r="B59" s="26" t="inlineStr">
-        <is>
-          <t>「라면 국물은 남기기」「치킨 대신 닭백숙」「김치는 백김치로」처럼 특정 음식 이름이 들어가 그 음식을 안 먹는 사람에게는 어색함</t>
-        </is>
-      </c>
-      <c r="C59" s="26" t="inlineStr">
-        <is>
-          <t>음식 이름을 음식 종류로 바꿈. 예: 라면 국물은 남기기 → 국물 음식은 국물 남기기, 치킨 대신 닭백숙 → 튀긴 닭 대신 삶은 닭, 김치는 백김치로 → 절임 반찬은 덜 짠 것으로. 함께 세 끼 어제처럼 먹기 → 세 끼 제때 먹기, 저녁 어제처럼 먹기 → 저녁은 제때 먹기, 한 숟갈 양을 절반으로 → 한 숟갈 양, 절반만, 다음 끼니는 챙기기 → 다음 끼니 잘 챙기기. 문구 ID · 축 · 단계 · 성격 · 노출조건은 그대로. 대상 DIET-P-0004 · DIET-P-0033 · DIET-P-0054 · DIET-P-0056 · DIET-P-0078 · DIET-P-0107 · DIET-P-0110 · DIET-P-0114 · DIET-P-0215 · DIET-P-0267 · DIET-P-0287 · DIET-P-0289 · DIET-P-0293 · DIET-P-0306 · DIET-P-0313 · DIET-P-0315 · DIET-P-0334 · DIET-P-0344 · DIET-P-0345 · DIET-P-0359 · DIET-P-0379 · DIET-P-0380 · DIET-P-0383 · DIET-P-0384 · DIET-P-0385 · DIET-P-0386 · DIET-P-0387 · DIET-P-0388 · DIET-P-0389 · DIET-P-0390 · DIET-P-0392 · DIET-P-0394 · DIET-P-0395 · DIET-P-0396 · DIET-P-0397 · DIET-P-0398 · DIET-P-0400 · DIET-P-0401 · DIET-P-0402 · DIET-P-0403 · DIET-P-0404 · DIET-P-0405 · DIET-P-0406</t>
-        </is>
-      </c>
-      <c r="D59" s="26" t="inlineStr">
-        <is>
-          <t>문구세트 타일 문구 · 글자수 · 풀어 쓴 문구 · 이유 한 줄 · 적용 메모</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="26" t="inlineStr">
-        <is>
-          <t>문구 일반화 · 혼자 · 가족 · 도시락 (10-19)</t>
-        </is>
-      </c>
-      <c r="B60" s="26" t="inlineStr">
-        <is>
-          <t>「혼밥에도」「도시락에」「가족 반찬에」「함께 먹는 끼니」처럼 혼자 사는지 · 가족이 있는지 · 도시락을 싸는지를 전제함</t>
-        </is>
-      </c>
-      <c r="C60" s="26" t="inlineStr">
-        <is>
-          <t>누구나 쓸 수 있게 바꿈. 예: 혼밥에도 채소 한 가지 → 간단히 먹어도 채소 하나, 도시락에 달걀 하나 → 달걀 반찬 하나 챙기기, 가족 반찬에 채소 하나 → 상 차릴 때 채소 하나 더, 함께 먹는 끼니 정하기 → 하루 한 끼는 여유 있게. 대상 DIET-P-0204 · DIET-P-0205 · DIET-P-0206 · DIET-P-0207 · DIET-P-0208 · DIET-P-0209 · DIET-P-0210 · DIET-P-0211 · DIET-P-0212 · DIET-P-0213 · DIET-P-0328 · DIET-P-0378</t>
-        </is>
-      </c>
-      <c r="D60" s="26" t="inlineStr">
-        <is>
-          <t>문구세트 같은 열</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="26" t="inlineStr">
-        <is>
-          <t>입문 문구 넓히기 (10-19)</t>
-        </is>
-      </c>
-      <c r="B61" s="26" t="inlineStr">
-        <is>
-          <t>입문 단계에 「면 국물은 반만」「면 요리에 달걀 하나」「분말 스프는 반만」처럼 음식 종류가 좁은 문구가 있음</t>
-        </is>
-      </c>
-      <c r="C61" s="26" t="inlineStr">
-        <is>
-          <t>입문은 누구나 바로 할 수 있게 넓게 씀. 예: 국물 음식은 절반만, 끓일 때 달걀 하나 넣기, 양념은 절반만 넣기. 대상 DIET-P-0215 · DIET-P-0344 · DIET-P-0394 · DIET-P-0397 · DIET-P-0403</t>
-        </is>
-      </c>
-      <c r="D61" s="26" t="inlineStr">
-        <is>
-          <t>문구세트 같은 열</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="26" t="inlineStr">
-        <is>
-          <t>문구 다듬기 · 효과가 드러나게 (10-19)</t>
-        </is>
-      </c>
-      <c r="B62" s="26" t="inlineStr">
-        <is>
-          <t>「마실 것 미리 정하기」「내일 쓸 두부 준비하기」「마가린·쇼트닝 빼기」「저녁은 매일 7시쯤」「외식에도 채소 하나 더」가 무엇을 위한 것인지 모호하거나 특정 시각을 전제함</t>
-        </is>
-      </c>
-      <c r="C62" s="26" t="inlineStr">
-        <is>
-          <t>오늘 마실 음료 정하기 · 내일 두부 반찬 준비하기 · 트랜스지방 없는 하루 · 저녁은 매일 같은 시간에 · 외식 메뉴, 채소 곁들이기 · 먹기 편한 시간 적어보기. 앞 둘은 풀어 쓴 문구에 효과 한 문장을 덧붙임(예: 정해 두면 단 음료를 충동적으로 고르는 일이 줄어요). 대상 DIET-P-0292 · DIET-P-0046 · DIET-P-0231 · DIET-P-0236 · DIET-P-0241 · DIET-P-0325</t>
-        </is>
-      </c>
-      <c r="D62" s="26" t="inlineStr">
-        <is>
-          <t>문구세트 같은 열</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="26" t="inlineStr">
-        <is>
-          <t>입문 「A 대신 B」 → 기본 단계 (10-19)</t>
-        </is>
-      </c>
-      <c r="B63" s="26" t="inlineStr">
-        <is>
-          <t>입문 단계에 「국 대신 나물 반찬」「튀김 대신 구이 · 찜」처럼 무엇을 먹고 있다는 전제가 있는 바꾸기 문구 20개가 있음</t>
-        </is>
-      </c>
-      <c r="C63" s="26" t="inlineStr">
-        <is>
-          <t>20개를 입문 → 기본 단계로 옮김(야식 대신 물 한 잔 · 야식 대신 따뜻한 차는 입문 유지). 문구 ID · 문구 버전 · 축은 그대로. 옮긴 뒤에도 축마다 입문 문구 17개 이상. 대상 DIET-P-0044 · 0050 · 0075 · 0126 · 0260 · 0290 · 0298 · 0299 · 0379 · 0380 · 0384~0390 · 0400 · 0405 · 0406</t>
-        </is>
-      </c>
-      <c r="D63" s="26" t="inlineStr">
-        <is>
-          <t>문구세트 단계(입문 → 기본) · 적용 메모</t>
+      <c r="E63" s="34" t="inlineStr">
+        <is>
+          <t>반영 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" hidden="1">
+      <c r="A64" s="26" t="inlineStr">
+        <is>
+          <t>목표 문구 227개 추가</t>
+        </is>
+      </c>
+      <c r="B64" s="26" t="inlineStr">
+        <is>
+          <t>저녁·새벽 식후 문구 15개 · 입문 문구 부족으로 같은 문구 반복</t>
+        </is>
+      </c>
+      <c r="C64" s="26" t="inlineStr">
+        <is>
+          <t>문구세트 · 노출조건에 DIET-P-0274~0500 227개 추가(데이터계약과 같은 값)</t>
+        </is>
+      </c>
+      <c r="D64" s="26" t="inlineStr">
+        <is>
+          <t>문구세트 · 노출조건 시트 추가 행</t>
+        </is>
+      </c>
+      <c r="E64" s="34" t="inlineStr">
+        <is>
+          <t>반영 완료</t>
         </is>
       </c>
     </row>
@@ -23060,9 +23237,9 @@
           <t>입문</t>
         </is>
       </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>한 잔은 물로 바꾸기</t>
+      <c r="G10" s="35" t="inlineStr">
+        <is>
+          <t>단 음료 대신 물 한 잔</t>
         </is>
       </c>
       <c r="H10" s="8" t="n">
@@ -24371,7 +24548,7 @@
         </is>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="25" customHeight="1">
       <c r="A27" s="13" t="n">
         <v>33</v>
       </c>
@@ -25267,7 +25444,7 @@
         </is>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="25" customHeight="1">
       <c r="A38" s="13" t="n">
         <v>46</v>
       </c>
@@ -26007,7 +26184,7 @@
         </is>
       </c>
     </row>
-    <row r="47">
+    <row r="47" ht="25" customHeight="1">
       <c r="A47" s="13" t="n">
         <v>56</v>
       </c>
@@ -28327,7 +28504,7 @@
         </is>
       </c>
     </row>
-    <row r="75">
+    <row r="75" ht="25" customHeight="1">
       <c r="A75" s="13" t="n">
         <v>107</v>
       </c>
@@ -29075,7 +29252,7 @@
         </is>
       </c>
     </row>
-    <row r="84">
+    <row r="84" ht="25" customHeight="1">
       <c r="A84" s="13" t="n">
         <v>126</v>
       </c>
@@ -31467,7 +31644,7 @@
         </is>
       </c>
     </row>
-    <row r="113">
+    <row r="113" ht="25" customHeight="1">
       <c r="A113" s="13" t="n">
         <v>205</v>
       </c>
@@ -31719,7 +31896,7 @@
         </is>
       </c>
     </row>
-    <row r="116">
+    <row r="116" ht="25" customHeight="1">
       <c r="A116" s="13" t="n">
         <v>208</v>
       </c>
@@ -31803,7 +31980,7 @@
         </is>
       </c>
     </row>
-    <row r="117">
+    <row r="117" ht="25" customHeight="1">
       <c r="A117" s="13" t="n">
         <v>209</v>
       </c>
@@ -32055,7 +32232,7 @@
         </is>
       </c>
     </row>
-    <row r="120">
+    <row r="120" ht="25" customHeight="1">
       <c r="A120" s="13" t="n">
         <v>212</v>
       </c>
@@ -32303,7 +32480,7 @@
         </is>
       </c>
     </row>
-    <row r="123">
+    <row r="123" ht="25" customHeight="1">
       <c r="A123" s="13" t="n">
         <v>215</v>
       </c>
@@ -33759,7 +33936,7 @@
         </is>
       </c>
     </row>
-    <row r="141">
+    <row r="141" ht="25" customHeight="1">
       <c r="A141" s="13" t="n">
         <v>169</v>
       </c>
@@ -35691,7 +35868,7 @@
         </is>
       </c>
     </row>
-    <row r="165">
+    <row r="165" ht="25" customHeight="1">
       <c r="A165" s="8" t="n">
         <v>193</v>
       </c>
@@ -36171,7 +36348,7 @@
         </is>
       </c>
     </row>
-    <row r="171">
+    <row r="171" ht="25" customHeight="1">
       <c r="A171" s="8" t="n">
         <v>200</v>
       </c>
@@ -42177,7 +42354,7 @@
       </c>
       <c r="R247" s="8" t="n"/>
     </row>
-    <row r="248">
+    <row r="248" ht="25" customHeight="1">
       <c r="A248" s="8" t="n">
         <v>277</v>
       </c>
@@ -44924,7 +45101,7 @@
       </c>
       <c r="R282" s="8" t="n"/>
     </row>
-    <row r="283">
+    <row r="283" ht="25" customHeight="1">
       <c r="A283" s="8" t="n">
         <v>312</v>
       </c>
@@ -45005,7 +45182,7 @@
       </c>
       <c r="R283" s="8" t="n"/>
     </row>
-    <row r="284">
+    <row r="284" ht="25" customHeight="1">
       <c r="A284" s="8" t="n">
         <v>313</v>
       </c>
@@ -45321,7 +45498,7 @@
       </c>
       <c r="R287" s="8" t="n"/>
     </row>
-    <row r="288">
+    <row r="288" ht="25" customHeight="1">
       <c r="A288" s="8" t="n">
         <v>317</v>
       </c>
@@ -45402,7 +45579,7 @@
       </c>
       <c r="R288" s="8" t="n"/>
     </row>
-    <row r="289">
+    <row r="289" ht="25" customHeight="1">
       <c r="A289" s="8" t="n">
         <v>318</v>
       </c>
@@ -45483,7 +45660,7 @@
       </c>
       <c r="R289" s="8" t="n"/>
     </row>
-    <row r="290">
+    <row r="290" ht="25" customHeight="1">
       <c r="A290" s="8" t="n">
         <v>319</v>
       </c>
@@ -45564,7 +45741,7 @@
       </c>
       <c r="R290" s="8" t="n"/>
     </row>
-    <row r="291">
+    <row r="291" ht="25" customHeight="1">
       <c r="A291" s="8" t="n">
         <v>320</v>
       </c>
@@ -45641,7 +45818,7 @@
       </c>
       <c r="R291" s="8" t="n"/>
     </row>
-    <row r="292">
+    <row r="292" ht="25" customHeight="1">
       <c r="A292" s="8" t="n">
         <v>321</v>
       </c>
@@ -45718,7 +45895,7 @@
       </c>
       <c r="R292" s="8" t="n"/>
     </row>
-    <row r="293">
+    <row r="293" ht="25" customHeight="1">
       <c r="A293" s="8" t="n">
         <v>322</v>
       </c>
@@ -45795,7 +45972,7 @@
       </c>
       <c r="R293" s="8" t="n"/>
     </row>
-    <row r="294">
+    <row r="294" ht="25" customHeight="1">
       <c r="A294" s="8" t="n">
         <v>323</v>
       </c>
@@ -46107,7 +46284,7 @@
       </c>
       <c r="R297" s="8" t="n"/>
     </row>
-    <row r="298">
+    <row r="298" ht="25" customHeight="1">
       <c r="A298" s="8" t="n">
         <v>327</v>
       </c>
@@ -46350,7 +46527,7 @@
       </c>
       <c r="R300" s="8" t="n"/>
     </row>
-    <row r="301">
+    <row r="301" ht="25" customHeight="1">
       <c r="A301" s="8" t="n">
         <v>330</v>
       </c>
@@ -46585,7 +46762,7 @@
       </c>
       <c r="R303" s="8" t="n"/>
     </row>
-    <row r="304">
+    <row r="304" ht="25" customHeight="1">
       <c r="A304" s="8" t="n">
         <v>333</v>
       </c>
@@ -46824,7 +47001,7 @@
       </c>
       <c r="R306" s="8" t="n"/>
     </row>
-    <row r="307">
+    <row r="307" ht="25" customHeight="1">
       <c r="A307" s="8" t="n">
         <v>336</v>
       </c>
@@ -46982,7 +47159,7 @@
       </c>
       <c r="R308" s="8" t="n"/>
     </row>
-    <row r="309">
+    <row r="309" ht="25" customHeight="1">
       <c r="A309" s="8" t="n">
         <v>338</v>
       </c>
@@ -47063,7 +47240,7 @@
       </c>
       <c r="R309" s="8" t="n"/>
     </row>
-    <row r="310">
+    <row r="310" ht="25" customHeight="1">
       <c r="A310" s="8" t="n">
         <v>339</v>
       </c>
@@ -55329,7 +55506,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="37.5" customHeight="1">
       <c r="A10" s="27" t="n">
         <v>9</v>
       </c>
@@ -55407,7 +55584,7 @@
       <c r="Q10" s="27" t="n"/>
       <c r="R10" s="27" t="n"/>
     </row>
-    <row r="11">
+    <row r="11" ht="25" customHeight="1">
       <c r="A11" s="27" t="n">
         <v>10</v>
       </c>
@@ -55563,7 +55740,7 @@
       <c r="Q12" s="27" t="n"/>
       <c r="R12" s="27" t="n"/>
     </row>
-    <row r="13">
+    <row r="13" ht="25" customHeight="1">
       <c r="A13" s="27" t="n">
         <v>12</v>
       </c>
@@ -56486,8 +56663,8 @@
           <t>EQ</t>
         </is>
       </c>
-      <c r="D23" s="8" t="n">
-        <v>30</v>
+      <c r="D23" s="30" t="n">
+        <v>365</v>
       </c>
       <c r="E23" s="4" t="n"/>
       <c r="F23" s="8" t="inlineStr">
@@ -56500,9 +56677,9 @@
           <t>SOURCE_ATOM</t>
         </is>
       </c>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>사용자별 최근 30일 일반·식후 목표를 최신순으로 조회</t>
+      <c r="H23" s="30" t="inlineStr">
+        <is>
+          <t>사용자별 최근 365일 일반·식후 목표를 최신순으로 조회</t>
         </is>
       </c>
     </row>
@@ -60258,7 +60435,7 @@
         </is>
       </c>
     </row>
-    <row r="64">
+    <row r="64" ht="25" customHeight="1">
       <c r="A64" s="8" t="inlineStr">
         <is>
           <t>CFG-065</t>
@@ -60274,9 +60451,9 @@
           <t>목표 최근 노출 조회 기간</t>
         </is>
       </c>
-      <c r="D64" s="4" t="inlineStr">
-        <is>
-          <t>30일</t>
+      <c r="D64" s="29" t="inlineStr">
+        <is>
+          <t>365일</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
@@ -60284,9 +60461,9 @@
           <t>전체 목표 반복 방지</t>
         </is>
       </c>
-      <c r="F64" s="4" t="inlineStr">
-        <is>
-          <t>일반·식후 모두 최근 30일 미노출 우선, 모두 노출 시 가장 오래된 문구 우선</t>
+      <c r="F64" s="29" t="inlineStr">
+        <is>
+          <t>일반·식후 모두 최근 365일 미노출 우선, 모두 노출 시 가장 오래된 문구 우선. 긴 문구 목록도 1년 안에 한 바퀴 돎</t>
         </is>
       </c>
     </row>
